--- a/Cuadrante_Marzo_2026.xlsx
+++ b/Cuadrante_Marzo_2026.xlsx
@@ -501,7 +501,7 @@
     <row r="1" ht="25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CUADRANTE HORARIO - MARZO 2026 - JAÉN</t>
+          <t>CUADRANTE HORARIO - MARZO 2026 - JAÉN CAPITAL</t>
         </is>
       </c>
     </row>
@@ -728,106 +728,106 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:56</t>
+          <t>07:04-14:58</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:04</t>
+          <t>06:55-15:01</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>08:03-13:56
-15:04-17:32</t>
+          <t>07:55-13:56
+14:55-17:27</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:02</t>
+          <t>07:01-14:56</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:55</t>
+          <t>07:03-15:01</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:56</t>
+          <t>06:58-14:57</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:00</t>
+          <t>07:04-15:02</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:01</t>
+          <t>06:55-15:01</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
+          <t>07:55-14:02
+15:03-17:33</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>06:55-15:03</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>07:00-14:58</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>07:01-15:02</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>06:58-15:05</t>
+        </is>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>06:56-14:58</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>08:01-13:56
+14:55-17:34</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>07:00-15:04</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>07:04-14:56</t>
+        </is>
+      </c>
+      <c r="S5" s="6" t="inlineStr">
+        <is>
+          <t>08:55-13:55</t>
+        </is>
+      </c>
+      <c r="T5" s="6" t="inlineStr">
+        <is>
+          <t>07:03-14:55</t>
+        </is>
+      </c>
+      <c r="U5" s="6" t="inlineStr">
+        <is>
           <t>07:55-13:57
-14:57-17:31</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>06:58-14:59</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>06:55-14:56</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>06:59-15:04</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>06:55-14:58</t>
-        </is>
-      </c>
-      <c r="O5" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:05</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>08:02-13:58
-15:03-17:30</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>06:59-14:55</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>07:04-15:05</t>
-        </is>
-      </c>
-      <c r="S5" s="6" t="inlineStr">
-        <is>
-          <t>08:57-14:03</t>
-        </is>
-      </c>
-      <c r="T5" s="6" t="inlineStr">
-        <is>
-          <t>07:04-15:04</t>
-        </is>
-      </c>
-      <c r="U5" s="6" t="inlineStr">
-        <is>
-          <t>07:59-14:05
-15:01-17:34</t>
+15:04-17:28</t>
         </is>
       </c>
     </row>
@@ -839,106 +839,106 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
+          <t>06:59-14:59</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:00</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>07:56-14:00
+14:56-17:27</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>06:56-15:05</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>07:00-15:02</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>06:58-14:59</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>07:04-15:00</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>07:01-14:58</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>07:59-14:04
+15:00-17:34</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>07:03-15:02</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>06:58-15:02</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>06:58-15:01</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>07:00-15:03</t>
+        </is>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>07:00-14:58</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>08:03-14:04
+15:02-17:30</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>07:04-14:55</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
           <t>06:57-14:56</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:59</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>08:04-13:55
-15:01-17:35</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>07:00-15:02</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>07:01-14:56</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>07:03-14:57</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>07:00-14:58</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>07:00-14:57</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>07:59-14:00
-15:01-17:31</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>07:03-14:55</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>06:58-14:55</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>07:04-14:56</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:56</t>
-        </is>
-      </c>
-      <c r="O6" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:56</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>08:01-14:02
-15:05-17:31</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>06:58-14:55</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>07:00-14:58</t>
-        </is>
-      </c>
       <c r="S6" s="6" t="inlineStr">
         <is>
-          <t>08:59-14:01</t>
+          <t>08:55-14:02</t>
         </is>
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:05</t>
+          <t>07:00-15:04</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
         <is>
-          <t>08:03-13:57
-14:58-17:35</t>
+          <t>08:02-14:00
+14:59-17:29</t>
         </is>
       </c>
     </row>
@@ -950,106 +950,106 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:57</t>
+          <t>07:05-15:01</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:56</t>
+          <t>06:56-14:58</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
+          <t>07:57-14:05
+14:58-17:35</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>07:03-15:01</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:02</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:04</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>07:00-15:03</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>07:02-14:59</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>08:05-14:05
+14:58-17:29</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>07:05-15:02</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>06:58-14:56</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>07:03-14:56</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>07:00-15:01</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>06:58-14:58</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
           <t>08:00-13:56
-14:56-17:32</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>07:04-15:05</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:04</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>07:01-15:04</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>07:04-15:05</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:59</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>07:56-14:01
-15:04-17:34</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>06:56-14:59</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:55</t>
-        </is>
-      </c>
-      <c r="M7" s="6" t="inlineStr">
-        <is>
-          <t>07:04-15:02</t>
-        </is>
-      </c>
-      <c r="N7" s="6" t="inlineStr">
-        <is>
-          <t>06:57-15:03</t>
-        </is>
-      </c>
-      <c r="O7" s="6" t="inlineStr">
-        <is>
-          <t>06:57-14:55</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>07:57-14:01
-15:00-17:30</t>
+14:57-17:28</t>
         </is>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
+          <t>07:03-15:01</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
           <t>07:02-15:00</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>07:03-15:05</t>
-        </is>
-      </c>
       <c r="S7" s="6" t="inlineStr">
         <is>
-          <t>09:00-14:05</t>
+          <t>09:02-14:03</t>
         </is>
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:05</t>
+          <t>06:59-15:00</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
         <is>
-          <t>08:05-13:55
-14:59-17:31</t>
+          <t>07:59-13:58
+15:00-17:34</t>
         </is>
       </c>
     </row>
@@ -1061,106 +1061,106 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:57</t>
+          <t>07:01-14:57</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:57</t>
+          <t>06:58-15:03</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>08:00-13:58
-15:01-17:34</t>
+          <t>08:05-14:00
+15:05-17:25</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:55</t>
+          <t>06:56-15:02</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:01</t>
+          <t>06:55-15:05</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:03</t>
+          <t>07:02-14:58</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
+          <t>06:56-15:02</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>06:58-14:55</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>07:59-13:57
+15:03-17:29</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>07:01-14:55</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>07:04-15:01</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>07:04-14:56</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>06:55-14:55</t>
+        </is>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:00</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>08:01-13:55
+15:00-17:27</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
           <t>06:59-14:59</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>07:03-15:01</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>08:03-13:55
-15:04-17:34</t>
-        </is>
-      </c>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>07:02-14:58</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>07:01-15:03</t>
-        </is>
-      </c>
-      <c r="M8" s="6" t="inlineStr">
-        <is>
-          <t>07:04-14:55</t>
-        </is>
-      </c>
-      <c r="N8" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:05</t>
-        </is>
-      </c>
-      <c r="O8" s="6" t="inlineStr">
-        <is>
-          <t>07:05-15:04</t>
-        </is>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>08:04-14:05
-14:57-17:35</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>06:58-14:59</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>06:57-15:05</t>
-        </is>
-      </c>
       <c r="S8" s="6" t="inlineStr">
         <is>
-          <t>08:57-14:02</t>
+          <t>09:01-13:59</t>
         </is>
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:55</t>
+          <t>06:59-14:56</t>
         </is>
       </c>
       <c r="U8" s="6" t="inlineStr">
         <is>
-          <t>07:57-13:55
-14:55-17:28</t>
+          <t>08:04-14:01
+15:05-17:28</t>
         </is>
       </c>
     </row>
@@ -1172,106 +1172,106 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
+          <t>06:55-14:55</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>06:58-14:58</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>08:05-14:01
+14:56-17:30</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>07:05-15:00</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>07:03-15:04</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>06:57-15:02</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>07:03-14:55</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>07:02-14:57</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>08:05-14:03
+14:59-17:32</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>07:00-15:03</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>06:59-14:57</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>07:01-15:05</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>07:05-15:03</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>07:01-15:01</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>07:55-13:58
+15:01-17:33</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>06:55-14:58</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>06:57-15:05</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>09:02-14:04</t>
+        </is>
+      </c>
+      <c r="T9" s="6" t="inlineStr">
+        <is>
           <t>06:59-15:05</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>06:57-14:59</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>07:57-14:03
-14:57-17:31</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>06:59-14:59</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>07:03-14:59</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>07:02-14:57</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>06:57-14:58</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:03</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>08:03-14:05
-14:56-17:33</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:58</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:05</t>
-        </is>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>06:55-14:58</t>
-        </is>
-      </c>
-      <c r="N9" s="6" t="inlineStr">
-        <is>
-          <t>07:04-14:55</t>
-        </is>
-      </c>
-      <c r="O9" s="6" t="inlineStr">
-        <is>
-          <t>07:00-15:02</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>08:03-14:03
-15:02-17:33</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:59</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>06:58-14:58</t>
-        </is>
-      </c>
-      <c r="S9" s="6" t="inlineStr">
-        <is>
-          <t>09:05-14:02</t>
-        </is>
-      </c>
-      <c r="T9" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:04</t>
-        </is>
-      </c>
       <c r="U9" s="6" t="inlineStr">
         <is>
-          <t>08:00-14:05
-15:03-17:35</t>
+          <t>08:04-14:00
+15:03-17:27</t>
         </is>
       </c>
     </row>
@@ -1497,106 +1497,106 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:57</t>
+          <t>07:02-14:59</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:05</t>
+          <t>07:05-15:01</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>08:05-14:01
+          <t>07:56-14:05
+15:04-17:31</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>07:01-14:59</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>07:01-14:55</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>07:01-14:58</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>06:57-14:59</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>07:01-15:05</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>08:00-14:01
+14:56-17:34</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>07:02-15:00</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>07:04-15:05</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>07:00-14:59</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>06:56-15:00</t>
+        </is>
+      </c>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>07:04-15:02</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>08:00-13:55
 14:58-17:31</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>06:59-14:58</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:55</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:56</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>06:59-14:55</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>06:56-14:58</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>07:57-13:55
-15:05-17:35</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:01</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="inlineStr">
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>07:04-15:05</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>07:03-14:55</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>09:01-14:00</t>
+        </is>
+      </c>
+      <c r="T12" s="6" t="inlineStr">
         <is>
           <t>07:05-15:00</t>
         </is>
       </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:04</t>
-        </is>
-      </c>
-      <c r="N12" s="6" t="inlineStr">
-        <is>
-          <t>06:58-15:02</t>
-        </is>
-      </c>
-      <c r="O12" s="6" t="inlineStr">
-        <is>
-          <t>06:58-15:04</t>
-        </is>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>07:55-13:59
-15:01-17:35</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>06:59-15:03</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>06:58-14:59</t>
-        </is>
-      </c>
-      <c r="S12" s="6" t="inlineStr">
-        <is>
-          <t>09:05-14:04</t>
-        </is>
-      </c>
-      <c r="T12" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:01</t>
-        </is>
-      </c>
       <c r="U12" s="6" t="inlineStr">
         <is>
-          <t>08:05-13:56
-15:01-17:29</t>
+          <t>08:04-13:59
+14:58-17:31</t>
         </is>
       </c>
     </row>
@@ -1608,106 +1608,106 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:00</t>
+          <t>07:02-15:03</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:04</t>
+          <t>07:01-14:56</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>07:59-13:59
-14:55-17:31</t>
+          <t>08:05-13:57
+15:03-17:35</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:04</t>
+          <t>07:04-15:02</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:59</t>
+          <t>06:55-14:59</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:56</t>
+          <t>07:01-15:05</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:03</t>
+          <t>07:00-15:00</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:00</t>
+          <t>07:01-14:55</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>08:03-14:04
-15:05-17:25</t>
+          <t>08:04-14:01
+14:57-17:29</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:05</t>
+          <t>06:58-15:00</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:55</t>
+          <t>06:56-15:00</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:00</t>
+          <t>06:55-14:59</t>
         </is>
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:03</t>
+          <t>06:56-14:59</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:57</t>
+          <t>06:58-14:57</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>07:59-14:00
-14:58-17:30</t>
+          <t>08:03-14:01
+15:04-17:32</t>
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:00</t>
+          <t>06:55-15:01</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:56</t>
+          <t>06:57-14:58</t>
         </is>
       </c>
       <c r="S13" s="6" t="inlineStr">
         <is>
-          <t>09:04-14:03</t>
+          <t>08:56-14:01</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:58</t>
+          <t>07:02-15:03</t>
         </is>
       </c>
       <c r="U13" s="6" t="inlineStr">
         <is>
-          <t>08:04-14:03
-15:05-17:32</t>
+          <t>08:04-14:01
+14:57-17:35</t>
         </is>
       </c>
     </row>
@@ -1719,106 +1719,106 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:58</t>
+          <t>06:56-15:00</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:58</t>
+          <t>07:01-14:57</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>08:05-14:00
-15:02-17:27</t>
+          <t>07:59-13:56
+14:55-17:33</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:56</t>
+          <t>07:03-14:58</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:04</t>
+          <t>07:04-15:01</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:04</t>
+          <t>06:58-15:01</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:04</t>
+          <t>06:58-15:00</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:04</t>
+          <t>06:57-14:55</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>08:00-13:57
-15:01-17:26</t>
+          <t>08:00-14:03
+14:58-17:28</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:00</t>
+          <t>06:56-14:56</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:58</t>
+          <t>06:59-14:55</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:04</t>
+          <t>07:02-15:05</t>
         </is>
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:58</t>
+          <t>06:57-15:05</t>
         </is>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:58</t>
+          <t>06:58-15:03</t>
         </is>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>08:01-14:05
-15:02-17:27</t>
+          <t>08:04-13:59
+15:02-17:33</t>
         </is>
       </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:00</t>
+          <t>06:59-14:59</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:03</t>
+          <t>07:01-15:03</t>
         </is>
       </c>
       <c r="S14" s="6" t="inlineStr">
         <is>
-          <t>09:02-13:57</t>
+          <t>08:58-13:56</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:57</t>
+          <t>07:02-14:57</t>
         </is>
       </c>
       <c r="U14" s="6" t="inlineStr">
         <is>
-          <t>07:57-14:02
-14:57-17:31</t>
+          <t>08:04-14:02
+15:04-17:34</t>
         </is>
       </c>
     </row>
@@ -1830,106 +1830,106 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:57</t>
+          <t>07:00-15:05</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:55</t>
+          <t>06:58-15:05</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>07:56-13:57
-15:05-17:31</t>
+          <t>08:02-13:59
+15:00-17:27</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:02</t>
+          <t>07:05-15:03</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:00</t>
+          <t>06:58-14:56</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:57</t>
+          <t>07:03-15:04</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:03</t>
+          <t>06:57-15:02</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:01</t>
+          <t>07:03-15:05</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>08:00-13:58
-15:01-17:32</t>
+          <t>08:00-13:57
+15:02-17:32</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:56</t>
+          <t>07:00-14:58</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:58</t>
+          <t>07:05-14:59</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:56</t>
+          <t>07:04-14:56</t>
         </is>
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:05</t>
+          <t>07:02-15:05</t>
         </is>
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:56</t>
+          <t>06:55-14:58</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>07:57-13:57
-15:00-17:34</t>
+          <t>07:58-14:05
+14:57-17:32</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:00</t>
+          <t>06:55-15:00</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:59</t>
+          <t>07:04-15:03</t>
         </is>
       </c>
       <c r="S15" s="6" t="inlineStr">
         <is>
-          <t>08:55-13:59</t>
+          <t>08:55-13:55</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:56</t>
+          <t>07:03-14:56</t>
         </is>
       </c>
       <c r="U15" s="6" t="inlineStr">
         <is>
-          <t>08:01-14:05
-15:04-17:32</t>
+          <t>07:55-14:02
+15:00-17:29</t>
         </is>
       </c>
     </row>
@@ -1941,106 +1941,106 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:01</t>
+          <t>07:04-15:04</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:04</t>
+          <t>07:05-14:56</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>08:01-14:02
-15:04-17:29</t>
+          <t>07:56-14:01
+15:03-17:26</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:58</t>
+          <t>06:57-14:58</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
+          <t>07:05-15:04</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>07:00-14:58</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>07:01-15:03</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>06:57-14:56</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>07:59-14:05
+15:03-17:34</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>07:05-15:04</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
           <t>06:57-15:03</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>06:57-15:03</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>07:00-14:55</t>
+        </is>
+      </c>
+      <c r="O16" s="6" t="inlineStr">
         <is>
           <t>06:58-15:03</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>07:56-13:57
+14:58-17:27</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>07:04-15:00</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>07:00-14:55</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>06:57-14:57</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>08:03-13:57
-14:58-17:25</t>
-        </is>
-      </c>
-      <c r="K16" s="6" t="inlineStr">
-        <is>
-          <t>07:03-15:04</t>
-        </is>
-      </c>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>06:59-14:59</t>
-        </is>
-      </c>
-      <c r="M16" s="6" t="inlineStr">
-        <is>
-          <t>07:03-15:03</t>
-        </is>
-      </c>
-      <c r="N16" s="6" t="inlineStr">
-        <is>
-          <t>07:01-15:02</t>
-        </is>
-      </c>
-      <c r="O16" s="6" t="inlineStr">
-        <is>
-          <t>07:01-14:57</t>
-        </is>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>08:00-13:55
-15:04-17:33</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>07:03-15:02</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:59</t>
-        </is>
-      </c>
       <c r="S16" s="6" t="inlineStr">
         <is>
-          <t>09:03-13:56</t>
+          <t>09:01-14:05</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:03</t>
+          <t>07:02-15:05</t>
         </is>
       </c>
       <c r="U16" s="6" t="inlineStr">
         <is>
-          <t>07:58-13:57
-15:01-17:30</t>
+          <t>07:59-14:00
+15:01-17:31</t>
         </is>
       </c>
     </row>
@@ -2266,106 +2266,106 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:57</t>
+          <t>06:55-15:01</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:59</t>
+          <t>07:04-14:58</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>08:01-13:57
-15:00-17:29</t>
+          <t>08:05-13:55
+14:58-17:30</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:00</t>
+          <t>07:03-15:00</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:00</t>
+          <t>07:01-15:00</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:56</t>
+          <t>07:01-14:58</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:59</t>
+          <t>06:56-14:55</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
+          <t>06:55-15:03</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>07:56-14:05
+14:59-17:32</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>07:04-14:56</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>07:04-14:59</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>06:57-15:02</t>
+        </is>
+      </c>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
           <t>07:02-14:58</t>
         </is>
       </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>07:55-14:03
-14:59-17:25</t>
-        </is>
-      </c>
-      <c r="K19" s="6" t="inlineStr">
-        <is>
-          <t>06:59-14:55</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="inlineStr">
-        <is>
-          <t>07:03-14:57</t>
-        </is>
-      </c>
-      <c r="M19" s="6" t="inlineStr">
-        <is>
-          <t>07:05-15:04</t>
-        </is>
-      </c>
-      <c r="N19" s="6" t="inlineStr">
-        <is>
-          <t>06:59-15:03</t>
-        </is>
-      </c>
       <c r="O19" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:03</t>
+          <t>07:00-14:58</t>
         </is>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>07:59-14:01
-14:57-17:25</t>
+          <t>08:00-14:02
+14:55-17:29</t>
         </is>
       </c>
       <c r="Q19" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:58</t>
+          <t>07:03-15:02</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:59</t>
+          <t>06:59-14:59</t>
         </is>
       </c>
       <c r="S19" s="6" t="inlineStr">
         <is>
-          <t>08:58-13:56</t>
+          <t>09:01-13:59</t>
         </is>
       </c>
       <c r="T19" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:05</t>
+          <t>06:55-15:03</t>
         </is>
       </c>
       <c r="U19" s="6" t="inlineStr">
         <is>
-          <t>08:00-14:02
-15:03-17:26</t>
+          <t>07:58-14:00
+14:56-17:33</t>
         </is>
       </c>
     </row>
@@ -2377,106 +2377,106 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:55</t>
+          <t>06:58-15:05</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:56</t>
+          <t>07:03-15:03</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>07:58-14:04
-15:05-17:33</t>
+          <t>07:56-13:57
+15:05-17:31</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:03</t>
+          <t>06:56-14:59</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:57</t>
+          <t>07:01-15:01</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:58</t>
+          <t>07:01-14:58</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:57</t>
+          <t>06:57-15:02</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:56</t>
+          <t>06:57-15:02</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>07:56-14:04
-15:00-17:25</t>
+          <t>08:03-13:56
+14:56-17:26</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:04</t>
+          <t>07:05-14:58</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:01</t>
+          <t>07:00-14:55</t>
         </is>
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:05</t>
+          <t>06:58-15:02</t>
         </is>
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:03</t>
+          <t>06:59-14:55</t>
         </is>
       </c>
       <c r="O20" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:57</t>
+          <t>07:01-15:02</t>
         </is>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>07:55-14:02
-15:00-17:31</t>
+          <t>07:57-14:02
+14:56-17:26</t>
         </is>
       </c>
       <c r="Q20" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:56</t>
+          <t>06:59-14:56</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:57</t>
+          <t>07:01-15:02</t>
         </is>
       </c>
       <c r="S20" s="6" t="inlineStr">
         <is>
-          <t>09:04-13:58</t>
+          <t>08:57-13:58</t>
         </is>
       </c>
       <c r="T20" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:04</t>
+          <t>07:04-14:55</t>
         </is>
       </c>
       <c r="U20" s="6" t="inlineStr">
         <is>
-          <t>07:55-14:02
-15:02-17:27</t>
+          <t>08:01-14:05
+14:55-17:29</t>
         </is>
       </c>
     </row>
@@ -2488,106 +2488,106 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
+          <t>07:04-15:03</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>07:02-14:58</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>08:01-14:01
+14:55-17:35</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>06:57-14:56</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
           <t>06:56-15:01</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>07:05-15:03</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>08:02-14:04
-15:05-17:25</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>06:55-14:58</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>07:01-15:01</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>07:04-14:56</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>07:02-15:00</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>07:05-15:01</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>07:01-14:57</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>06:57-15:03</t>
-        </is>
-      </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>07:55-14:03
-15:02-17:34</t>
+          <t>08:04-13:59
+14:59-17:27</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:58</t>
+          <t>07:04-14:59</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:00</t>
+          <t>06:55-14:55</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:01</t>
+          <t>06:56-14:59</t>
         </is>
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:59</t>
+          <t>06:58-15:03</t>
         </is>
       </c>
       <c r="O21" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:03</t>
+          <t>06:58-14:56</t>
         </is>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>08:05-14:03
-15:04-17:31</t>
+          <t>08:01-14:01
+15:02-17:27</t>
         </is>
       </c>
       <c r="Q21" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:00</t>
+          <t>06:58-15:01</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:02</t>
+          <t>06:58-14:58</t>
         </is>
       </c>
       <c r="S21" s="6" t="inlineStr">
         <is>
-          <t>09:01-13:56</t>
+          <t>09:04-13:59</t>
         </is>
       </c>
       <c r="T21" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:00</t>
+          <t>07:03-14:55</t>
         </is>
       </c>
       <c r="U21" s="6" t="inlineStr">
         <is>
-          <t>07:58-13:58
-15:01-17:31</t>
+          <t>08:00-14:00
+14:55-17:26</t>
         </is>
       </c>
     </row>
@@ -2599,106 +2599,106 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:04</t>
+          <t>06:58-15:05</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:01</t>
+          <t>07:00-15:03</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>08:05-14:01
-15:03-17:34</t>
+          <t>08:04-13:59
+15:03-17:27</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:59</t>
+          <t>06:58-15:05</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:05</t>
+          <t>06:59-14:55</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:05</t>
+          <t>06:56-15:00</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:56</t>
+          <t>06:55-15:01</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:59</t>
+          <t>06:56-15:01</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>08:05-14:05
-14:58-17:30</t>
+          <t>08:01-14:03
+15:00-17:35</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:04</t>
+          <t>06:55-15:04</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:55</t>
+          <t>06:56-14:55</t>
         </is>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:59</t>
+          <t>07:05-14:59</t>
         </is>
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:04</t>
+          <t>07:02-14:57</t>
         </is>
       </c>
       <c r="O22" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:05</t>
+          <t>06:56-15:01</t>
         </is>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>08:00-14:05
-15:04-17:31</t>
+          <t>08:00-13:56
+15:02-17:35</t>
         </is>
       </c>
       <c r="Q22" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:00</t>
+          <t>06:57-15:03</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:02</t>
+          <t>07:05-14:56</t>
         </is>
       </c>
       <c r="S22" s="6" t="inlineStr">
         <is>
-          <t>09:01-14:01</t>
+          <t>08:58-13:57</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:03</t>
+          <t>07:02-15:01</t>
         </is>
       </c>
       <c r="U22" s="6" t="inlineStr">
         <is>
-          <t>07:57-14:04
-15:03-17:33</t>
+          <t>07:55-14:03
+15:02-17:27</t>
         </is>
       </c>
     </row>
@@ -2710,106 +2710,106 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:58</t>
+          <t>07:05-15:05</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:04</t>
+          <t>06:59-14:57</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>07:55-14:01
-14:57-17:29</t>
+          <t>08:03-14:04
+14:57-17:31</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:00</t>
+          <t>07:02-14:56</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:03</t>
+          <t>07:03-14:56</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
+          <t>07:04-14:59</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
           <t>06:59-15:03</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>07:00-14:59</t>
-        </is>
-      </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:02</t>
+          <t>06:55-14:56</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>07:57-14:02
-15:05-17:34</t>
+          <t>08:00-14:01
+15:04-17:28</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:57</t>
+          <t>07:03-15:02</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:02</t>
+          <t>06:58-15:00</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:03</t>
+          <t>07:01-15:03</t>
         </is>
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:56</t>
+          <t>06:58-14:59</t>
         </is>
       </c>
       <c r="O23" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:05</t>
+          <t>07:03-15:01</t>
         </is>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>08:02-14:02
-14:55-17:28</t>
+          <t>07:58-14:03
+14:55-17:26</t>
         </is>
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:04</t>
+          <t>06:59-14:55</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:05</t>
+          <t>07:05-15:05</t>
         </is>
       </c>
       <c r="S23" s="6" t="inlineStr">
         <is>
-          <t>09:00-14:05</t>
+          <t>08:56-13:58</t>
         </is>
       </c>
       <c r="T23" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:05</t>
+          <t>06:58-15:03</t>
         </is>
       </c>
       <c r="U23" s="6" t="inlineStr">
         <is>
-          <t>07:55-13:59
-15:03-17:26</t>
+          <t>08:04-14:01
+14:59-17:28</t>
         </is>
       </c>
     </row>
@@ -3035,106 +3035,106 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:59</t>
+          <t>07:05-15:01</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:02</t>
+          <t>07:05-14:55</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>08:01-13:55
-15:02-17:35</t>
+          <t>08:05-14:04
+14:56-17:32</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:56</t>
+          <t>07:00-15:02</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:58</t>
+          <t>07:04-15:00</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:59</t>
+          <t>06:55-15:03</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:00</t>
+          <t>07:05-15:02</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:05</t>
+          <t>06:57-14:56</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>08:05-14:01
-14:58-17:28</t>
+          <t>07:58-14:05
+15:00-17:33</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:01</t>
+          <t>06:57-15:02</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:00</t>
+          <t>07:04-15:04</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:04</t>
+          <t>07:04-15:04</t>
         </is>
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:57</t>
+          <t>06:57-14:59</t>
         </is>
       </c>
       <c r="O26" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:57</t>
+          <t>06:57-15:02</t>
         </is>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>07:55-14:01
-14:57-17:25</t>
+          <t>07:58-14:01
+15:01-17:31</t>
         </is>
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:05</t>
+          <t>07:00-15:04</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:58</t>
+          <t>06:56-14:55</t>
         </is>
       </c>
       <c r="S26" s="6" t="inlineStr">
         <is>
-          <t>08:59-14:01</t>
+          <t>09:02-14:04</t>
         </is>
       </c>
       <c r="T26" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:56</t>
+          <t>06:59-14:58</t>
         </is>
       </c>
       <c r="U26" s="6" t="inlineStr">
         <is>
-          <t>08:02-14:00
-15:02-17:35</t>
+          <t>08:01-13:56
+15:01-17:34</t>
         </is>
       </c>
     </row>
@@ -3146,106 +3146,106 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:02</t>
+          <t>06:56-14:59</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
+          <t>06:59-15:01</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>07:59-14:04
+14:56-17:33</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>07:04-15:02</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:00</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>07:01-15:00</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>06:59-14:57</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>07:01-14:59</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>08:05-13:57
+14:55-17:29</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>07:00-14:58</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>07:01-14:59</t>
+        </is>
+      </c>
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:00</t>
+        </is>
+      </c>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:05</t>
+        </is>
+      </c>
+      <c r="O27" s="6" t="inlineStr">
+        <is>
+          <t>07:03-15:03</t>
+        </is>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>07:59-13:59
+15:00-17:28</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:01</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>07:00-14:55</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>08:58-13:59</t>
+        </is>
+      </c>
+      <c r="T27" s="6" t="inlineStr">
+        <is>
           <t>06:56-14:58</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>08:05-14:04
-14:55-17:26</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:57</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>06:56-14:58</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>07:02-14:56</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>06:59-15:01</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>06:58-14:59</t>
-        </is>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
-        <is>
-          <t>07:55-14:05
-15:05-17:25</t>
-        </is>
-      </c>
-      <c r="K27" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:01</t>
-        </is>
-      </c>
-      <c r="L27" s="6" t="inlineStr">
-        <is>
-          <t>07:01-15:05</t>
-        </is>
-      </c>
-      <c r="M27" s="6" t="inlineStr">
-        <is>
-          <t>07:00-15:03</t>
-        </is>
-      </c>
-      <c r="N27" s="6" t="inlineStr">
-        <is>
-          <t>06:57-14:56</t>
-        </is>
-      </c>
-      <c r="O27" s="6" t="inlineStr">
-        <is>
-          <t>07:03-15:05</t>
-        </is>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>08:02-13:56
-15:05-17:31</t>
-        </is>
-      </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>06:55-14:58</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>06:59-15:01</t>
-        </is>
-      </c>
-      <c r="S27" s="6" t="inlineStr">
-        <is>
-          <t>08:57-13:55</t>
-        </is>
-      </c>
-      <c r="T27" s="6" t="inlineStr">
-        <is>
-          <t>07:02-15:01</t>
-        </is>
-      </c>
       <c r="U27" s="6" t="inlineStr">
         <is>
-          <t>08:05-14:01
-14:59-17:33</t>
+          <t>07:58-13:59
+15:01-17:27</t>
         </is>
       </c>
     </row>
@@ -3257,106 +3257,106 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:58</t>
+          <t>07:05-15:00</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:00</t>
+          <t>06:58-15:00</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>08:04-13:59
-15:01-17:34</t>
+          <t>08:05-14:01
+14:57-17:30</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:02</t>
+          <t>06:55-15:01</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:59</t>
+          <t>07:01-15:02</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:03</t>
+          <t>07:01-14:58</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:58</t>
+          <t>06:57-15:01</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:00</t>
+          <t>07:04-15:00</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>08:01-14:05
-15:00-17:26</t>
+          <t>07:59-14:02
+14:57-17:35</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:58</t>
+          <t>06:57-15:04</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:04</t>
+          <t>07:04-14:57</t>
         </is>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:04</t>
+          <t>06:58-14:57</t>
         </is>
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:04</t>
+          <t>07:04-14:59</t>
         </is>
       </c>
       <c r="O28" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:04</t>
+          <t>07:03-15:05</t>
         </is>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>07:59-14:03
-14:59-17:32</t>
+          <t>07:55-13:57
+15:05-17:31</t>
         </is>
       </c>
       <c r="Q28" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:02</t>
+          <t>06:57-14:58</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:59</t>
+          <t>06:55-15:00</t>
         </is>
       </c>
       <c r="S28" s="6" t="inlineStr">
         <is>
-          <t>08:57-13:55</t>
+          <t>08:55-14:03</t>
         </is>
       </c>
       <c r="T28" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:00</t>
+          <t>07:01-15:03</t>
         </is>
       </c>
       <c r="U28" s="6" t="inlineStr">
         <is>
-          <t>07:57-14:00
-14:57-17:25</t>
+          <t>07:56-14:03
+15:04-17:28</t>
         </is>
       </c>
     </row>
@@ -3368,95 +3368,95 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:58</t>
+          <t>07:02-15:04</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:04</t>
+          <t>07:00-15:01</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>08:03-14:02
-15:03-17:31</t>
+          <t>07:58-14:04
+15:02-17:35</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:56</t>
+          <t>07:04-15:05</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:56</t>
+          <t>06:56-14:57</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:03</t>
+          <t>07:00-15:00</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:01</t>
+          <t>07:01-14:57</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:57</t>
+          <t>07:02-15:03</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>08:05-14:05
-15:05-17:26</t>
+          <t>07:59-14:02
+14:55-17:31</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:58</t>
+          <t>07:05-14:57</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:02</t>
+          <t>07:01-15:01</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:05</t>
+          <t>07:01-14:55</t>
         </is>
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:56</t>
+          <t>07:04-15:02</t>
         </is>
       </c>
       <c r="O29" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:57</t>
+          <t>06:55-14:55</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>08:00-14:00
-14:58-17:34</t>
+          <t>08:01-14:02
+14:56-17:34</t>
         </is>
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:58</t>
+          <t>06:58-14:55</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:58</t>
+          <t>06:55-14:56</t>
         </is>
       </c>
       <c r="S29" s="6" t="inlineStr">
         <is>
-          <t>09:05-13:55</t>
+          <t>08:57-14:03</t>
         </is>
       </c>
       <c r="T29" s="6" t="inlineStr">
@@ -3466,8 +3466,8 @@
       </c>
       <c r="U29" s="6" t="inlineStr">
         <is>
-          <t>07:58-14:03
-14:58-17:35</t>
+          <t>07:59-13:58
+15:01-17:27</t>
         </is>
       </c>
     </row>
@@ -3479,106 +3479,106 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
+          <t>06:57-14:55</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>06:56-15:01</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>07:58-13:56
+15:00-17:31</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>06:57-15:04</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:02</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
           <t>06:58-14:55</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>07:02-15:00</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>08:01-13:58
-14:56-17:31</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>07:02-14:56</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>07:02-14:59</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:57</t>
-        </is>
-      </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:58</t>
+          <t>06:59-15:00</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:56</t>
+          <t>07:04-14:58</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>07:55-14:04
-15:00-17:32</t>
+          <t>08:00-13:56
+15:05-17:25</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:01</t>
+          <t>07:00-14:59</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:03</t>
+          <t>07:03-15:03</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
+          <t>07:01-14:59</t>
+        </is>
+      </c>
+      <c r="N30" s="6" t="inlineStr">
+        <is>
+          <t>07:03-15:00</t>
+        </is>
+      </c>
+      <c r="O30" s="6" t="inlineStr">
+        <is>
+          <t>06:55-15:05</t>
+        </is>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>08:00-14:04
+14:56-17:30</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>07:05-15:05</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
           <t>06:58-15:03</t>
         </is>
       </c>
-      <c r="N30" s="6" t="inlineStr">
-        <is>
-          <t>07:01-14:58</t>
-        </is>
-      </c>
-      <c r="O30" s="6" t="inlineStr">
-        <is>
-          <t>06:57-14:58</t>
-        </is>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>07:55-13:59
-14:56-17:33</t>
-        </is>
-      </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>07:05-15:05</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>07:00-15:05</t>
-        </is>
-      </c>
       <c r="S30" s="6" t="inlineStr">
         <is>
-          <t>08:57-13:57</t>
+          <t>09:01-14:01</t>
         </is>
       </c>
       <c r="T30" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:03</t>
+          <t>07:05-14:58</t>
         </is>
       </c>
       <c r="U30" s="6" t="inlineStr">
         <is>
-          <t>07:58-14:03
-14:59-17:34</t>
+          <t>07:58-13:57
+14:59-17:29</t>
         </is>
       </c>
     </row>
@@ -3804,106 +3804,106 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:04</t>
+          <t>06:58-14:57</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:58</t>
+          <t>06:59-14:59</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>07:56-14:02
-14:58-17:26</t>
+          <t>07:59-13:56
+14:55-17:25</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:58</t>
+          <t>06:58-14:58</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:03</t>
+          <t>07:03-15:03</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:04</t>
+          <t>06:56-14:56</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:03</t>
+          <t>07:04-15:02</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:59</t>
+          <t>07:02-15:01</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
+          <t>07:57-14:04
+15:05-17:33</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>06:57-14:57</t>
+        </is>
+      </c>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>07:01-15:01</t>
+        </is>
+      </c>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>06:55-15:02</t>
+        </is>
+      </c>
+      <c r="N33" s="6" t="inlineStr">
+        <is>
+          <t>07:05-15:00</t>
+        </is>
+      </c>
+      <c r="O33" s="6" t="inlineStr">
+        <is>
+          <t>07:05-14:58</t>
+        </is>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>08:01-14:05
+15:05-17:34</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>06:57-15:01</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>06:58-15:00</t>
+        </is>
+      </c>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>09:04-14:02</t>
+        </is>
+      </c>
+      <c r="T33" s="6" t="inlineStr">
+        <is>
+          <t>06:58-15:04</t>
+        </is>
+      </c>
+      <c r="U33" s="6" t="inlineStr">
+        <is>
           <t>08:02-13:57
-14:56-17:27</t>
-        </is>
-      </c>
-      <c r="K33" s="6" t="inlineStr">
-        <is>
-          <t>06:57-15:05</t>
-        </is>
-      </c>
-      <c r="L33" s="6" t="inlineStr">
-        <is>
-          <t>07:02-15:05</t>
-        </is>
-      </c>
-      <c r="M33" s="6" t="inlineStr">
-        <is>
-          <t>07:04-14:59</t>
-        </is>
-      </c>
-      <c r="N33" s="6" t="inlineStr">
-        <is>
-          <t>07:05-15:03</t>
-        </is>
-      </c>
-      <c r="O33" s="6" t="inlineStr">
-        <is>
-          <t>06:58-14:58</t>
-        </is>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>08:00-13:58
-15:00-17:34</t>
-        </is>
-      </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>07:05-15:04</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>07:02-14:57</t>
-        </is>
-      </c>
-      <c r="S33" s="6" t="inlineStr">
-        <is>
-          <t>08:55-13:57</t>
-        </is>
-      </c>
-      <c r="T33" s="6" t="inlineStr">
-        <is>
-          <t>06:57-14:59</t>
-        </is>
-      </c>
-      <c r="U33" s="6" t="inlineStr">
-        <is>
-          <t>08:04-13:57
-15:05-17:27</t>
+15:04-17:27</t>
         </is>
       </c>
     </row>
@@ -3915,106 +3915,106 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:01</t>
+          <t>07:04-15:02</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:03</t>
+          <t>06:59-14:57</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>07:57-14:01
-15:02-17:30</t>
+          <t>08:03-14:03
+14:55-17:30</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
+          <t>06:59-15:02</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>07:02-14:59</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>07:02-14:59</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>06:58-15:05</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:01</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>08:00-14:04
+14:56-17:33</t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>06:56-15:05</t>
+        </is>
+      </c>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>07:03-14:56</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>06:55-15:04</t>
+        </is>
+      </c>
+      <c r="N34" s="6" t="inlineStr">
+        <is>
+          <t>07:02-14:58</t>
+        </is>
+      </c>
+      <c r="O34" s="6" t="inlineStr">
+        <is>
           <t>06:57-15:01</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>07:03-15:01</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>07:01-15:02</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>07:01-14:58</t>
-        </is>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>07:01-15:04</t>
-        </is>
-      </c>
-      <c r="J34" s="6" t="inlineStr">
-        <is>
-          <t>08:03-13:58
-14:58-17:35</t>
-        </is>
-      </c>
-      <c r="K34" s="6" t="inlineStr">
-        <is>
-          <t>06:55-14:58</t>
-        </is>
-      </c>
-      <c r="L34" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:59</t>
-        </is>
-      </c>
-      <c r="M34" s="6" t="inlineStr">
-        <is>
-          <t>06:59-15:04</t>
-        </is>
-      </c>
-      <c r="N34" s="6" t="inlineStr">
-        <is>
-          <t>07:01-15:00</t>
-        </is>
-      </c>
-      <c r="O34" s="6" t="inlineStr">
-        <is>
-          <t>07:04-14:58</t>
-        </is>
-      </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>07:57-14:02
-14:58-17:27</t>
+          <t>08:05-13:55
+14:59-17:31</t>
         </is>
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:59</t>
+          <t>06:58-14:59</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:01</t>
+          <t>06:58-14:57</t>
         </is>
       </c>
       <c r="S34" s="6" t="inlineStr">
         <is>
-          <t>09:03-13:56</t>
+          <t>08:58-13:58</t>
         </is>
       </c>
       <c r="T34" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:00</t>
+          <t>06:56-15:02</t>
         </is>
       </c>
       <c r="U34" s="6" t="inlineStr">
         <is>
-          <t>07:55-13:59
-15:03-17:30</t>
+          <t>08:04-14:03
+15:00-17:30</t>
         </is>
       </c>
     </row>

--- a/Cuadrante_Marzo_2026.xlsx
+++ b/Cuadrante_Marzo_2026.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U34"/>
+  <dimension ref="A1:S34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -494,8 +494,6 @@
     <col width="25" customWidth="1" min="17" max="17"/>
     <col width="25" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
-    <col width="25" customWidth="1" min="20" max="20"/>
-    <col width="25" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -539,75 +537,65 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Cristóbal Rodríguez Campos</t>
+          <t>Fabio Gutiérrez Basante</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Fabio Gutiérrez Basante</t>
+          <t>Francisco Javier Cárdenas Moga</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Francisco Javier Cárdenas Moga</t>
+          <t>Francisco Ordoñez Perabá</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Francisco Ordoñez Perabá</t>
+          <t>Héctor López Ramírez</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Francisco Rodríguez Lendínez</t>
+          <t>Javier Galera Andújar</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Héctor López Ramírez</t>
+          <t>Jesus Montilla Hermoso</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Javier Galera Andújar</t>
+          <t>Juan José Borrás Ferrete</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Jesus Montilla Hermoso</t>
+          <t>Lourdes Fuentes Buendía</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Juan José Borrás Ferrete</t>
+          <t>Luis Miguel Colmenero Cobo</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Lourdes Fuentes Buendía</t>
+          <t>Manuel Martín Martínez</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Luis Miguel Colmenero Cobo</t>
+          <t>Manuel Peinado García</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>Manuel Martín Martínez</t>
+          <t>Tomás García</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>Manuel Peinado García</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>Tomás García</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
         <is>
           <t>Victoria Romero Sabalete</t>
         </is>
@@ -709,16 +697,6 @@
           <t>DESCANSO</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -728,106 +706,96 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:58</t>
+          <t>07:01-14:56</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:01</t>
+          <t>07:01-14:56</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>07:55-13:56
-14:55-17:27</t>
+          <t>07:57-14:03
+14:59-17:28</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:56</t>
+          <t>07:02-14:57</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:01</t>
+          <t>06:58-14:59</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:57</t>
+          <t>07:01-14:57</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:02</t>
+          <t>06:57-14:57</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:01</t>
+          <t>07:56-14:02
+14:57-17:30</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>07:55-14:02
-15:03-17:33</t>
+          <t>06:57-15:01</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:03</t>
+          <t>06:57-15:03</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:58</t>
+          <t>07:02-14:56</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:02</t>
+          <t>06:57-15:02</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:05</t>
+          <t>07:59-14:03
+14:57-17:29</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:58</t>
+          <t>07:03-15:02</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>08:01-13:56
-14:55-17:34</t>
+          <t>07:02-14:59</t>
         </is>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:04</t>
+          <t>08:57-14:00</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:56</t>
+          <t>07:05-14:58</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
         <is>
-          <t>08:55-13:55</t>
-        </is>
-      </c>
-      <c r="T5" s="6" t="inlineStr">
-        <is>
-          <t>07:03-14:55</t>
-        </is>
-      </c>
-      <c r="U5" s="6" t="inlineStr">
-        <is>
-          <t>07:55-13:57
-15:04-17:28</t>
+          <t>08:00-13:55
+15:02-17:26</t>
         </is>
       </c>
     </row>
@@ -839,106 +807,96 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
+          <t>07:04-14:56</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>06:57-15:00</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>07:55-13:58
+14:59-17:28</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>07:02-15:05</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>07:02-15:03</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
           <t>06:59-14:59</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>06:59-15:00</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>07:56-14:00
-14:56-17:27</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>06:58-15:05</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>07:57-13:57
+15:04-17:26</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>06:57-15:00</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>06:56-15:05</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>07:00-15:02</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>06:58-14:59</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>07:04-15:00</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>07:01-14:58</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>07:59-14:04
-15:00-17:34</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>07:03-15:02</t>
-        </is>
-      </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:02</t>
+          <t>06:58-15:03</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:01</t>
+          <t>06:57-15:00</t>
         </is>
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:03</t>
+          <t>08:03-13:56
+15:02-17:27</t>
         </is>
       </c>
       <c r="O6" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:58</t>
+          <t>06:56-15:01</t>
         </is>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>08:03-14:04
-15:02-17:30</t>
+          <t>06:57-14:57</t>
         </is>
       </c>
       <c r="Q6" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:55</t>
+          <t>08:55-13:55</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:56</t>
+          <t>07:05-15:00</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
         <is>
-          <t>08:55-14:02</t>
-        </is>
-      </c>
-      <c r="T6" s="6" t="inlineStr">
-        <is>
-          <t>07:00-15:04</t>
-        </is>
-      </c>
-      <c r="U6" s="6" t="inlineStr">
-        <is>
-          <t>08:02-14:00
-14:59-17:29</t>
+          <t>07:58-13:56
+15:00-17:27</t>
         </is>
       </c>
     </row>
@@ -950,106 +908,96 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:01</t>
+          <t>07:04-14:59</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:58</t>
+          <t>06:59-14:57</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>07:57-14:05
-14:58-17:35</t>
+          <t>08:00-14:03
+15:04-17:29</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:01</t>
+          <t>06:56-15:03</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:02</t>
+          <t>07:02-15:00</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:04</t>
+          <t>06:55-15:05</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:03</t>
+          <t>06:58-15:03</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:59</t>
+          <t>08:01-14:03
+14:56-17:35</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>08:05-14:05
-14:58-17:29</t>
+          <t>06:58-15:00</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:02</t>
+          <t>06:56-14:56</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
+          <t>06:59-14:58</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>07:01-14:59</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>07:55-14:03
+14:58-17:34</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>07:04-15:00</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
           <t>06:58-14:56</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr">
-        <is>
-          <t>07:03-14:56</t>
-        </is>
-      </c>
-      <c r="N7" s="6" t="inlineStr">
-        <is>
-          <t>07:00-15:01</t>
-        </is>
-      </c>
-      <c r="O7" s="6" t="inlineStr">
-        <is>
-          <t>06:58-14:58</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>08:00-13:56
-14:57-17:28</t>
-        </is>
-      </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:01</t>
+          <t>08:59-14:01</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:00</t>
+          <t>06:57-15:03</t>
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
         <is>
-          <t>09:02-14:03</t>
-        </is>
-      </c>
-      <c r="T7" s="6" t="inlineStr">
-        <is>
-          <t>06:59-15:00</t>
-        </is>
-      </c>
-      <c r="U7" s="6" t="inlineStr">
-        <is>
-          <t>07:59-13:58
-15:00-17:34</t>
+          <t>08:03-14:05
+15:04-17:27</t>
         </is>
       </c>
     </row>
@@ -1061,106 +1009,96 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:57</t>
+          <t>06:56-15:01</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:03</t>
+          <t>06:59-14:58</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
+          <t>07:57-13:59
+15:04-17:28</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>06:57-15:02</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>06:55-15:01</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>06:55-15:04</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>07:04-15:05</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>08:00-14:01
+15:05-17:33</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>06:55-15:01</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>06:58-15:02</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>06:55-15:01</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>07:03-15:02</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>08:01-13:56
+14:55-17:29</t>
+        </is>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>06:58-15:04</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>06:58-14:55</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>08:55-13:58</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>06:57-15:01</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
           <t>08:05-14:00
-15:05-17:25</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:02</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:05</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>07:02-14:58</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:02</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>06:58-14:55</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>07:59-13:57
-15:03-17:29</t>
-        </is>
-      </c>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>07:01-14:55</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>07:04-15:01</t>
-        </is>
-      </c>
-      <c r="M8" s="6" t="inlineStr">
-        <is>
-          <t>07:04-14:56</t>
-        </is>
-      </c>
-      <c r="N8" s="6" t="inlineStr">
-        <is>
-          <t>06:55-14:55</t>
-        </is>
-      </c>
-      <c r="O8" s="6" t="inlineStr">
-        <is>
-          <t>06:59-15:00</t>
-        </is>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>08:01-13:55
-15:00-17:27</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>06:59-14:59</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>06:58-14:59</t>
-        </is>
-      </c>
-      <c r="S8" s="6" t="inlineStr">
-        <is>
-          <t>09:01-13:59</t>
-        </is>
-      </c>
-      <c r="T8" s="6" t="inlineStr">
-        <is>
-          <t>06:59-14:56</t>
-        </is>
-      </c>
-      <c r="U8" s="6" t="inlineStr">
-        <is>
-          <t>08:04-14:01
-15:05-17:28</t>
+15:01-17:26</t>
         </is>
       </c>
     </row>
@@ -1172,106 +1110,96 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:55</t>
+          <t>07:03-15:00</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:58</t>
+          <t>07:01-15:01</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>08:05-14:01
-14:56-17:30</t>
+          <t>07:55-14:00
+15:03-17:34</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:00</t>
+          <t>06:56-15:00</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:04</t>
+          <t>07:01-15:02</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:02</t>
+          <t>07:03-15:05</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:55</t>
+          <t>06:57-15:05</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:57</t>
+          <t>08:04-14:03
+14:56-17:26</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>08:05-14:03
-14:59-17:32</t>
+          <t>07:05-14:57</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:03</t>
+          <t>06:57-15:03</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:57</t>
+          <t>06:55-15:04</t>
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:05</t>
+          <t>07:04-15:03</t>
         </is>
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:03</t>
+          <t>07:57-14:05
+15:00-17:26</t>
         </is>
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:01</t>
+          <t>07:03-14:57</t>
         </is>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>07:55-13:58
-15:01-17:33</t>
+          <t>06:55-15:04</t>
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:58</t>
+          <t>09:03-13:55</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:05</t>
+          <t>07:01-15:03</t>
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
         <is>
-          <t>09:02-14:04</t>
-        </is>
-      </c>
-      <c r="T9" s="6" t="inlineStr">
-        <is>
-          <t>06:59-15:05</t>
-        </is>
-      </c>
-      <c r="U9" s="6" t="inlineStr">
-        <is>
-          <t>08:04-14:00
-15:03-17:27</t>
+          <t>08:02-13:57
+14:59-17:35</t>
         </is>
       </c>
     </row>
@@ -1371,16 +1299,6 @@
           <t>DESCANSO</t>
         </is>
       </c>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -1478,16 +1396,6 @@
           <t>DESCANSO</t>
         </is>
       </c>
-      <c r="T11" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -1497,106 +1405,96 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:59</t>
+          <t>07:00-14:55</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:01</t>
+          <t>06:59-15:02</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>07:56-14:05
-15:04-17:31</t>
+          <t>07:56-13:59
+15:01-17:26</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:59</t>
+          <t>06:59-14:57</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:55</t>
+          <t>07:02-14:57</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:58</t>
+          <t>06:55-15:01</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:59</t>
+          <t>07:04-14:55</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:05</t>
+          <t>07:58-14:00
+15:01-17:26</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>08:00-14:01
+          <t>07:01-15:04</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>07:04-14:57</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>07:00-15:00</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>06:55-15:02</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>08:02-13:58
+15:02-17:29</t>
+        </is>
+      </c>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>07:02-15:04</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:04</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>09:01-14:04</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>07:02-14:57</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>08:00-14:00
 14:56-17:34</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>07:02-15:00</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="inlineStr">
-        <is>
-          <t>07:04-15:05</t>
-        </is>
-      </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>07:00-14:59</t>
-        </is>
-      </c>
-      <c r="N12" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:00</t>
-        </is>
-      </c>
-      <c r="O12" s="6" t="inlineStr">
-        <is>
-          <t>07:04-15:02</t>
-        </is>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>08:00-13:55
-14:58-17:31</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>07:04-15:05</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>07:03-14:55</t>
-        </is>
-      </c>
-      <c r="S12" s="6" t="inlineStr">
-        <is>
-          <t>09:01-14:00</t>
-        </is>
-      </c>
-      <c r="T12" s="6" t="inlineStr">
-        <is>
-          <t>07:05-15:00</t>
-        </is>
-      </c>
-      <c r="U12" s="6" t="inlineStr">
-        <is>
-          <t>08:04-13:59
-14:58-17:31</t>
         </is>
       </c>
     </row>
@@ -1608,106 +1506,96 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:03</t>
+          <t>06:57-15:05</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
+          <t>07:03-15:02</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>07:59-13:56
+14:57-17:31</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>07:05-14:55</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>07:02-15:05</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>06:57-14:57</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>06:55-15:05</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>07:56-14:02
+15:01-17:33</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>06:59-14:55</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>07:05-14:59</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>07:04-15:00</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>07:00-15:01</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>08:03-13:57
+15:02-17:33</t>
+        </is>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>06:58-15:03</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
           <t>07:01-14:56</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>08:05-13:57
-15:03-17:35</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>07:04-15:02</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>06:55-14:59</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>07:01-15:05</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>07:00-15:00</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>07:01-14:55</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>08:04-14:01
-14:57-17:29</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>06:58-15:00</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:00</t>
-        </is>
-      </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>06:55-14:59</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="inlineStr">
-        <is>
-          <t>06:56-14:59</t>
-        </is>
-      </c>
-      <c r="O13" s="6" t="inlineStr">
-        <is>
-          <t>06:58-14:57</t>
-        </is>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>08:03-14:01
-15:04-17:32</t>
-        </is>
-      </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:01</t>
+          <t>08:58-13:55</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:58</t>
+          <t>06:59-15:00</t>
         </is>
       </c>
       <c r="S13" s="6" t="inlineStr">
         <is>
-          <t>08:56-14:01</t>
-        </is>
-      </c>
-      <c r="T13" s="6" t="inlineStr">
-        <is>
-          <t>07:02-15:03</t>
-        </is>
-      </c>
-      <c r="U13" s="6" t="inlineStr">
-        <is>
-          <t>08:04-14:01
-14:57-17:35</t>
+          <t>07:57-13:55
+15:00-17:31</t>
         </is>
       </c>
     </row>
@@ -1719,106 +1607,96 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:00</t>
+          <t>07:03-14:59</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:57</t>
+          <t>07:05-14:55</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>07:59-13:56
-14:55-17:33</t>
+          <t>07:55-13:59
+15:00-17:27</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:58</t>
+          <t>07:05-14:59</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:01</t>
+          <t>06:57-15:05</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:01</t>
+          <t>07:05-15:00</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:00</t>
+          <t>07:05-15:01</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:55</t>
+          <t>08:03-13:58
+15:01-17:26</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>08:00-14:03
-14:58-17:28</t>
+          <t>07:05-15:00</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:56</t>
+          <t>06:55-15:05</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:55</t>
+          <t>07:04-15:00</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:05</t>
+          <t>06:59-15:04</t>
         </is>
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:05</t>
+          <t>08:04-13:57
+14:55-17:26</t>
         </is>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:03</t>
+          <t>06:58-14:58</t>
         </is>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>08:04-13:59
-15:02-17:33</t>
+          <t>06:59-15:05</t>
         </is>
       </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:59</t>
+          <t>09:01-14:01</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:03</t>
+          <t>06:58-14:56</t>
         </is>
       </c>
       <c r="S14" s="6" t="inlineStr">
         <is>
-          <t>08:58-13:56</t>
-        </is>
-      </c>
-      <c r="T14" s="6" t="inlineStr">
-        <is>
-          <t>07:02-14:57</t>
-        </is>
-      </c>
-      <c r="U14" s="6" t="inlineStr">
-        <is>
-          <t>08:04-14:02
-15:04-17:34</t>
+          <t>08:02-13:58
+15:00-17:29</t>
         </is>
       </c>
     </row>
@@ -1830,35 +1708,35 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
+          <t>07:02-15:02</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>07:05-15:04</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>07:59-13:57
+15:04-17:28</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>06:55-15:01</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>06:58-14:58</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
           <t>07:00-15:05</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>06:58-15:05</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>08:02-13:59
-15:00-17:27</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>07:05-15:03</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>06:58-14:56</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>07:03-15:04</t>
-        </is>
-      </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
           <t>06:57-15:02</t>
@@ -1866,70 +1744,60 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:05</t>
+          <t>07:57-14:03
+15:02-17:35</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>08:00-13:57
-15:02-17:32</t>
+          <t>07:02-14:56</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:58</t>
+          <t>07:05-14:58</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:59</t>
+          <t>06:59-14:55</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:56</t>
+          <t>07:03-15:00</t>
         </is>
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:05</t>
+          <t>07:59-14:00
+15:00-17:34</t>
         </is>
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:58</t>
+          <t>06:56-15:01</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>07:58-14:05
-14:57-17:32</t>
+          <t>07:01-14:58</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:00</t>
+          <t>09:02-14:03</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:03</t>
+          <t>06:57-15:02</t>
         </is>
       </c>
       <c r="S15" s="6" t="inlineStr">
         <is>
-          <t>08:55-13:55</t>
-        </is>
-      </c>
-      <c r="T15" s="6" t="inlineStr">
-        <is>
-          <t>07:03-14:56</t>
-        </is>
-      </c>
-      <c r="U15" s="6" t="inlineStr">
-        <is>
-          <t>07:55-14:02
-15:00-17:29</t>
+          <t>08:05-14:02
+14:59-17:29</t>
         </is>
       </c>
     </row>
@@ -1941,106 +1809,96 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:04</t>
+          <t>06:56-15:04</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
+          <t>06:58-14:56</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>08:02-14:04
+14:55-17:32</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>06:59-14:55</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>07:03-14:56</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
           <t>07:05-14:56</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>07:56-14:01
-15:03-17:26</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>06:57-14:58</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>07:05-15:04</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>07:00-14:58</t>
-        </is>
-      </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:03</t>
+          <t>06:58-15:05</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:56</t>
+          <t>08:03-14:05
+15:04-17:32</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>07:59-14:05
-15:03-17:34</t>
+          <t>07:03-14:57</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:04</t>
+          <t>07:02-14:57</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:03</t>
+          <t>07:00-14:57</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:03</t>
+          <t>07:00-15:01</t>
         </is>
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:55</t>
+          <t>08:03-14:04
+15:04-17:30</t>
         </is>
       </c>
       <c r="O16" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:03</t>
+          <t>07:05-14:55</t>
         </is>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>07:56-13:57
-14:58-17:27</t>
+          <t>07:04-15:05</t>
         </is>
       </c>
       <c r="Q16" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:00</t>
+          <t>09:05-14:01</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:55</t>
+          <t>07:05-15:05</t>
         </is>
       </c>
       <c r="S16" s="6" t="inlineStr">
         <is>
-          <t>09:01-14:05</t>
-        </is>
-      </c>
-      <c r="T16" s="6" t="inlineStr">
-        <is>
-          <t>07:02-15:05</t>
-        </is>
-      </c>
-      <c r="U16" s="6" t="inlineStr">
-        <is>
-          <t>07:59-14:00
-15:01-17:31</t>
+          <t>08:03-13:59
+14:58-17:25</t>
         </is>
       </c>
     </row>
@@ -2140,16 +1998,6 @@
           <t>DESCANSO</t>
         </is>
       </c>
-      <c r="T17" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
-      <c r="U17" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
@@ -2247,16 +2095,6 @@
           <t>DESCANSO</t>
         </is>
       </c>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
-      <c r="U18" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
@@ -2266,106 +2104,96 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:01</t>
+          <t>07:02-15:00</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:58</t>
+          <t>06:57-15:00</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>08:05-13:55
-14:58-17:30</t>
+          <t>07:57-13:59
+14:59-17:28</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:00</t>
+          <t>06:59-15:04</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:00</t>
+          <t>06:58-14:57</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:58</t>
+          <t>06:58-14:56</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
+          <t>07:05-15:04</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>08:02-14:03
+15:04-17:26</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:02</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
           <t>06:56-14:55</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:03</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>07:56-14:05
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:00</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>07:05-15:03</t>
+        </is>
+      </c>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t>08:02-13:59
 14:59-17:32</t>
         </is>
       </c>
-      <c r="K19" s="6" t="inlineStr">
-        <is>
-          <t>07:04-14:56</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="inlineStr">
-        <is>
-          <t>07:04-14:59</t>
-        </is>
-      </c>
-      <c r="M19" s="6" t="inlineStr">
-        <is>
-          <t>06:57-15:02</t>
-        </is>
-      </c>
-      <c r="N19" s="6" t="inlineStr">
-        <is>
-          <t>07:02-14:58</t>
-        </is>
-      </c>
       <c r="O19" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:58</t>
+          <t>06:55-14:55</t>
         </is>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>08:00-14:02
-14:55-17:29</t>
+          <t>07:03-15:04</t>
         </is>
       </c>
       <c r="Q19" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:02</t>
+          <t>09:00-13:59</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:59</t>
+          <t>06:56-15:03</t>
         </is>
       </c>
       <c r="S19" s="6" t="inlineStr">
         <is>
-          <t>09:01-13:59</t>
-        </is>
-      </c>
-      <c r="T19" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:03</t>
-        </is>
-      </c>
-      <c r="U19" s="6" t="inlineStr">
-        <is>
-          <t>07:58-14:00
-14:56-17:33</t>
+          <t>08:02-14:04
+15:02-17:27</t>
         </is>
       </c>
     </row>
@@ -2377,106 +2205,96 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:05</t>
+          <t>06:56-14:55</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
+          <t>06:56-14:55</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>08:03-14:05
+14:55-17:25</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>06:56-15:00</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>06:58-14:55</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>06:58-15:01</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>07:00-15:04</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>07:58-14:03
+14:59-17:25</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>06:58-15:04</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>07:03-15:00</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
           <t>07:03-15:03</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>07:56-13:57
-15:05-17:31</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>06:56-14:59</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>07:01-15:01</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>07:01-14:58</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>06:57-15:02</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>06:57-15:02</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>08:03-13:56
-14:56-17:26</t>
-        </is>
-      </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:58</t>
-        </is>
-      </c>
-      <c r="L20" s="6" t="inlineStr">
-        <is>
-          <t>07:00-14:55</t>
-        </is>
-      </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:02</t>
+          <t>06:59-15:04</t>
         </is>
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:55</t>
+          <t>07:59-14:03
+15:05-17:29</t>
         </is>
       </c>
       <c r="O20" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:02</t>
+          <t>06:56-15:03</t>
         </is>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>07:57-14:02
-14:56-17:26</t>
+          <t>06:57-15:01</t>
         </is>
       </c>
       <c r="Q20" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:56</t>
+          <t>09:03-14:01</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:02</t>
+          <t>07:03-14:57</t>
         </is>
       </c>
       <c r="S20" s="6" t="inlineStr">
         <is>
-          <t>08:57-13:58</t>
-        </is>
-      </c>
-      <c r="T20" s="6" t="inlineStr">
-        <is>
-          <t>07:04-14:55</t>
-        </is>
-      </c>
-      <c r="U20" s="6" t="inlineStr">
-        <is>
-          <t>08:01-14:05
-14:55-17:29</t>
+          <t>07:56-13:58
+14:56-17:29</t>
         </is>
       </c>
     </row>
@@ -2488,106 +2306,96 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
+          <t>07:00-14:57</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>07:01-14:59</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>08:04-13:57
+14:59-17:35</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:02</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>06:56-15:05</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>07:04-14:55</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>06:56-15:02</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>08:04-14:04
+14:58-17:29</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>07:02-14:57</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>06:56-15:05</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>07:05-15:05</t>
+        </is>
+      </c>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>06:58-15:03</t>
+        </is>
+      </c>
+      <c r="N21" s="6" t="inlineStr">
+        <is>
+          <t>08:02-14:02
+14:59-17:33</t>
+        </is>
+      </c>
+      <c r="O21" s="6" t="inlineStr">
+        <is>
+          <t>07:03-14:57</t>
+        </is>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
           <t>07:04-15:03</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>07:02-14:58</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>08:01-14:01
-14:55-17:35</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>06:57-14:56</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:01</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>07:01-15:01</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>07:04-14:56</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>07:02-15:00</t>
-        </is>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>08:04-13:59
-14:59-17:27</t>
-        </is>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>07:04-14:59</t>
-        </is>
-      </c>
-      <c r="L21" s="6" t="inlineStr">
-        <is>
-          <t>06:55-14:55</t>
-        </is>
-      </c>
-      <c r="M21" s="6" t="inlineStr">
-        <is>
-          <t>06:56-14:59</t>
-        </is>
-      </c>
-      <c r="N21" s="6" t="inlineStr">
-        <is>
-          <t>06:58-15:03</t>
-        </is>
-      </c>
-      <c r="O21" s="6" t="inlineStr">
-        <is>
-          <t>06:58-14:56</t>
-        </is>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
-        <is>
-          <t>08:01-14:01
-15:02-17:27</t>
-        </is>
-      </c>
       <c r="Q21" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:01</t>
+          <t>08:55-14:04</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:58</t>
+          <t>07:01-15:04</t>
         </is>
       </c>
       <c r="S21" s="6" t="inlineStr">
         <is>
-          <t>09:04-13:59</t>
-        </is>
-      </c>
-      <c r="T21" s="6" t="inlineStr">
-        <is>
-          <t>07:03-14:55</t>
-        </is>
-      </c>
-      <c r="U21" s="6" t="inlineStr">
-        <is>
-          <t>08:00-14:00
-14:55-17:26</t>
+          <t>08:02-13:59
+14:57-17:32</t>
         </is>
       </c>
     </row>
@@ -2599,106 +2407,96 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:05</t>
+          <t>06:59-14:58</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:03</t>
+          <t>07:01-15:01</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>08:04-13:59
-15:03-17:27</t>
+          <t>07:56-14:01
+15:05-17:27</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:05</t>
+          <t>06:55-15:03</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:55</t>
+          <t>06:56-14:58</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:00</t>
+          <t>06:59-15:04</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:01</t>
+          <t>07:05-14:57</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:01</t>
+          <t>08:03-14:05
+15:02-17:33</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>08:01-14:03
-15:00-17:35</t>
+          <t>07:03-14:58</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:04</t>
+          <t>07:00-14:59</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:55</t>
+          <t>07:02-15:04</t>
         </is>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:59</t>
+          <t>06:55-14:56</t>
         </is>
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
+          <t>07:58-14:05
+15:01-17:34</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>06:56-15:05</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
           <t>07:02-14:57</t>
         </is>
       </c>
-      <c r="O22" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:01</t>
-        </is>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>08:00-13:56
-15:02-17:35</t>
-        </is>
-      </c>
       <c r="Q22" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:03</t>
+          <t>08:56-14:02</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:56</t>
+          <t>07:01-14:56</t>
         </is>
       </c>
       <c r="S22" s="6" t="inlineStr">
         <is>
-          <t>08:58-13:57</t>
-        </is>
-      </c>
-      <c r="T22" s="6" t="inlineStr">
-        <is>
-          <t>07:02-15:01</t>
-        </is>
-      </c>
-      <c r="U22" s="6" t="inlineStr">
-        <is>
-          <t>07:55-14:03
-15:02-17:27</t>
+          <t>08:01-13:55
+14:57-17:28</t>
         </is>
       </c>
     </row>
@@ -2710,106 +2508,96 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:05</t>
+          <t>07:03-14:55</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:57</t>
+          <t>07:03-15:03</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>08:03-14:04
-14:57-17:31</t>
+          <t>07:56-13:55
+15:02-17:35</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:56</t>
+          <t>06:55-14:57</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:56</t>
+          <t>07:02-14:58</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:59</t>
+          <t>06:56-14:55</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
+          <t>06:59-15:02</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>08:04-14:04
+14:55-17:28</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>07:03-15:01</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>06:57-14:57</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
           <t>06:59-15:03</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>06:55-14:56</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>08:00-14:01
-15:04-17:28</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>07:03-15:02</t>
-        </is>
-      </c>
-      <c r="L23" s="6" t="inlineStr">
-        <is>
-          <t>06:58-15:00</t>
-        </is>
-      </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:03</t>
+          <t>06:57-15:00</t>
         </is>
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:59</t>
+          <t>08:02-13:57
+14:56-17:33</t>
         </is>
       </c>
       <c r="O23" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:01</t>
+          <t>07:00-14:58</t>
         </is>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>07:58-14:03
-14:55-17:26</t>
+          <t>06:58-15:04</t>
         </is>
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:55</t>
+          <t>09:01-13:59</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:05</t>
+          <t>06:56-14:59</t>
         </is>
       </c>
       <c r="S23" s="6" t="inlineStr">
         <is>
-          <t>08:56-13:58</t>
-        </is>
-      </c>
-      <c r="T23" s="6" t="inlineStr">
-        <is>
-          <t>06:58-15:03</t>
-        </is>
-      </c>
-      <c r="U23" s="6" t="inlineStr">
-        <is>
-          <t>08:04-14:01
-14:59-17:28</t>
+          <t>07:58-14:05
+14:57-17:34</t>
         </is>
       </c>
     </row>
@@ -2909,16 +2697,6 @@
           <t>DESCANSO</t>
         </is>
       </c>
-      <c r="T24" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -3016,16 +2794,6 @@
           <t>DESCANSO</t>
         </is>
       </c>
-      <c r="T25" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
-      <c r="U25" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
@@ -3035,106 +2803,96 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:01</t>
+          <t>07:01-15:02</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:55</t>
+          <t>07:01-14:57</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>08:05-14:04
-14:56-17:32</t>
+          <t>08:00-13:57
+14:56-17:29</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:02</t>
+          <t>06:56-14:55</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:00</t>
+          <t>06:59-15:04</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:03</t>
+          <t>06:55-15:02</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:02</t>
+          <t>07:01-15:00</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:56</t>
+          <t>08:01-14:01
+15:03-17:32</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>07:58-14:05
-15:00-17:33</t>
+          <t>07:03-14:57</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:02</t>
+          <t>07:05-14:59</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:04</t>
+          <t>06:56-15:03</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:04</t>
+          <t>07:02-14:57</t>
         </is>
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:59</t>
+          <t>08:05-14:05
+15:05-17:27</t>
         </is>
       </c>
       <c r="O26" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:02</t>
+          <t>06:58-14:55</t>
         </is>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>07:58-14:01
-15:01-17:31</t>
+          <t>07:01-14:58</t>
         </is>
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:04</t>
+          <t>08:57-13:56</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:55</t>
+          <t>07:03-14:58</t>
         </is>
       </c>
       <c r="S26" s="6" t="inlineStr">
         <is>
-          <t>09:02-14:04</t>
-        </is>
-      </c>
-      <c r="T26" s="6" t="inlineStr">
-        <is>
-          <t>06:59-14:58</t>
-        </is>
-      </c>
-      <c r="U26" s="6" t="inlineStr">
-        <is>
-          <t>08:01-13:56
-15:01-17:34</t>
+          <t>08:00-13:56
+15:01-17:32</t>
         </is>
       </c>
     </row>
@@ -3146,106 +2904,96 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:59</t>
+          <t>06:57-15:02</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:01</t>
+          <t>07:05-15:04</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>07:59-14:04
-14:56-17:33</t>
+          <t>08:05-14:05
+15:05-17:26</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:02</t>
+          <t>06:57-15:05</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:00</t>
+          <t>07:02-15:02</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:00</t>
+          <t>07:05-15:01</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:57</t>
+          <t>07:03-14:55</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:59</t>
+          <t>07:55-13:56
+14:57-17:29</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>08:05-13:57
-14:55-17:29</t>
+          <t>07:04-15:04</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:58</t>
+          <t>07:03-14:59</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:59</t>
+          <t>06:55-14:59</t>
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:00</t>
+          <t>07:02-14:55</t>
         </is>
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:05</t>
+          <t>07:58-14:00
+15:00-17:33</t>
         </is>
       </c>
       <c r="O27" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:03</t>
+          <t>06:58-15:01</t>
         </is>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>07:59-13:59
-15:00-17:28</t>
+          <t>06:58-14:56</t>
         </is>
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:01</t>
+          <t>08:57-14:01</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:55</t>
+          <t>07:01-15:02</t>
         </is>
       </c>
       <c r="S27" s="6" t="inlineStr">
         <is>
-          <t>08:58-13:59</t>
-        </is>
-      </c>
-      <c r="T27" s="6" t="inlineStr">
-        <is>
-          <t>06:56-14:58</t>
-        </is>
-      </c>
-      <c r="U27" s="6" t="inlineStr">
-        <is>
-          <t>07:58-13:59
-15:01-17:27</t>
+          <t>07:58-13:58
+15:02-17:25</t>
         </is>
       </c>
     </row>
@@ -3257,105 +3005,95 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:00</t>
+          <t>07:01-14:57</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:00</t>
+          <t>07:01-15:04</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
           <t>08:05-14:01
-14:57-17:30</t>
+15:00-17:30</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:01</t>
+          <t>07:05-14:57</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:02</t>
+          <t>06:57-15:05</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:58</t>
+          <t>07:02-15:02</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:01</t>
+          <t>06:58-14:59</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:00</t>
+          <t>07:55-13:55
+15:04-17:25</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>07:59-14:02
-14:57-17:35</t>
+          <t>06:56-14:59</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:04</t>
+          <t>06:59-15:02</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:57</t>
+          <t>06:58-14:55</t>
         </is>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:57</t>
+          <t>07:04-14:56</t>
         </is>
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:59</t>
+          <t>08:00-14:05
+15:04-17:27</t>
         </is>
       </c>
       <c r="O28" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:05</t>
+          <t>07:03-15:00</t>
         </is>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>07:55-13:57
-15:05-17:31</t>
+          <t>06:58-15:05</t>
         </is>
       </c>
       <c r="Q28" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:58</t>
+          <t>09:05-14:01</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:00</t>
+          <t>07:05-15:01</t>
         </is>
       </c>
       <c r="S28" s="6" t="inlineStr">
         <is>
-          <t>08:55-14:03</t>
-        </is>
-      </c>
-      <c r="T28" s="6" t="inlineStr">
-        <is>
-          <t>07:01-15:03</t>
-        </is>
-      </c>
-      <c r="U28" s="6" t="inlineStr">
-        <is>
-          <t>07:56-14:03
+          <t>08:00-13:56
 15:04-17:28</t>
         </is>
       </c>
@@ -3368,106 +3106,96 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:04</t>
+          <t>07:01-15:04</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:01</t>
+          <t>07:03-15:03</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>07:58-14:04
-15:02-17:35</t>
+          <t>08:04-13:58
+15:02-17:25</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:05</t>
+          <t>07:01-15:03</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:57</t>
+          <t>06:56-14:59</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:00</t>
+          <t>06:55-14:56</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:57</t>
+          <t>07:02-14:59</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:03</t>
+          <t>08:03-13:56
+14:59-17:33</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>07:59-14:02
+          <t>06:59-15:02</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>06:56-14:59</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>07:01-15:01</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>06:59-14:56</t>
+        </is>
+      </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>08:05-13:55
+14:56-17:29</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>06:59-14:58</t>
+        </is>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>07:04-14:56</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>08:57-14:04</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>07:05-15:00</t>
+        </is>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>07:55-13:55
 14:55-17:31</t>
-        </is>
-      </c>
-      <c r="K29" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:57</t>
-        </is>
-      </c>
-      <c r="L29" s="6" t="inlineStr">
-        <is>
-          <t>07:01-15:01</t>
-        </is>
-      </c>
-      <c r="M29" s="6" t="inlineStr">
-        <is>
-          <t>07:01-14:55</t>
-        </is>
-      </c>
-      <c r="N29" s="6" t="inlineStr">
-        <is>
-          <t>07:04-15:02</t>
-        </is>
-      </c>
-      <c r="O29" s="6" t="inlineStr">
-        <is>
-          <t>06:55-14:55</t>
-        </is>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>08:01-14:02
-14:56-17:34</t>
-        </is>
-      </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>06:58-14:55</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>06:55-14:56</t>
-        </is>
-      </c>
-      <c r="S29" s="6" t="inlineStr">
-        <is>
-          <t>08:57-14:03</t>
-        </is>
-      </c>
-      <c r="T29" s="6" t="inlineStr">
-        <is>
-          <t>06:57-15:00</t>
-        </is>
-      </c>
-      <c r="U29" s="6" t="inlineStr">
-        <is>
-          <t>07:59-13:58
-15:01-17:27</t>
         </is>
       </c>
     </row>
@@ -3479,106 +3207,96 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:55</t>
+          <t>06:56-14:59</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:01</t>
+          <t>07:01-14:56</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>07:58-13:56
-15:00-17:31</t>
+          <t>08:03-14:01
+15:04-17:29</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:04</t>
+          <t>07:05-15:00</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:02</t>
+          <t>07:03-15:03</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:55</t>
+          <t>07:00-14:58</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:00</t>
+          <t>06:57-15:03</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:58</t>
+          <t>07:56-14:02
+14:55-17:28</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>08:00-13:56
-15:05-17:25</t>
+          <t>07:04-15:03</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:59</t>
+          <t>07:05-14:59</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:03</t>
+          <t>06:57-14:58</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:59</t>
+          <t>06:56-14:57</t>
         </is>
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:00</t>
+          <t>08:03-14:01
+15:05-17:32</t>
         </is>
       </c>
       <c r="O30" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:05</t>
+          <t>07:05-15:00</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>08:00-14:04
-14:56-17:30</t>
+          <t>07:05-15:04</t>
         </is>
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:05</t>
+          <t>09:04-13:59</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:03</t>
+          <t>07:00-15:00</t>
         </is>
       </c>
       <c r="S30" s="6" t="inlineStr">
         <is>
-          <t>09:01-14:01</t>
-        </is>
-      </c>
-      <c r="T30" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:58</t>
-        </is>
-      </c>
-      <c r="U30" s="6" t="inlineStr">
-        <is>
-          <t>07:58-13:57
-14:59-17:29</t>
+          <t>08:04-13:58
+14:58-17:35</t>
         </is>
       </c>
     </row>
@@ -3678,16 +3396,6 @@
           <t>DESCANSO</t>
         </is>
       </c>
-      <c r="T31" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
-      <c r="U31" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
@@ -3785,16 +3493,6 @@
           <t>DESCANSO</t>
         </is>
       </c>
-      <c r="T32" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
-      <c r="U32" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
@@ -3804,106 +3502,96 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:57</t>
+          <t>07:05-15:02</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:59</t>
+          <t>07:03-14:55</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>07:59-13:56
-14:55-17:25</t>
+          <t>07:59-14:05
+14:57-17:30</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:58</t>
+          <t>06:59-15:02</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:03</t>
+          <t>07:03-15:00</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:56</t>
+          <t>07:04-14:55</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:02</t>
+          <t>06:58-15:01</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:01</t>
+          <t>08:03-13:58
+14:57-17:27</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>07:57-14:04
-15:05-17:33</t>
+          <t>07:04-14:59</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:57</t>
+          <t>07:04-15:01</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:01</t>
+          <t>06:58-15:04</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:02</t>
+          <t>07:04-15:05</t>
         </is>
       </c>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:00</t>
+          <t>08:00-14:00
+15:03-17:28</t>
         </is>
       </c>
       <c r="O33" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:58</t>
+          <t>07:05-15:03</t>
         </is>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>08:01-14:05
-15:05-17:34</t>
+          <t>06:56-14:55</t>
         </is>
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:01</t>
+          <t>09:01-13:59</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:00</t>
+          <t>06:55-14:59</t>
         </is>
       </c>
       <c r="S33" s="6" t="inlineStr">
         <is>
-          <t>09:04-14:02</t>
-        </is>
-      </c>
-      <c r="T33" s="6" t="inlineStr">
-        <is>
-          <t>06:58-15:04</t>
-        </is>
-      </c>
-      <c r="U33" s="6" t="inlineStr">
-        <is>
-          <t>08:02-13:57
-15:04-17:27</t>
+          <t>07:58-13:58
+15:03-17:33</t>
         </is>
       </c>
     </row>
@@ -3915,112 +3603,102 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:02</t>
+          <t>07:03-15:03</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:57</t>
+          <t>07:03-14:57</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>08:03-14:03
-14:55-17:30</t>
+          <t>08:01-14:01
+15:01-17:25</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:02</t>
+          <t>07:01-14:55</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:59</t>
+          <t>06:55-15:05</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:59</t>
+          <t>06:56-14:59</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:05</t>
+          <t>06:57-14:55</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:01</t>
+          <t>07:56-13:59
+14:56-17:29</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>08:00-14:04
-14:56-17:33</t>
+          <t>06:56-14:57</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:05</t>
+          <t>06:56-15:03</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:56</t>
+          <t>07:05-15:05</t>
         </is>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:04</t>
+          <t>07:04-15:00</t>
         </is>
       </c>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:58</t>
+          <t>07:55-14:02
+14:56-17:34</t>
         </is>
       </c>
       <c r="O34" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:01</t>
+          <t>07:02-15:05</t>
         </is>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>08:05-13:55
-14:59-17:31</t>
+          <t>06:55-15:02</t>
         </is>
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:59</t>
+          <t>09:05-14:02</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:57</t>
+          <t>06:57-15:00</t>
         </is>
       </c>
       <c r="S34" s="6" t="inlineStr">
         <is>
-          <t>08:58-13:58</t>
-        </is>
-      </c>
-      <c r="T34" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:02</t>
-        </is>
-      </c>
-      <c r="U34" s="6" t="inlineStr">
-        <is>
-          <t>08:04-14:03
-15:00-17:30</t>
+          <t>08:05-14:05
+14:55-17:29</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Cuadrante_Marzo_2026.xlsx
+++ b/Cuadrante_Marzo_2026.xlsx
@@ -604,7 +604,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>01/03/2026 (Sun)</t>
+          <t>01/03/2026 (dom)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -701,411 +701,411 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>02/03/2026 (Mon)</t>
+          <t>02/03/2026 (lun)</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:56</t>
+          <t>07:02-15:01</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:56</t>
+          <t>07:00-14:55</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>07:57-14:03
-14:59-17:28</t>
+          <t>08:00-13:59
+15:01-17:30</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:57</t>
+          <t>07:02-15:05</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:59</t>
+          <t>06:59-14:59</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:57</t>
+          <t>06:55-15:00</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:57</t>
+          <t>06:57-15:04</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>07:56-14:02
-14:57-17:30</t>
+          <t>07:57-14:00
+15:05-17:25</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:01</t>
+          <t>06:55-15:04</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:03</t>
+          <t>06:59-15:03</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:56</t>
+          <t>06:57-15:05</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:02</t>
+          <t>06:58-14:55</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>07:59-14:03
-14:57-17:29</t>
+          <t>08:00-13:55
+15:02-17:29</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:02</t>
+          <t>06:57-15:05</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:59</t>
+          <t>07:04-14:58</t>
         </is>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>08:57-14:00</t>
+          <t>08:56-14:04</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:58</t>
+          <t>07:04-15:02</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
         <is>
-          <t>08:00-13:55
-15:02-17:26</t>
+          <t>08:02-13:58
+15:01-17:32</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>03/03/2026 (Tue)</t>
+          <t>03/03/2026 (mar)</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:56</t>
+          <t>06:58-15:05</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:00</t>
+          <t>07:01-15:00</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>07:55-13:58
+          <t>07:56-14:00
 14:59-17:28</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:05</t>
+          <t>06:57-15:01</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:03</t>
+          <t>07:04-15:02</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:59</t>
+          <t>07:05-15:00</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:05</t>
+          <t>06:56-14:55</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>07:57-13:57
-15:04-17:26</t>
+          <t>08:01-14:01
+15:04-17:34</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:00</t>
+          <t>06:57-14:58</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:05</t>
+          <t>07:03-14:59</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:03</t>
+          <t>06:58-15:04</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:00</t>
+          <t>06:57-15:04</t>
         </is>
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>08:03-13:56
-15:02-17:27</t>
+          <t>08:05-14:01
+14:59-17:32</t>
         </is>
       </c>
       <c r="O6" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:01</t>
+          <t>06:59-15:01</t>
         </is>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:57</t>
+          <t>06:58-14:58</t>
         </is>
       </c>
       <c r="Q6" s="6" t="inlineStr">
         <is>
-          <t>08:55-13:55</t>
+          <t>08:59-13:55</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:00</t>
+          <t>07:03-15:01</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
         <is>
-          <t>07:58-13:56
-15:00-17:27</t>
+          <t>08:00-14:05
+15:05-17:32</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>04/03/2026 (Wed)</t>
+          <t>04/03/2026 (mié)</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:59</t>
+          <t>07:02-15:00</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:57</t>
+          <t>07:02-14:55</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>08:00-14:03
-15:04-17:29</t>
+          <t>08:05-14:01
+14:56-17:31</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:03</t>
+          <t>07:05-15:02</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:00</t>
+          <t>06:56-14:58</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
+          <t>06:59-14:58</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>07:05-15:00</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>08:04-13:55
+14:59-17:32</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>06:55-15:04</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>06:56-15:02</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>06:59-14:59</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>07:01-15:02</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>08:03-14:00
+15:03-17:25</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>07:04-15:01</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>06:58-15:02</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>09:02-13:56</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
           <t>06:55-15:05</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>06:58-15:03</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>08:01-14:03
-14:56-17:35</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>06:58-15:00</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>06:56-14:56</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="inlineStr">
-        <is>
-          <t>06:59-14:58</t>
-        </is>
-      </c>
-      <c r="M7" s="6" t="inlineStr">
-        <is>
-          <t>07:01-14:59</t>
-        </is>
-      </c>
-      <c r="N7" s="6" t="inlineStr">
-        <is>
-          <t>07:55-14:03
-14:58-17:34</t>
-        </is>
-      </c>
-      <c r="O7" s="6" t="inlineStr">
-        <is>
-          <t>07:04-15:00</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>06:58-14:56</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>08:59-14:01</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>06:57-15:03</t>
-        </is>
-      </c>
       <c r="S7" s="6" t="inlineStr">
         <is>
-          <t>08:03-14:05
-15:04-17:27</t>
+          <t>07:57-14:02
+15:04-17:26</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>05/03/2026 (Thu)</t>
+          <t>05/03/2026 (jue)</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:01</t>
+          <t>06:59-15:01</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:58</t>
+          <t>07:00-15:01</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
+          <t>08:04-13:56
+14:59-17:35</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:01</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>06:55-14:59</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>06:55-14:57</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>07:01-15:00</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>07:57-14:02
+14:58-17:30</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>07:00-14:55</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>07:02-15:04</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>07:01-15:02</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>06:57-15:01</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
           <t>07:57-13:59
-15:04-17:28</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>06:57-15:02</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:01</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:04</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>07:04-15:05</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>08:00-14:01
-15:05-17:33</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:01</t>
-        </is>
-      </c>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>06:58-15:02</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:01</t>
-        </is>
-      </c>
-      <c r="M8" s="6" t="inlineStr">
-        <is>
-          <t>07:03-15:02</t>
-        </is>
-      </c>
-      <c r="N8" s="6" t="inlineStr">
-        <is>
-          <t>08:01-13:56
-14:55-17:29</t>
+14:56-17:29</t>
         </is>
       </c>
       <c r="O8" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:04</t>
+          <t>06:56-14:59</t>
         </is>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:55</t>
+          <t>07:01-15:00</t>
         </is>
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
-          <t>08:55-13:58</t>
+          <t>09:01-14:01</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:01</t>
+          <t>06:58-15:03</t>
         </is>
       </c>
       <c r="S8" s="6" t="inlineStr">
         <is>
-          <t>08:05-14:00
-15:01-17:26</t>
+          <t>07:55-14:00
+15:05-17:32</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>06/03/2026 (Fri)</t>
+          <t>06/03/2026 (vie)</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -1115,54 +1115,54 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:01</t>
+          <t>06:57-14:58</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>07:55-14:00
-15:03-17:34</t>
+          <t>07:58-14:01
+14:58-17:32</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:00</t>
+          <t>07:02-15:03</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:02</t>
+          <t>07:00-15:00</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:05</t>
+          <t>06:56-14:57</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:05</t>
+          <t>07:05-15:04</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>08:04-14:03
-14:56-17:26</t>
+          <t>07:59-14:05
+15:01-17:28</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:57</t>
+          <t>06:57-15:02</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:03</t>
+          <t>06:56-14:59</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:04</t>
+          <t>07:05-14:59</t>
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr">
@@ -1172,41 +1172,41 @@
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>07:57-14:05
-15:00-17:26</t>
+          <t>08:01-13:55
+15:05-17:30</t>
         </is>
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:57</t>
+          <t>07:02-15:03</t>
         </is>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:04</t>
+          <t>07:02-14:56</t>
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
-          <t>09:03-13:55</t>
+          <t>08:55-13:55</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:03</t>
+          <t>06:55-15:01</t>
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
         <is>
-          <t>08:02-13:57
-14:59-17:35</t>
+          <t>08:05-14:04
+14:59-17:27</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>07/03/2026 (Sat)</t>
+          <t>07/03/2026 (sáb)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>08/03/2026 (Sun)</t>
+          <t>08/03/2026 (dom)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1400,512 +1400,512 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>09/03/2026 (Mon)</t>
+          <t>09/03/2026 (lun)</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:55</t>
+          <t>07:03-15:02</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:02</t>
+          <t>06:59-14:59</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>07:56-13:59
-15:01-17:26</t>
+          <t>08:01-13:57
+14:56-17:33</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:57</t>
+          <t>07:05-14:55</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:57</t>
+          <t>07:01-15:05</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:01</t>
+          <t>07:01-15:05</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:55</t>
+          <t>07:02-14:59</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>07:58-14:00
-15:01-17:26</t>
+          <t>08:02-13:58
+15:02-17:33</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:04</t>
+          <t>06:57-15:04</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:57</t>
+          <t>07:01-14:55</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:00</t>
+          <t>06:59-14:55</t>
         </is>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:02</t>
+          <t>06:57-15:05</t>
         </is>
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>08:02-13:58
-15:02-17:29</t>
+          <t>08:01-13:58
+15:00-17:33</t>
         </is>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:04</t>
+          <t>07:05-15:05</t>
         </is>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:04</t>
+          <t>07:00-15:03</t>
         </is>
       </c>
       <c r="Q12" s="6" t="inlineStr">
         <is>
-          <t>09:01-14:04</t>
+          <t>09:01-14:00</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:57</t>
+          <t>06:56-14:58</t>
         </is>
       </c>
       <c r="S12" s="6" t="inlineStr">
         <is>
-          <t>08:00-14:00
-14:56-17:34</t>
+          <t>07:57-13:59
+14:56-17:33</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>10/03/2026 (Tue)</t>
+          <t>10/03/2026 (mar)</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:05</t>
+          <t>06:55-15:00</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:02</t>
+          <t>06:59-15:04</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>07:59-13:56
-14:57-17:31</t>
+          <t>08:03-14:04
+15:00-17:25</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:55</t>
+          <t>07:01-14:58</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:05</t>
+          <t>06:59-15:01</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:57</t>
+          <t>06:58-14:58</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:05</t>
+          <t>07:04-14:57</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>07:56-14:02
-15:01-17:33</t>
+          <t>07:55-13:55
+15:05-17:26</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:55</t>
+          <t>06:55-15:01</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:59</t>
+          <t>06:58-15:03</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:00</t>
+          <t>06:58-15:01</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:01</t>
+          <t>07:00-14:57</t>
         </is>
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>08:03-13:57
-15:02-17:33</t>
+          <t>07:56-14:05
+15:00-17:26</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:03</t>
+          <t>06:58-15:05</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:56</t>
+          <t>07:02-14:58</t>
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
-          <t>08:58-13:55</t>
+          <t>08:55-14:01</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:00</t>
+          <t>07:02-15:04</t>
         </is>
       </c>
       <c r="S13" s="6" t="inlineStr">
         <is>
-          <t>07:57-13:55
-15:00-17:31</t>
+          <t>07:55-14:01
+14:59-17:35</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>11/03/2026 (Wed)</t>
+          <t>11/03/2026 (mié)</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:59</t>
+          <t>06:56-15:03</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:55</t>
+          <t>07:05-15:03</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>07:55-13:59
-15:00-17:27</t>
+          <t>07:58-14:05
+15:05-17:35</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:59</t>
+          <t>07:01-14:59</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:05</t>
+          <t>07:02-15:02</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:00</t>
+          <t>07:05-15:02</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:01</t>
+          <t>06:55-15:05</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>08:03-13:58
-15:01-17:26</t>
+          <t>08:02-13:59
+15:04-17:35</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:00</t>
+          <t>07:00-14:55</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:05</t>
+          <t>06:59-15:00</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:00</t>
+          <t>07:00-14:59</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:04</t>
+          <t>07:04-15:04</t>
         </is>
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>08:04-13:57
-14:55-17:26</t>
+          <t>08:01-14:03
+15:03-17:33</t>
         </is>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:58</t>
+          <t>07:03-14:55</t>
         </is>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:05</t>
+          <t>07:02-14:58</t>
         </is>
       </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
-          <t>09:01-14:01</t>
+          <t>08:56-14:00</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:56</t>
+          <t>06:57-15:03</t>
         </is>
       </c>
       <c r="S14" s="6" t="inlineStr">
         <is>
-          <t>08:02-13:58
-15:00-17:29</t>
+          <t>07:56-14:04
+14:58-17:32</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>12/03/2026 (Thu)</t>
+          <t>12/03/2026 (jue)</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:02</t>
+          <t>06:55-14:56</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:04</t>
+          <t>06:57-15:02</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>07:59-13:57
-15:04-17:28</t>
+          <t>07:58-13:56
+15:01-17:29</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:01</t>
+          <t>07:04-15:00</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:58</t>
+          <t>06:57-14:55</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:05</t>
+          <t>07:03-15:00</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:02</t>
+          <t>06:58-15:03</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>07:57-14:03
-15:02-17:35</t>
+          <t>07:58-13:59
+15:00-17:32</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:56</t>
+          <t>07:04-14:56</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:58</t>
+          <t>06:59-15:05</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:55</t>
+          <t>06:55-15:03</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:00</t>
+          <t>06:56-14:56</t>
         </is>
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>07:59-14:00
-15:00-17:34</t>
+          <t>08:03-14:05
+14:57-17:29</t>
         </is>
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:01</t>
+          <t>07:03-14:58</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:58</t>
+          <t>07:04-14:57</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>09:02-14:03</t>
+          <t>08:55-14:02</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:02</t>
+          <t>07:00-14:56</t>
         </is>
       </c>
       <c r="S15" s="6" t="inlineStr">
         <is>
-          <t>08:05-14:02
-14:59-17:29</t>
+          <t>07:55-13:56
+15:01-17:33</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>13/03/2026 (Fri)</t>
+          <t>13/03/2026 (vie)</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:04</t>
+          <t>06:56-14:56</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:56</t>
+          <t>06:55-15:01</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>08:02-14:04
-14:55-17:32</t>
+          <t>08:00-14:04
+15:00-17:33</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:55</t>
+          <t>06:57-15:03</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:56</t>
+          <t>07:00-15:03</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:56</t>
+          <t>07:03-15:02</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:05</t>
+          <t>07:03-14:59</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>08:03-14:05
-15:04-17:32</t>
+          <t>08:05-13:57
+15:03-17:26</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:57</t>
+          <t>07:01-14:55</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:57</t>
+          <t>07:01-15:05</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:57</t>
+          <t>06:59-15:01</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:01</t>
+          <t>06:55-14:57</t>
         </is>
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>08:03-14:04
-15:04-17:30</t>
+          <t>07:59-13:57
+15:05-17:34</t>
         </is>
       </c>
       <c r="O16" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:55</t>
+          <t>06:58-14:58</t>
         </is>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:05</t>
+          <t>06:55-15:03</t>
         </is>
       </c>
       <c r="Q16" s="6" t="inlineStr">
         <is>
-          <t>09:05-14:01</t>
+          <t>08:56-14:05</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:05</t>
+          <t>06:59-14:59</t>
         </is>
       </c>
       <c r="S16" s="6" t="inlineStr">
         <is>
-          <t>08:03-13:59
-14:58-17:25</t>
+          <t>07:56-14:05
+14:59-17:33</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>14/03/2026 (Sat)</t>
+          <t>14/03/2026 (sáb)</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -2002,7 +2002,7 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>15/03/2026 (Sun)</t>
+          <t>15/03/2026 (dom)</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -2099,287 +2099,287 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>16/03/2026 (Mon)</t>
+          <t>16/03/2026 (lun)</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:00</t>
+          <t>06:59-14:58</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:00</t>
+          <t>07:02-14:58</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>07:57-13:59
-14:59-17:28</t>
+          <t>07:59-14:02
+14:58-17:26</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:04</t>
+          <t>06:56-15:03</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:57</t>
+          <t>07:03-14:59</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:56</t>
+          <t>06:55-15:03</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:04</t>
+          <t>07:04-15:05</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>08:02-14:03
-15:04-17:26</t>
+          <t>07:58-14:05
+15:02-17:28</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:02</t>
+          <t>07:05-15:00</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:55</t>
+          <t>06:58-15:04</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:00</t>
+          <t>07:00-14:59</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:03</t>
+          <t>07:03-14:57</t>
         </is>
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>08:02-13:59
-14:59-17:32</t>
+          <t>08:01-13:59
+14:58-17:32</t>
         </is>
       </c>
       <c r="O19" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:55</t>
+          <t>06:59-14:56</t>
         </is>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:04</t>
+          <t>06:57-14:56</t>
         </is>
       </c>
       <c r="Q19" s="6" t="inlineStr">
         <is>
-          <t>09:00-13:59</t>
+          <t>09:00-14:03</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:03</t>
+          <t>07:00-15:05</t>
         </is>
       </c>
       <c r="S19" s="6" t="inlineStr">
         <is>
-          <t>08:02-14:04
-15:02-17:27</t>
+          <t>08:02-13:56
+15:01-17:29</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>17/03/2026 (Tue)</t>
+          <t>17/03/2026 (mar)</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:55</t>
+          <t>07:03-15:02</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:55</t>
+          <t>06:55-15:00</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>08:03-14:05
-14:55-17:25</t>
+          <t>07:55-14:04
+15:01-17:26</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:00</t>
+          <t>07:05-15:03</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:55</t>
+          <t>06:55-15:04</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:01</t>
+          <t>07:05-14:56</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:04</t>
+          <t>07:00-15:05</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>07:58-14:03
+          <t>08:01-13:56
+14:57-17:34</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>06:55-15:01</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>06:57-15:01</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:03</t>
+        </is>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>07:02-14:55</t>
+        </is>
+      </c>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>08:03-14:00
+14:59-17:29</t>
+        </is>
+      </c>
+      <c r="O20" s="6" t="inlineStr">
+        <is>
+          <t>06:55-14:58</t>
+        </is>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>07:05-15:01</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>08:58-14:01</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>07:00-14:55</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>07:58-14:04
 14:59-17:25</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>06:58-15:04</t>
-        </is>
-      </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>07:03-15:00</t>
-        </is>
-      </c>
-      <c r="L20" s="6" t="inlineStr">
-        <is>
-          <t>07:03-15:03</t>
-        </is>
-      </c>
-      <c r="M20" s="6" t="inlineStr">
-        <is>
-          <t>06:59-15:04</t>
-        </is>
-      </c>
-      <c r="N20" s="6" t="inlineStr">
-        <is>
-          <t>07:59-14:03
-15:05-17:29</t>
-        </is>
-      </c>
-      <c r="O20" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:03</t>
-        </is>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>06:57-15:01</t>
-        </is>
-      </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>09:03-14:01</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>07:03-14:57</t>
-        </is>
-      </c>
-      <c r="S20" s="6" t="inlineStr">
-        <is>
-          <t>07:56-13:58
-14:56-17:29</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>18/03/2026 (Wed)</t>
+          <t>18/03/2026 (mié)</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:57</t>
+          <t>06:59-15:04</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:59</t>
+          <t>07:04-15:04</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>08:04-13:57
-14:59-17:35</t>
+          <t>08:04-14:04
+15:03-17:31</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:02</t>
+          <t>07:02-15:04</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:05</t>
+          <t>07:00-14:59</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:55</t>
+          <t>06:58-15:05</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:02</t>
+          <t>07:00-15:02</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>08:04-14:04
-14:58-17:29</t>
+          <t>08:02-13:57
+15:05-17:34</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:57</t>
+          <t>07:01-14:55</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:05</t>
+          <t>06:55-15:00</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:05</t>
+          <t>07:02-15:01</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:03</t>
+          <t>06:59-14:57</t>
         </is>
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>08:02-14:02
-14:59-17:33</t>
+          <t>08:03-13:55
+15:04-17:25</t>
         </is>
       </c>
       <c r="O21" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:57</t>
+          <t>06:59-15:03</t>
         </is>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:03</t>
+          <t>06:56-14:55</t>
         </is>
       </c>
       <c r="Q21" s="6" t="inlineStr">
@@ -2389,222 +2389,222 @@
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:04</t>
+          <t>06:55-15:05</t>
         </is>
       </c>
       <c r="S21" s="6" t="inlineStr">
         <is>
-          <t>08:02-13:59
-14:57-17:32</t>
+          <t>07:58-13:58
+14:59-17:26</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>19/03/2026 (Thu)</t>
+          <t>19/03/2026 (jue)</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:58</t>
+          <t>07:04-15:03</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
+          <t>07:01-15:04</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>08:05-14:02
+15:01-17:30</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>06:56-15:02</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>07:00-14:59</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>06:56-15:05</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>07:02-15:04</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>07:55-13:58
+14:57-17:28</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>07:04-15:04</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:05</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>07:05-15:04</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>07:04-15:00</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>07:59-13:58
+14:57-17:32</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
           <t>07:01-15:01</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>07:56-14:01
-15:05-17:27</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:03</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>06:56-14:58</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>06:59-15:04</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:57</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>08:03-14:05
-15:02-17:33</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
+      <c r="P22" s="6" t="inlineStr">
         <is>
           <t>07:03-14:58</t>
         </is>
       </c>
-      <c r="K22" s="6" t="inlineStr">
-        <is>
-          <t>07:00-14:59</t>
-        </is>
-      </c>
-      <c r="L22" s="6" t="inlineStr">
-        <is>
-          <t>07:02-15:04</t>
-        </is>
-      </c>
-      <c r="M22" s="6" t="inlineStr">
-        <is>
-          <t>06:55-14:56</t>
-        </is>
-      </c>
-      <c r="N22" s="6" t="inlineStr">
-        <is>
-          <t>07:58-14:05
-15:01-17:34</t>
-        </is>
-      </c>
-      <c r="O22" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:05</t>
-        </is>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>07:02-14:57</t>
-        </is>
-      </c>
       <c r="Q22" s="6" t="inlineStr">
         <is>
-          <t>08:56-14:02</t>
+          <t>09:04-13:58</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:56</t>
+          <t>07:00-15:00</t>
         </is>
       </c>
       <c r="S22" s="6" t="inlineStr">
         <is>
-          <t>08:01-13:55
-14:57-17:28</t>
+          <t>07:57-13:59
+14:56-17:34</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>20/03/2026 (Fri)</t>
+          <t>20/03/2026 (vie)</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:55</t>
+          <t>06:56-14:59</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:03</t>
+          <t>07:01-14:57</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>07:56-13:55
-15:02-17:35</t>
+          <t>07:59-14:01
+15:05-17:31</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:57</t>
+          <t>07:01-14:59</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:58</t>
+          <t>07:01-15:05</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:55</t>
+          <t>07:02-15:05</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:02</t>
+          <t>07:00-15:05</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>08:04-14:04
-14:55-17:28</t>
+          <t>08:05-14:00
+15:03-17:29</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:01</t>
+          <t>06:56-15:01</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:57</t>
+          <t>07:00-14:59</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:03</t>
+          <t>07:04-14:56</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:00</t>
+          <t>07:04-15:02</t>
         </is>
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
-          <t>08:02-13:57
-14:56-17:33</t>
+          <t>08:04-14:00
+15:01-17:26</t>
         </is>
       </c>
       <c r="O23" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:58</t>
+          <t>06:58-15:05</t>
         </is>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:04</t>
+          <t>07:01-14:57</t>
         </is>
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
-          <t>09:01-13:59</t>
+          <t>09:05-13:56</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:59</t>
+          <t>06:59-15:05</t>
         </is>
       </c>
       <c r="S23" s="6" t="inlineStr">
         <is>
-          <t>07:58-14:05
-14:57-17:34</t>
+          <t>08:03-13:58
+14:55-17:30</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>21/03/2026 (Sat)</t>
+          <t>21/03/2026 (sáb)</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -2701,7 +2701,7 @@
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>22/03/2026 (Sun)</t>
+          <t>22/03/2026 (dom)</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -2798,209 +2798,209 @@
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>23/03/2026 (Mon)</t>
+          <t>23/03/2026 (lun)</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:02</t>
+          <t>06:55-14:56</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:57</t>
+          <t>07:04-14:59</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>08:00-13:57
-14:56-17:29</t>
+          <t>07:59-14:05
+14:57-17:27</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
+          <t>07:03-14:59</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
           <t>06:56-14:55</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>07:02-14:55</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>07:05-15:04</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>07:56-14:00
+15:03-17:28</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>07:01-15:05</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:00</t>
+        </is>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>06:55-15:05</t>
+        </is>
+      </c>
+      <c r="M26" s="6" t="inlineStr">
         <is>
           <t>06:59-15:04</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:02</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>07:01-15:00</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>08:01-14:01
-15:03-17:32</t>
-        </is>
-      </c>
-      <c r="J26" s="6" t="inlineStr">
-        <is>
-          <t>07:03-14:57</t>
-        </is>
-      </c>
-      <c r="K26" s="6" t="inlineStr">
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>08:00-13:55
+14:59-17:35</t>
+        </is>
+      </c>
+      <c r="O26" s="6" t="inlineStr">
+        <is>
+          <t>07:00-14:55</t>
+        </is>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
         <is>
           <t>07:05-14:59</t>
         </is>
       </c>
-      <c r="L26" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:03</t>
-        </is>
-      </c>
-      <c r="M26" s="6" t="inlineStr">
-        <is>
-          <t>07:02-14:57</t>
-        </is>
-      </c>
-      <c r="N26" s="6" t="inlineStr">
-        <is>
-          <t>08:05-14:05
-15:05-17:27</t>
-        </is>
-      </c>
-      <c r="O26" s="6" t="inlineStr">
-        <is>
-          <t>06:58-14:55</t>
-        </is>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>07:01-14:58</t>
-        </is>
-      </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>08:57-13:56</t>
+          <t>09:03-14:00</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:58</t>
+          <t>06:55-14:59</t>
         </is>
       </c>
       <c r="S26" s="6" t="inlineStr">
         <is>
-          <t>08:00-13:56
-15:01-17:32</t>
+          <t>07:57-13:58
+14:55-17:25</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>24/03/2026 (Tue)</t>
+          <t>24/03/2026 (mar)</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
+          <t>06:58-14:56</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>06:55-14:57</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>07:56-14:02
+15:04-17:33</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>07:03-15:01</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>06:57-15:04</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>07:04-15:04</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>07:05-14:57</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>07:55-14:04
+14:56-17:32</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>07:05-15:00</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>06:58-14:56</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
           <t>06:57-15:02</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t>07:00-15:00</t>
+        </is>
+      </c>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
+          <t>07:56-14:03
+14:59-17:33</t>
+        </is>
+      </c>
+      <c r="O27" s="6" t="inlineStr">
+        <is>
+          <t>07:02-14:59</t>
+        </is>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
         <is>
           <t>07:05-15:04</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>08:05-14:05
-15:05-17:26</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>06:57-15:05</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>07:02-15:02</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>07:05-15:01</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>07:03-14:55</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>07:55-13:56
-14:57-17:29</t>
-        </is>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
-        <is>
-          <t>07:04-15:04</t>
-        </is>
-      </c>
-      <c r="K27" s="6" t="inlineStr">
-        <is>
-          <t>07:03-14:59</t>
-        </is>
-      </c>
-      <c r="L27" s="6" t="inlineStr">
-        <is>
-          <t>06:55-14:59</t>
-        </is>
-      </c>
-      <c r="M27" s="6" t="inlineStr">
-        <is>
-          <t>07:02-14:55</t>
-        </is>
-      </c>
-      <c r="N27" s="6" t="inlineStr">
-        <is>
-          <t>07:58-14:00
-15:00-17:33</t>
-        </is>
-      </c>
-      <c r="O27" s="6" t="inlineStr">
-        <is>
-          <t>06:58-15:01</t>
-        </is>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>06:58-14:56</t>
-        </is>
-      </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
-          <t>08:57-14:01</t>
+          <t>09:03-13:59</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:02</t>
+          <t>06:57-15:04</t>
         </is>
       </c>
       <c r="S27" s="6" t="inlineStr">
         <is>
-          <t>07:58-13:58
-15:02-17:25</t>
+          <t>08:02-13:56
+14:56-17:25</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>25/03/2026 (Wed)</t>
+          <t>25/03/2026 (mié)</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -3010,300 +3010,300 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:04</t>
+          <t>06:59-15:05</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>08:05-14:01
-15:00-17:30</t>
+          <t>08:04-13:56
+15:03-17:32</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:57</t>
+          <t>06:56-14:57</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:05</t>
+          <t>06:58-14:59</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:02</t>
+          <t>07:04-14:56</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:59</t>
+          <t>06:59-15:02</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>07:55-13:55
-15:04-17:25</t>
+          <t>07:55-14:04
+14:58-17:34</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:59</t>
+          <t>07:02-14:59</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:02</t>
+          <t>06:55-14:55</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:55</t>
+          <t>07:05-14:56</t>
         </is>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:56</t>
+          <t>07:00-15:01</t>
         </is>
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>08:00-14:05
-15:04-17:27</t>
+          <t>08:03-14:05
+14:57-17:33</t>
         </is>
       </c>
       <c r="O28" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:00</t>
+          <t>06:57-14:55</t>
         </is>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:05</t>
+          <t>06:56-15:00</t>
         </is>
       </c>
       <c r="Q28" s="6" t="inlineStr">
         <is>
-          <t>09:05-14:01</t>
+          <t>09:00-13:58</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:01</t>
+          <t>07:00-14:59</t>
         </is>
       </c>
       <c r="S28" s="6" t="inlineStr">
         <is>
-          <t>08:00-13:56
-15:04-17:28</t>
+          <t>07:57-13:59
+14:56-17:34</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>26/03/2026 (Thu)</t>
+          <t>26/03/2026 (jue)</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:04</t>
+          <t>07:02-15:00</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:03</t>
+          <t>07:04-14:58</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
+          <t>07:59-13:57
+15:04-17:27</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>06:56-15:02</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>07:02-15:02</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>07:04-15:05</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>06:58-14:55</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>07:56-13:58
+14:59-17:30</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:00</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>06:57-14:55</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>06:57-14:57</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:05</t>
+        </is>
+      </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
           <t>08:04-13:58
-15:02-17:25</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>07:01-15:03</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>06:56-14:59</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>06:55-14:56</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
+14:57-17:35</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:05</t>
+        </is>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
         <is>
           <t>07:02-14:59</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>08:03-13:56
-14:59-17:33</t>
-        </is>
-      </c>
-      <c r="J29" s="6" t="inlineStr">
-        <is>
-          <t>06:59-15:02</t>
-        </is>
-      </c>
-      <c r="K29" s="6" t="inlineStr">
-        <is>
-          <t>06:56-14:59</t>
-        </is>
-      </c>
-      <c r="L29" s="6" t="inlineStr">
-        <is>
-          <t>07:01-15:01</t>
-        </is>
-      </c>
-      <c r="M29" s="6" t="inlineStr">
-        <is>
-          <t>06:59-14:56</t>
-        </is>
-      </c>
-      <c r="N29" s="6" t="inlineStr">
-        <is>
-          <t>08:05-13:55
-14:56-17:29</t>
-        </is>
-      </c>
-      <c r="O29" s="6" t="inlineStr">
-        <is>
-          <t>06:59-14:58</t>
-        </is>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>07:04-14:56</t>
-        </is>
-      </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
-          <t>08:57-14:04</t>
+          <t>08:58-13:59</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:00</t>
+          <t>06:59-15:01</t>
         </is>
       </c>
       <c r="S29" s="6" t="inlineStr">
         <is>
-          <t>07:55-13:55
-14:55-17:31</t>
+          <t>08:03-13:58
+15:05-17:35</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>27/03/2026 (Fri)</t>
+          <t>27/03/2026 (vie)</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:59</t>
+          <t>06:55-14:56</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
+          <t>06:55-15:04</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>08:04-14:01
+14:55-17:29</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>06:59-14:58</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>07:05-15:01</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>06:58-15:01</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>07:01-15:01</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>07:59-13:57
+14:57-17:29</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>07:05-15:05</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:02</t>
+        </is>
+      </c>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>07:01-15:00</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>07:04-15:03</t>
+        </is>
+      </c>
+      <c r="N30" s="6" t="inlineStr">
+        <is>
+          <t>08:02-14:05
+15:01-17:26</t>
+        </is>
+      </c>
+      <c r="O30" s="6" t="inlineStr">
+        <is>
+          <t>07:02-15:03</t>
+        </is>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>06:56-15:05</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>08:56-13:57</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
           <t>07:01-14:56</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>08:03-14:01
-15:04-17:29</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>07:05-15:00</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>07:03-15:03</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>07:00-14:58</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>06:57-15:03</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>07:56-14:02
-14:55-17:28</t>
-        </is>
-      </c>
-      <c r="J30" s="6" t="inlineStr">
-        <is>
-          <t>07:04-15:03</t>
-        </is>
-      </c>
-      <c r="K30" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:59</t>
-        </is>
-      </c>
-      <c r="L30" s="6" t="inlineStr">
-        <is>
-          <t>06:57-14:58</t>
-        </is>
-      </c>
-      <c r="M30" s="6" t="inlineStr">
-        <is>
-          <t>06:56-14:57</t>
-        </is>
-      </c>
-      <c r="N30" s="6" t="inlineStr">
-        <is>
-          <t>08:03-14:01
-15:05-17:32</t>
-        </is>
-      </c>
-      <c r="O30" s="6" t="inlineStr">
-        <is>
-          <t>07:05-15:00</t>
-        </is>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>07:05-15:04</t>
-        </is>
-      </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>09:04-13:59</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>07:00-15:00</t>
-        </is>
-      </c>
       <c r="S30" s="6" t="inlineStr">
         <is>
-          <t>08:04-13:58
-14:58-17:35</t>
+          <t>08:00-13:57
+14:58-17:34</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>28/03/2026 (Sat)</t>
+          <t>28/03/2026 (sáb)</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -3400,7 +3400,7 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>29/03/2026 (Sun)</t>
+          <t>29/03/2026 (dom)</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -3497,208 +3497,208 @@
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>30/03/2026 (Mon)</t>
+          <t>30/03/2026 (lun)</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:02</t>
+          <t>07:01-15:05</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:55</t>
+          <t>07:04-15:01</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>07:59-14:05
-14:57-17:30</t>
+          <t>08:00-14:04
+14:56-17:34</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:02</t>
+          <t>06:58-14:56</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:00</t>
+          <t>07:01-15:00</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:55</t>
+          <t>07:02-15:04</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:01</t>
+          <t>07:00-15:00</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>08:03-13:58
-14:57-17:27</t>
+          <t>08:03-14:01
+14:58-17:30</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:59</t>
+          <t>07:04-15:01</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:01</t>
+          <t>07:04-14:58</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:04</t>
+          <t>06:58-15:02</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:05</t>
+          <t>06:55-15:03</t>
         </is>
       </c>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>08:00-14:00
-15:03-17:28</t>
+          <t>07:57-14:05
+15:05-17:34</t>
         </is>
       </c>
       <c r="O33" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:03</t>
+          <t>06:58-15:05</t>
         </is>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:55</t>
+          <t>07:05-15:01</t>
         </is>
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
-          <t>09:01-13:59</t>
+          <t>08:56-13:58</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:59</t>
+          <t>06:59-14:59</t>
         </is>
       </c>
       <c r="S33" s="6" t="inlineStr">
         <is>
-          <t>07:58-13:58
-15:03-17:33</t>
+          <t>07:55-14:03
+14:55-17:35</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026 (Tue)</t>
+          <t>31/03/2026 (mar)</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:03</t>
+          <t>07:00-15:01</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:57</t>
+          <t>06:56-14:59</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>08:01-14:01
-15:01-17:25</t>
+          <t>07:56-14:03
+14:57-17:34</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:55</t>
+          <t>07:02-15:00</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:05</t>
+          <t>07:05-14:58</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:59</t>
+          <t>07:01-14:58</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:55</t>
+          <t>06:56-15:00</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>07:56-13:59
-14:56-17:29</t>
+          <t>07:58-13:56
+15:04-17:29</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:57</t>
+          <t>07:01-15:03</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:03</t>
+          <t>07:00-15:00</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:05</t>
+          <t>07:00-14:55</t>
         </is>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:00</t>
+          <t>07:00-15:03</t>
         </is>
       </c>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>07:55-14:02
-14:56-17:34</t>
+          <t>08:00-14:01
+14:55-17:28</t>
         </is>
       </c>
       <c r="O34" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:05</t>
+          <t>07:00-15:01</t>
         </is>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:02</t>
+          <t>07:03-14:56</t>
         </is>
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>09:05-14:02</t>
+          <t>09:03-14:05</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:00</t>
+          <t>07:04-14:57</t>
         </is>
       </c>
       <c r="S34" s="6" t="inlineStr">
         <is>
-          <t>08:05-14:05
-14:55-17:29</t>
+          <t>08:01-13:56
+14:56-17:32</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A1:R1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Cuadrante_Marzo_2026.xlsx
+++ b/Cuadrante_Marzo_2026.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ADRIAN INIESTA PUNZANO</t>
+          <t>Adrián Iniesta Punzano</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Jesus Montilla Hermoso</t>
+          <t>Jesús Montilla Hermoso</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -604,7 +604,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>01/03/2026 (dom)</t>
+          <t>01/03/2026 (Domingo)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -701,512 +701,512 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>02/03/2026 (lun)</t>
+          <t>02/03/2026 (Lunes)</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:01</t>
+          <t>07:02-15:03</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:55</t>
+          <t>06:56-14:56</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>08:00-13:59
-15:01-17:30</t>
+          <t>08:00-13:57
+15:02-17:25</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:05</t>
+          <t>07:00-15:02</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:59</t>
+          <t>06:57-15:02</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:00</t>
+          <t>06:57-14:56</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:04</t>
+          <t>07:05-15:04</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>07:57-14:00
-15:05-17:25</t>
+          <t>07:58-14:04
+15:04-17:33</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:04</t>
+          <t>06:56-14:57</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:03</t>
+          <t>06:59-14:55</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:05</t>
+          <t>07:00-14:57</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:55</t>
+          <t>07:00-14:59</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>08:00-13:55
-15:02-17:29</t>
+          <t>07:59-14:00
+15:04-17:35</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:05</t>
+          <t>06:59-15:05</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:58</t>
+          <t>06:59-14:58</t>
         </is>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>08:56-14:04</t>
+          <t>08:58-14:01</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:02</t>
+          <t>07:03-15:04</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
         <is>
-          <t>08:02-13:58
-15:01-17:32</t>
+          <t>08:02-14:01
+14:57-17:30</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>03/03/2026 (mar)</t>
+          <t>03/03/2026 (Martes)</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:05</t>
+          <t>06:55-15:04</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:00</t>
+          <t>07:05-14:58</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>07:56-14:00
-14:59-17:28</t>
+          <t>07:57-14:03
+14:57-17:34</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:01</t>
+          <t>06:56-15:05</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:02</t>
+          <t>07:02-14:56</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:00</t>
+          <t>06:55-14:56</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:55</t>
+          <t>06:59-14:58</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>08:01-14:01
-15:04-17:34</t>
+          <t>08:04-14:01
+15:02-17:27</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:58</t>
+          <t>07:03-15:01</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:59</t>
+          <t>06:58-14:59</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:04</t>
+          <t>07:03-14:55</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:04</t>
+          <t>06:55-14:56</t>
         </is>
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>08:05-14:01
-14:59-17:32</t>
+          <t>08:00-13:55
+14:55-17:27</t>
         </is>
       </c>
       <c r="O6" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:01</t>
+          <t>06:55-14:59</t>
         </is>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:58</t>
+          <t>07:03-14:55</t>
         </is>
       </c>
       <c r="Q6" s="6" t="inlineStr">
         <is>
-          <t>08:59-13:55</t>
+          <t>08:56-14:01</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:01</t>
+          <t>07:03-14:55</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
         <is>
-          <t>08:00-14:05
-15:05-17:32</t>
+          <t>07:59-14:01
+15:05-17:27</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>04/03/2026 (mié)</t>
+          <t>04/03/2026 (Miércoles)</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:00</t>
+          <t>07:01-15:02</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:55</t>
+          <t>07:00-14:57</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>08:05-14:01
-14:56-17:31</t>
+          <t>07:59-13:55
+15:05-17:32</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:02</t>
+          <t>07:04-14:55</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:58</t>
+          <t>06:56-15:02</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:58</t>
+          <t>06:56-15:05</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
+          <t>07:05-14:57</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>08:03-14:04
+14:57-17:28</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:05</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>07:04-14:56</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
           <t>07:05-15:00</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>08:04-13:55
-14:59-17:32</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:04</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:02</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="inlineStr">
-        <is>
-          <t>06:59-14:59</t>
-        </is>
-      </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:02</t>
+          <t>07:05-14:56</t>
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>08:03-14:00
-15:03-17:25</t>
+          <t>08:03-14:01
+15:00-17:31</t>
         </is>
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:01</t>
+          <t>06:56-15:05</t>
         </is>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:02</t>
+          <t>07:04-14:55</t>
         </is>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>09:02-13:56</t>
+          <t>08:56-13:55</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:05</t>
+          <t>07:00-14:57</t>
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
         <is>
-          <t>07:57-14:02
-15:04-17:26</t>
+          <t>07:56-14:05
+14:55-17:30</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>05/03/2026 (jue)</t>
+          <t>05/03/2026 (Jueves)</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:01</t>
+          <t>07:02-15:04</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:01</t>
+          <t>06:55-14:55</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>08:04-13:56
-14:59-17:35</t>
+          <t>07:59-14:03
+15:02-17:33</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:01</t>
+          <t>06:58-14:56</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:59</t>
+          <t>06:58-14:59</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:57</t>
+          <t>07:02-15:04</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:00</t>
+          <t>07:03-14:58</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>07:57-14:02
-14:58-17:30</t>
+          <t>08:01-14:05
+14:57-17:33</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:55</t>
+          <t>06:58-15:03</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:04</t>
+          <t>06:56-14:59</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:02</t>
+          <t>07:00-15:03</t>
         </is>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:01</t>
+          <t>07:01-15:03</t>
         </is>
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>07:57-13:59
-14:56-17:29</t>
+          <t>07:55-13:58
+15:05-17:31</t>
         </is>
       </c>
       <c r="O8" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:59</t>
+          <t>07:05-15:03</t>
         </is>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:00</t>
+          <t>07:02-15:03</t>
         </is>
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
-          <t>09:01-14:01</t>
+          <t>09:01-13:55</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:03</t>
+          <t>06:59-14:56</t>
         </is>
       </c>
       <c r="S8" s="6" t="inlineStr">
         <is>
-          <t>07:55-14:00
-15:05-17:32</t>
+          <t>08:01-14:02
+14:58-17:33</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>06/03/2026 (vie)</t>
+          <t>06/03/2026 (Viernes)</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:00</t>
+          <t>06:56-15:05</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
+          <t>07:02-15:04</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>07:57-13:56
+15:02-17:27</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>07:01-15:04</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>06:58-15:05</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>07:05-15:05</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>06:59-14:58</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>07:57-14:01
+15:01-17:33</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>06:57-14:59</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>07:03-14:56</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
           <t>06:57-14:58</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>07:58-14:01
-14:58-17:32</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>07:02-15:03</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>07:00-15:00</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>06:56-14:57</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>07:05-15:04</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>07:59-14:05
-15:01-17:28</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>06:57-15:02</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>06:56-14:59</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:59</t>
-        </is>
-      </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:03</t>
+          <t>07:03-14:58</t>
         </is>
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>08:01-13:55
-15:05-17:30</t>
+          <t>08:02-13:57
+14:56-17:28</t>
         </is>
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:03</t>
+          <t>07:01-15:05</t>
         </is>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:56</t>
+          <t>07:01-15:00</t>
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
-          <t>08:55-13:55</t>
+          <t>09:02-14:03</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:01</t>
+          <t>06:59-15:02</t>
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
         <is>
-          <t>08:05-14:04
-14:59-17:27</t>
+          <t>08:01-14:05
+14:55-17:27</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>07/03/2026 (sáb)</t>
+          <t>07/03/2026 (Sábado)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>08/03/2026 (dom)</t>
+          <t>08/03/2026 (Domingo)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1400,479 +1400,479 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>09/03/2026 (lun)</t>
+          <t>09/03/2026 (Lunes)</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:02</t>
+          <t>07:03-14:57</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:59</t>
+          <t>07:02-15:02</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>08:01-13:57
-14:56-17:33</t>
+          <t>07:55-14:01
+15:04-17:31</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:55</t>
+          <t>07:04-14:55</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
+          <t>07:01-15:04</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>07:05-15:03</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
           <t>07:01-15:05</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>07:01-15:05</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>07:02-14:59</t>
-        </is>
-      </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>08:02-13:58
-15:02-17:33</t>
+          <t>08:01-13:55
+15:03-17:31</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:04</t>
+          <t>07:05-15:00</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:55</t>
+          <t>06:56-15:04</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:55</t>
+          <t>07:05-14:59</t>
         </is>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:05</t>
+          <t>06:55-14:56</t>
         </is>
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>08:01-13:58
-15:00-17:33</t>
+          <t>07:59-13:55
+14:59-17:26</t>
         </is>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:05</t>
+          <t>06:56-14:56</t>
         </is>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:03</t>
+          <t>07:01-14:56</t>
         </is>
       </c>
       <c r="Q12" s="6" t="inlineStr">
         <is>
-          <t>09:01-14:00</t>
+          <t>09:04-13:58</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:58</t>
+          <t>07:02-14:55</t>
         </is>
       </c>
       <c r="S12" s="6" t="inlineStr">
         <is>
-          <t>07:57-13:59
-14:56-17:33</t>
+          <t>08:00-13:59
+14:57-17:34</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>10/03/2026 (mar)</t>
+          <t>10/03/2026 (Martes)</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:00</t>
+          <t>07:00-14:58</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:04</t>
+          <t>06:57-15:05</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>08:03-14:04
-15:00-17:25</t>
+          <t>07:58-14:04
+14:58-17:32</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:58</t>
+          <t>07:00-15:00</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:01</t>
+          <t>07:02-14:56</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:58</t>
+          <t>06:57-14:57</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:57</t>
+          <t>06:57-15:05</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>07:55-13:55
-15:05-17:26</t>
+          <t>08:02-14:01
+15:00-17:34</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:01</t>
+          <t>06:56-15:05</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:03</t>
+          <t>07:02-15:02</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:01</t>
+          <t>06:57-14:57</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:57</t>
+          <t>06:57-14:56</t>
         </is>
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>07:56-14:05
-15:00-17:26</t>
+          <t>08:00-13:55
+15:05-17:29</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:05</t>
+          <t>07:05-14:56</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:58</t>
+          <t>07:00-14:55</t>
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
-          <t>08:55-14:01</t>
+          <t>09:00-14:03</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:04</t>
+          <t>06:56-15:04</t>
         </is>
       </c>
       <c r="S13" s="6" t="inlineStr">
         <is>
-          <t>07:55-14:01
-14:59-17:35</t>
+          <t>07:55-13:56
+14:55-17:29</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>11/03/2026 (mié)</t>
+          <t>11/03/2026 (Miércoles)</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:03</t>
+          <t>06:57-15:05</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:03</t>
+          <t>06:57-15:03</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>07:58-14:05
-15:05-17:35</t>
+          <t>08:02-14:00
+15:02-17:35</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:59</t>
+          <t>06:55-14:59</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:02</t>
+          <t>07:03-15:03</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:02</t>
+          <t>07:01-15:05</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:05</t>
+          <t>07:00-15:05</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>08:02-13:59
-15:04-17:35</t>
+          <t>07:55-14:00
+15:05-17:27</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:55</t>
+          <t>06:56-15:00</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:00</t>
+          <t>07:04-14:56</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:59</t>
+          <t>06:55-15:00</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
+          <t>06:56-15:00</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>08:01-14:01
+14:59-17:25</t>
+        </is>
+      </c>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>06:59-14:59</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>07:01-14:55</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>08:59-13:55</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
           <t>07:04-15:04</t>
         </is>
       </c>
-      <c r="N14" s="6" t="inlineStr">
-        <is>
-          <t>08:01-14:03
-15:03-17:33</t>
-        </is>
-      </c>
-      <c r="O14" s="6" t="inlineStr">
-        <is>
-          <t>07:03-14:55</t>
-        </is>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>07:02-14:58</t>
-        </is>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>08:56-14:00</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>06:57-15:03</t>
-        </is>
-      </c>
       <c r="S14" s="6" t="inlineStr">
         <is>
-          <t>07:56-14:04
-14:58-17:32</t>
+          <t>07:59-14:00
+14:58-17:33</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>12/03/2026 (jue)</t>
+          <t>12/03/2026 (Jueves)</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:56</t>
+          <t>07:00-14:56</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:02</t>
+          <t>06:55-15:03</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>07:58-13:56
-15:01-17:29</t>
+          <t>08:04-14:03
+15:03-17:34</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:00</t>
+          <t>07:04-14:58</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:55</t>
+          <t>07:05-15:03</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:00</t>
+          <t>07:04-15:04</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:03</t>
+          <t>06:59-15:00</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>07:58-13:59
-15:00-17:32</t>
+          <t>07:57-14:02
+14:59-17:30</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:56</t>
+          <t>07:05-15:03</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:05</t>
+          <t>06:55-15:03</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:03</t>
+          <t>07:00-15:04</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:56</t>
+          <t>06:57-15:03</t>
         </is>
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>08:03-14:05
-14:57-17:29</t>
+          <t>07:58-13:57
+14:58-17:27</t>
         </is>
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:58</t>
+          <t>06:58-14:58</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:57</t>
+          <t>07:01-15:00</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>08:55-14:02</t>
+          <t>08:57-14:02</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:56</t>
+          <t>07:05-15:03</t>
         </is>
       </c>
       <c r="S15" s="6" t="inlineStr">
         <is>
-          <t>07:55-13:56
-15:01-17:33</t>
+          <t>07:59-13:58
+15:04-17:34</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>13/03/2026 (vie)</t>
+          <t>13/03/2026 (Viernes)</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:56</t>
+          <t>07:01-15:05</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:01</t>
+          <t>07:00-15:01</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>08:00-14:04
-15:00-17:33</t>
+          <t>08:03-14:04
+15:05-17:30</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
+          <t>07:01-14:56</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>06:56-14:58</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>06:57-15:04</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>07:01-15:05</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>08:00-13:57
+14:57-17:32</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
           <t>06:57-15:03</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>07:00-15:03</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>07:03-15:02</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>07:03-14:59</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>08:05-13:57
-15:03-17:26</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>07:01-14:55</t>
-        </is>
-      </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:05</t>
+          <t>06:55-14:59</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:01</t>
+          <t>06:55-15:04</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:57</t>
+          <t>06:59-14:56</t>
         </is>
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>07:59-13:57
-15:05-17:34</t>
+          <t>07:56-13:59
+14:56-17:33</t>
         </is>
       </c>
       <c r="O16" s="6" t="inlineStr">
@@ -1882,30 +1882,30 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:03</t>
+          <t>07:04-14:59</t>
         </is>
       </c>
       <c r="Q16" s="6" t="inlineStr">
         <is>
-          <t>08:56-14:05</t>
+          <t>09:00-14:05</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:59</t>
+          <t>07:01-15:04</t>
         </is>
       </c>
       <c r="S16" s="6" t="inlineStr">
         <is>
-          <t>07:56-14:05
-14:59-17:33</t>
+          <t>08:01-13:57
+14:58-17:25</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>14/03/2026 (sáb)</t>
+          <t>14/03/2026 (Sábado)</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -2002,7 +2002,7 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>15/03/2026 (dom)</t>
+          <t>15/03/2026 (Domingo)</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -2099,512 +2099,512 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>16/03/2026 (lun)</t>
+          <t>16/03/2026 (Lunes)</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:58</t>
+          <t>07:02-15:02</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:58</t>
+          <t>06:55-15:03</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>07:59-14:02
-14:58-17:26</t>
+          <t>07:59-14:01
+15:02-17:25</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:03</t>
+          <t>07:03-14:57</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:59</t>
+          <t>07:00-14:57</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:03</t>
+          <t>06:57-15:03</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:05</t>
+          <t>06:57-14:55</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>07:58-14:05
-15:02-17:28</t>
+          <t>07:58-13:58
+14:58-17:34</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:00</t>
+          <t>06:56-14:57</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:04</t>
+          <t>07:05-14:59</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:59</t>
+          <t>06:59-15:04</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:57</t>
+          <t>07:04-15:01</t>
         </is>
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>08:01-13:59
-14:58-17:32</t>
+          <t>07:56-14:01
+14:59-17:29</t>
         </is>
       </c>
       <c r="O19" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:56</t>
+          <t>06:57-15:03</t>
         </is>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:56</t>
+          <t>07:02-14:55</t>
         </is>
       </c>
       <c r="Q19" s="6" t="inlineStr">
         <is>
-          <t>09:00-14:03</t>
+          <t>09:01-14:00</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:05</t>
+          <t>07:04-15:01</t>
         </is>
       </c>
       <c r="S19" s="6" t="inlineStr">
         <is>
-          <t>08:02-13:56
-15:01-17:29</t>
+          <t>07:55-13:55
+15:04-17:26</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>17/03/2026 (mar)</t>
+          <t>17/03/2026 (Martes)</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
+          <t>06:56-14:57</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
           <t>07:03-15:02</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:00</t>
-        </is>
-      </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>07:55-14:04
-15:01-17:26</t>
+          <t>07:55-14:05
+15:04-17:25</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:03</t>
+          <t>07:01-14:57</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:04</t>
+          <t>07:03-14:57</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:56</t>
+          <t>07:02-15:03</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:05</t>
+          <t>07:03-14:58</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>08:01-13:56
-14:57-17:34</t>
+          <t>07:59-14:01
+14:58-17:35</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:01</t>
+          <t>06:56-14:58</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:01</t>
+          <t>07:02-14:55</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:03</t>
+          <t>06:59-14:58</t>
         </is>
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:55</t>
+          <t>07:05-15:00</t>
         </is>
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
-          <t>08:03-14:00
-14:59-17:29</t>
+          <t>07:56-14:05
+15:02-17:33</t>
         </is>
       </c>
       <c r="O20" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:58</t>
+          <t>07:00-15:01</t>
         </is>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:01</t>
+          <t>07:03-15:02</t>
         </is>
       </c>
       <c r="Q20" s="6" t="inlineStr">
         <is>
-          <t>08:58-14:01</t>
+          <t>08:58-13:55</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:55</t>
+          <t>07:02-14:58</t>
         </is>
       </c>
       <c r="S20" s="6" t="inlineStr">
         <is>
-          <t>07:58-14:04
-14:59-17:25</t>
+          <t>07:57-13:55
+14:55-17:25</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>18/03/2026 (mié)</t>
+          <t>18/03/2026 (Miércoles)</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:04</t>
+          <t>06:58-14:57</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:04</t>
+          <t>06:57-14:57</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>08:04-14:04
-15:03-17:31</t>
+          <t>08:04-13:58
+15:00-17:29</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:04</t>
+          <t>07:03-15:05</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:59</t>
+          <t>07:00-14:57</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:05</t>
+          <t>07:05-15:01</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:02</t>
+          <t>06:55-15:00</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>08:02-13:57
-15:05-17:34</t>
+          <t>07:56-13:56
+15:05-17:27</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:55</t>
+          <t>07:05-14:56</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:00</t>
+          <t>06:56-15:00</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:01</t>
+          <t>07:00-15:03</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:57</t>
+          <t>06:55-14:57</t>
         </is>
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>08:03-13:55
-15:04-17:25</t>
+          <t>07:55-14:04
+14:59-17:35</t>
         </is>
       </c>
       <c r="O21" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:03</t>
+          <t>06:57-14:57</t>
         </is>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:55</t>
+          <t>07:00-15:03</t>
         </is>
       </c>
       <c r="Q21" s="6" t="inlineStr">
         <is>
-          <t>08:55-14:04</t>
+          <t>08:57-14:00</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:05</t>
+          <t>07:03-15:03</t>
         </is>
       </c>
       <c r="S21" s="6" t="inlineStr">
         <is>
-          <t>07:58-13:58
-14:59-17:26</t>
+          <t>08:00-14:03
+14:55-17:35</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>19/03/2026 (jue)</t>
+          <t>19/03/2026 (Jueves)</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:03</t>
+          <t>07:03-15:05</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:04</t>
+          <t>07:05-15:05</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>08:05-14:02
-15:01-17:30</t>
+          <t>08:01-13:57
+15:04-17:34</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:02</t>
+          <t>07:04-14:57</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:59</t>
+          <t>07:01-14:58</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
+          <t>07:02-14:59</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>07:00-15:04</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>08:05-13:58
+15:04-17:32</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>07:05-15:03</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>06:57-15:01</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>07:05-14:57</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>07:03-15:05</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>07:59-13:59
+14:59-17:29</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
           <t>06:56-15:05</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>07:02-15:04</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>07:55-13:58
-14:57-17:28</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>07:04-15:04</t>
-        </is>
-      </c>
-      <c r="K22" s="6" t="inlineStr">
-        <is>
-          <t>06:59-15:05</t>
-        </is>
-      </c>
-      <c r="L22" s="6" t="inlineStr">
-        <is>
-          <t>07:05-15:04</t>
-        </is>
-      </c>
-      <c r="M22" s="6" t="inlineStr">
-        <is>
-          <t>07:04-15:00</t>
-        </is>
-      </c>
-      <c r="N22" s="6" t="inlineStr">
-        <is>
-          <t>07:59-13:58
-14:57-17:32</t>
-        </is>
-      </c>
-      <c r="O22" s="6" t="inlineStr">
-        <is>
-          <t>07:01-15:01</t>
-        </is>
-      </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:58</t>
+          <t>07:04-15:02</t>
         </is>
       </c>
       <c r="Q22" s="6" t="inlineStr">
         <is>
-          <t>09:04-13:58</t>
+          <t>08:57-14:02</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:00</t>
+          <t>07:00-14:57</t>
         </is>
       </c>
       <c r="S22" s="6" t="inlineStr">
         <is>
-          <t>07:57-13:59
-14:56-17:34</t>
+          <t>08:03-14:00
+15:03-17:27</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>20/03/2026 (vie)</t>
+          <t>20/03/2026 (Viernes)</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:59</t>
+          <t>07:00-14:55</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:57</t>
+          <t>06:58-14:56</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>07:59-14:01
-15:05-17:31</t>
+          <t>08:00-14:03
+14:57-17:27</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:59</t>
+          <t>07:04-14:55</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:05</t>
+          <t>06:58-15:03</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:05</t>
+          <t>07:02-14:59</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:05</t>
+          <t>07:05-15:04</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>08:05-14:00
-15:03-17:29</t>
+          <t>07:59-14:00
+15:00-17:32</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:01</t>
+          <t>07:02-14:59</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:59</t>
+          <t>07:02-14:57</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:56</t>
+          <t>06:59-15:05</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:02</t>
+          <t>07:05-14:57</t>
         </is>
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
-          <t>08:04-14:00
-15:01-17:26</t>
+          <t>08:04-14:01
+14:58-17:33</t>
         </is>
       </c>
       <c r="O23" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:05</t>
+          <t>06:56-15:05</t>
         </is>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:57</t>
+          <t>07:04-15:03</t>
         </is>
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
-          <t>09:05-13:56</t>
+          <t>09:02-14:05</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:05</t>
+          <t>07:03-14:58</t>
         </is>
       </c>
       <c r="S23" s="6" t="inlineStr">
         <is>
-          <t>08:03-13:58
-14:55-17:30</t>
+          <t>08:00-14:01
+15:05-17:30</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>21/03/2026 (sáb)</t>
+          <t>21/03/2026 (Sábado)</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -2701,7 +2701,7 @@
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>22/03/2026 (dom)</t>
+          <t>22/03/2026 (Domingo)</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -2798,512 +2798,512 @@
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>23/03/2026 (lun)</t>
+          <t>23/03/2026 (Lunes)</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:56</t>
+          <t>07:00-14:59</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:59</t>
+          <t>06:59-15:02</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>07:59-14:05
+          <t>07:58-14:05
+15:01-17:28</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>06:55-15:04</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>06:56-15:05</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>07:05-14:55</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>07:03-14:58</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>07:58-13:56
 14:57-17:27</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>07:03-14:59</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>06:56-14:55</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>07:02-14:55</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>07:05-14:58</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
         <is>
           <t>07:05-15:04</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>07:56-14:00
-15:03-17:28</t>
-        </is>
-      </c>
-      <c r="J26" s="6" t="inlineStr">
-        <is>
-          <t>07:01-15:05</t>
-        </is>
-      </c>
-      <c r="K26" s="6" t="inlineStr">
-        <is>
-          <t>06:59-15:00</t>
-        </is>
-      </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:05</t>
+          <t>07:02-14:57</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:04</t>
+          <t>07:01-14:58</t>
         </is>
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>08:00-13:55
-14:59-17:35</t>
+          <t>08:05-13:59
+15:02-17:26</t>
         </is>
       </c>
       <c r="O26" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:55</t>
+          <t>07:04-15:03</t>
         </is>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:59</t>
+          <t>06:56-15:01</t>
         </is>
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>09:03-14:00</t>
+          <t>09:00-14:05</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:59</t>
+          <t>06:58-15:04</t>
         </is>
       </c>
       <c r="S26" s="6" t="inlineStr">
         <is>
-          <t>07:57-13:58
-14:55-17:25</t>
+          <t>08:01-14:00
+14:57-17:30</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>24/03/2026 (mar)</t>
+          <t>24/03/2026 (Martes)</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:56</t>
+          <t>06:59-15:03</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:57</t>
+          <t>07:01-14:58</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>07:56-14:02
-15:04-17:33</t>
+          <t>07:56-14:01
+15:01-17:25</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
+          <t>07:01-15:00</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>06:59-14:57</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>07:04-14:59</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>06:56-15:01</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>07:59-14:02
+15:03-17:27</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>06:59-14:55</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>07:04-14:58</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>06:58-15:00</t>
+        </is>
+      </c>
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t>07:05-14:58</t>
+        </is>
+      </c>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
+          <t>07:55-13:55
+14:58-17:29</t>
+        </is>
+      </c>
+      <c r="O27" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:05</t>
+        </is>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
           <t>07:03-15:01</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>06:57-15:04</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>07:04-15:04</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:57</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>07:55-14:04
-14:56-17:32</t>
-        </is>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
-        <is>
-          <t>07:05-15:00</t>
-        </is>
-      </c>
-      <c r="K27" s="6" t="inlineStr">
-        <is>
-          <t>06:58-14:56</t>
-        </is>
-      </c>
-      <c r="L27" s="6" t="inlineStr">
-        <is>
-          <t>06:57-15:02</t>
-        </is>
-      </c>
-      <c r="M27" s="6" t="inlineStr">
-        <is>
-          <t>07:00-15:00</t>
-        </is>
-      </c>
-      <c r="N27" s="6" t="inlineStr">
-        <is>
-          <t>07:56-14:03
-14:59-17:33</t>
-        </is>
-      </c>
-      <c r="O27" s="6" t="inlineStr">
-        <is>
-          <t>07:02-14:59</t>
-        </is>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>07:05-15:04</t>
-        </is>
-      </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
-          <t>09:03-13:59</t>
+          <t>08:55-13:59</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:04</t>
+          <t>07:02-15:04</t>
         </is>
       </c>
       <c r="S27" s="6" t="inlineStr">
         <is>
-          <t>08:02-13:56
-14:56-17:25</t>
+          <t>07:57-14:02
+14:57-17:27</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>25/03/2026 (mié)</t>
+          <t>25/03/2026 (Miércoles)</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:57</t>
+          <t>07:02-15:00</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:05</t>
+          <t>06:57-15:05</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>08:04-13:56
-15:03-17:32</t>
+          <t>07:59-14:03
+15:00-17:34</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:57</t>
+          <t>07:03-15:04</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:59</t>
+          <t>06:58-14:57</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:56</t>
+          <t>07:02-14:57</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
+          <t>07:05-14:59</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>08:02-14:00
+14:57-17:28</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>06:56-15:00</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
           <t>06:59-15:02</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>07:55-14:04
-14:58-17:34</t>
-        </is>
-      </c>
-      <c r="J28" s="6" t="inlineStr">
-        <is>
-          <t>07:02-14:59</t>
-        </is>
-      </c>
-      <c r="K28" s="6" t="inlineStr">
-        <is>
-          <t>06:55-14:55</t>
-        </is>
-      </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:56</t>
+          <t>07:03-14:55</t>
         </is>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:01</t>
+          <t>07:05-14:58</t>
         </is>
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>08:03-14:05
-14:57-17:33</t>
+          <t>08:02-14:01
+15:04-17:34</t>
         </is>
       </c>
       <c r="O28" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:55</t>
+          <t>07:04-15:00</t>
         </is>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:00</t>
+          <t>06:57-15:05</t>
         </is>
       </c>
       <c r="Q28" s="6" t="inlineStr">
         <is>
-          <t>09:00-13:58</t>
+          <t>09:04-13:56</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:59</t>
+          <t>07:02-15:02</t>
         </is>
       </c>
       <c r="S28" s="6" t="inlineStr">
         <is>
-          <t>07:57-13:59
-14:56-17:34</t>
+          <t>07:58-13:55
+15:01-17:33</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>26/03/2026 (jue)</t>
+          <t>26/03/2026 (Jueves)</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:00</t>
+          <t>07:03-15:04</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:58</t>
+          <t>07:00-14:58</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>07:59-13:57
-15:04-17:27</t>
+          <t>08:01-14:02
+15:04-17:35</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:02</t>
+          <t>06:58-15:03</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:02</t>
+          <t>07:01-15:01</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:05</t>
+          <t>06:58-14:58</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:55</t>
+          <t>07:01-14:56</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>07:56-13:58
-14:59-17:30</t>
+          <t>07:55-13:56
+15:03-17:25</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:00</t>
+          <t>07:05-14:58</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:55</t>
+          <t>06:56-15:04</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:57</t>
+          <t>07:00-14:58</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:05</t>
+          <t>06:58-14:57</t>
         </is>
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>08:04-13:58
-14:57-17:35</t>
+          <t>07:56-14:05
+14:56-17:31</t>
         </is>
       </c>
       <c r="O29" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:05</t>
+          <t>07:05-15:04</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:59</t>
+          <t>07:03-15:01</t>
         </is>
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
-          <t>08:58-13:59</t>
+          <t>09:03-14:01</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:01</t>
+          <t>06:55-15:03</t>
         </is>
       </c>
       <c r="S29" s="6" t="inlineStr">
         <is>
-          <t>08:03-13:58
-15:05-17:35</t>
+          <t>08:02-14:00
+15:04-17:28</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>27/03/2026 (vie)</t>
+          <t>27/03/2026 (Viernes)</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:56</t>
+          <t>07:02-14:59</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:04</t>
+          <t>07:04-15:02</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>08:04-14:01
-14:55-17:29</t>
+          <t>08:03-14:05
+15:03-17:26</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:58</t>
+          <t>06:56-14:55</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:01</t>
+          <t>06:55-15:03</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:01</t>
+          <t>07:03-15:01</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:01</t>
+          <t>06:56-15:02</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>07:59-13:57
-14:57-17:29</t>
+          <t>08:05-13:56
+15:00-17:26</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:05</t>
+          <t>07:04-15:00</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:02</t>
+          <t>07:01-14:58</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:00</t>
+          <t>06:56-15:02</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:03</t>
+          <t>07:02-14:55</t>
         </is>
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>08:02-14:05
-15:01-17:26</t>
+          <t>07:57-13:55
+14:58-17:25</t>
         </is>
       </c>
       <c r="O30" s="6" t="inlineStr">
         <is>
+          <t>07:04-14:57</t>
+        </is>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
           <t>07:02-15:03</t>
         </is>
       </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:05</t>
-        </is>
-      </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>08:56-13:57</t>
+          <t>09:00-14:05</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:56</t>
+          <t>06:59-14:55</t>
         </is>
       </c>
       <c r="S30" s="6" t="inlineStr">
         <is>
-          <t>08:00-13:57
-14:58-17:34</t>
+          <t>08:05-13:55
+15:00-17:30</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>28/03/2026 (sáb)</t>
+          <t>28/03/2026 (Sábado)</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -3400,7 +3400,7 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>29/03/2026 (dom)</t>
+          <t>29/03/2026 (Domingo)</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -3497,202 +3497,202 @@
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>30/03/2026 (lun)</t>
+          <t>30/03/2026 (Lunes)</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:05</t>
+          <t>07:00-14:59</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:01</t>
+          <t>06:55-15:02</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>08:00-14:04
-14:56-17:34</t>
+          <t>07:55-13:56
+15:03-17:34</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:56</t>
+          <t>06:58-15:04</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:00</t>
+          <t>06:56-14:58</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:04</t>
+          <t>06:58-14:55</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:00</t>
+          <t>06:57-15:05</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>08:03-14:01
-14:58-17:30</t>
+          <t>07:59-13:59
+14:59-17:31</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:01</t>
+          <t>06:56-15:05</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
+          <t>06:58-14:55</t>
+        </is>
+      </c>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>06:55-14:55</t>
+        </is>
+      </c>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>07:04-14:57</t>
+        </is>
+      </c>
+      <c r="N33" s="6" t="inlineStr">
+        <is>
+          <t>08:02-13:58
+15:00-17:35</t>
+        </is>
+      </c>
+      <c r="O33" s="6" t="inlineStr">
+        <is>
+          <t>07:02-15:00</t>
+        </is>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
           <t>07:04-14:58</t>
         </is>
       </c>
-      <c r="L33" s="6" t="inlineStr">
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>09:01-14:00</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
         <is>
           <t>06:58-15:02</t>
         </is>
       </c>
-      <c r="M33" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:03</t>
-        </is>
-      </c>
-      <c r="N33" s="6" t="inlineStr">
-        <is>
-          <t>07:57-14:05
-15:05-17:34</t>
-        </is>
-      </c>
-      <c r="O33" s="6" t="inlineStr">
-        <is>
-          <t>06:58-15:05</t>
-        </is>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>07:05-15:01</t>
-        </is>
-      </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>08:56-13:58</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>06:59-14:59</t>
-        </is>
-      </c>
       <c r="S33" s="6" t="inlineStr">
         <is>
           <t>07:55-14:03
-14:55-17:35</t>
+15:01-17:33</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026 (mar)</t>
+          <t>31/03/2026 (Martes)</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:01</t>
+          <t>07:01-14:56</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:59</t>
+          <t>06:58-14:55</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>07:56-14:03
-14:57-17:34</t>
+          <t>07:59-13:56
+15:02-17:25</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:00</t>
+          <t>07:02-15:02</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:58</t>
+          <t>06:57-14:55</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:58</t>
+          <t>06:58-14:57</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:00</t>
+          <t>06:59-15:03</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>07:58-13:56
-15:04-17:29</t>
+          <t>07:59-13:55
+15:02-17:34</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:03</t>
+          <t>07:05-15:03</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:00</t>
+          <t>06:58-15:04</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
+          <t>07:03-15:02</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>07:05-15:04</t>
+        </is>
+      </c>
+      <c r="N34" s="6" t="inlineStr">
+        <is>
+          <t>07:57-14:03
+15:01-17:35</t>
+        </is>
+      </c>
+      <c r="O34" s="6" t="inlineStr">
+        <is>
           <t>07:00-14:55</t>
         </is>
       </c>
-      <c r="M34" s="6" t="inlineStr">
-        <is>
-          <t>07:00-15:03</t>
-        </is>
-      </c>
-      <c r="N34" s="6" t="inlineStr">
-        <is>
-          <t>08:00-14:01
-14:55-17:28</t>
-        </is>
-      </c>
-      <c r="O34" s="6" t="inlineStr">
-        <is>
-          <t>07:00-15:01</t>
-        </is>
-      </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:56</t>
+          <t>06:57-15:05</t>
         </is>
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>09:03-14:05</t>
+          <t>08:55-13:56</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:57</t>
+          <t>06:59-15:00</t>
         </is>
       </c>
       <c r="S34" s="6" t="inlineStr">
         <is>
-          <t>08:01-13:56
-14:56-17:32</t>
+          <t>08:00-13:55
+15:02-17:28</t>
         </is>
       </c>
     </row>

--- a/Cuadrante_Marzo_2026.xlsx
+++ b/Cuadrante_Marzo_2026.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:T34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -494,6 +494,7 @@
     <col width="25" customWidth="1" min="17" max="17"/>
     <col width="25" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
+    <col width="25" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -522,80 +523,85 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>Alberto Gómez Marín</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>Antonio Escalzo Morales</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Antonio Ramón Fuentes Medina</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Antonio Ruíz Perete</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Fabio Gutiérrez Basante</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Francisco Javier Cárdenas Moga</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Francisco Ordoñez Perabá</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>Héctor López Ramírez</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>Javier Galera Andújar</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Jesús Montilla Hermoso</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Juan José Borrás Ferrete</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>Lourdes Fuentes Buendía</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>Luis Miguel Colmenero Cobo</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>Manuel Martín Martínez</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="R3" s="2" t="inlineStr">
         <is>
           <t>Manuel Peinado García</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>Tomás García</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>Victoria Romero Sabalete</t>
         </is>
@@ -697,6 +703,11 @@
           <t>DESCANSO</t>
         </is>
       </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>DESCANSO</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -706,96 +717,101 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:03</t>
+          <t>06:58-14:56</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:56</t>
+          <t>07:03-15:04</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>08:00-13:57
-15:02-17:25</t>
+          <t>07:04-15:03</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:02</t>
+          <t>08:01-13:58
+14:59-17:34</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:02</t>
+          <t>06:55-14:55</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:56</t>
+          <t>06:56-15:02</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:04</t>
+          <t>06:57-15:01</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>07:58-14:04
-15:04-17:33</t>
+          <t>07:00-15:03</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:57</t>
+          <t>08:05-13:59
+14:55-17:26</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:55</t>
+          <t>07:02-15:04</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:57</t>
+          <t>07:04-15:01</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:59</t>
+          <t>07:04-14:55</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>07:59-14:00
-15:04-17:35</t>
+          <t>07:02-15:04</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:05</t>
+          <t>07:56-13:56
+14:56-17:34</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:58</t>
+          <t>06:56-15:02</t>
         </is>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>08:58-14:01</t>
+          <t>06:56-15:05</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:04</t>
+          <t>09:03-14:00</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
         <is>
-          <t>08:02-14:01
-14:57-17:30</t>
+          <t>07:04-14:57</t>
+        </is>
+      </c>
+      <c r="T5" s="6" t="inlineStr">
+        <is>
+          <t>07:58-14:05
+14:56-17:28</t>
         </is>
       </c>
     </row>
@@ -807,96 +823,101 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:04</t>
+          <t>07:01-15:00</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:58</t>
+          <t>07:05-14:59</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>07:57-14:03
-14:57-17:34</t>
+          <t>07:04-15:04</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:05</t>
+          <t>08:04-13:56
+15:02-17:26</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:56</t>
+          <t>06:57-15:02</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:56</t>
+          <t>07:03-14:59</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:58</t>
+          <t>07:03-15:02</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>08:04-14:01
-15:02-17:27</t>
+          <t>07:05-15:04</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:01</t>
+          <t>08:01-13:57
+14:59-17:32</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:59</t>
+          <t>07:00-14:56</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:55</t>
+          <t>06:56-15:02</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:56</t>
+          <t>06:56-14:56</t>
         </is>
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>08:00-13:55
-14:55-17:27</t>
+          <t>06:57-14:56</t>
         </is>
       </c>
       <c r="O6" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:59</t>
+          <t>08:04-13:59
+14:56-17:28</t>
         </is>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:55</t>
+          <t>06:58-15:02</t>
         </is>
       </c>
       <c r="Q6" s="6" t="inlineStr">
         <is>
-          <t>08:56-14:01</t>
+          <t>07:04-15:01</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:55</t>
+          <t>09:04-14:01</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
         <is>
-          <t>07:59-14:01
-15:05-17:27</t>
+          <t>06:58-14:56</t>
+        </is>
+      </c>
+      <c r="T6" s="6" t="inlineStr">
+        <is>
+          <t>08:04-14:03
+15:00-17:31</t>
         </is>
       </c>
     </row>
@@ -908,96 +929,101 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:02</t>
+          <t>07:05-15:00</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:57</t>
+          <t>06:59-14:57</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>07:59-13:55
-15:05-17:32</t>
+          <t>06:57-14:58</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:55</t>
+          <t>07:55-14:00
+14:59-17:26</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:02</t>
+          <t>06:56-14:56</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:05</t>
+          <t>07:00-15:04</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:57</t>
+          <t>06:56-15:04</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>08:03-14:04
-14:57-17:28</t>
+          <t>07:05-15:05</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:05</t>
+          <t>07:58-13:58
+15:03-17:32</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:56</t>
+          <t>06:57-15:01</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:00</t>
+          <t>07:02-15:02</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:56</t>
+          <t>07:02-15:04</t>
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>08:03-14:01
-15:00-17:31</t>
+          <t>07:03-14:55</t>
         </is>
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:05</t>
+          <t>08:02-13:59
+14:55-17:26</t>
         </is>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:55</t>
+          <t>07:02-14:58</t>
         </is>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>08:56-13:55</t>
+          <t>07:04-15:04</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:57</t>
+          <t>09:04-14:05</t>
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
         <is>
-          <t>07:56-14:05
-14:55-17:30</t>
+          <t>07:01-15:04</t>
+        </is>
+      </c>
+      <c r="T7" s="6" t="inlineStr">
+        <is>
+          <t>07:55-13:59
+14:58-17:33</t>
         </is>
       </c>
     </row>
@@ -1009,96 +1035,101 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:04</t>
+          <t>06:56-15:05</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:55</t>
+          <t>07:05-15:04</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>07:59-14:03
-15:02-17:33</t>
+          <t>07:00-14:58</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
+          <t>08:01-14:02
+15:00-17:35</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
           <t>06:58-14:56</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>06:58-14:59</t>
-        </is>
-      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:04</t>
+          <t>06:57-15:00</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:58</t>
+          <t>06:55-15:02</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>08:01-14:05
-14:57-17:33</t>
+          <t>07:05-15:04</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
+          <t>07:57-14:02
+14:59-17:34</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>07:03-14:56</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>07:03-15:05</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>07:00-14:55</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
           <t>06:58-15:03</t>
         </is>
       </c>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>06:56-14:59</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>07:00-15:03</t>
-        </is>
-      </c>
-      <c r="M8" s="6" t="inlineStr">
-        <is>
-          <t>07:01-15:03</t>
-        </is>
-      </c>
-      <c r="N8" s="6" t="inlineStr">
-        <is>
-          <t>07:55-13:58
-15:05-17:31</t>
-        </is>
-      </c>
       <c r="O8" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:03</t>
+          <t>07:58-14:03
+15:03-17:28</t>
         </is>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:03</t>
+          <t>07:04-15:04</t>
         </is>
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
-          <t>09:01-13:55</t>
+          <t>06:58-15:03</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:56</t>
+          <t>08:58-14:00</t>
         </is>
       </c>
       <c r="S8" s="6" t="inlineStr">
         <is>
-          <t>08:01-14:02
-14:58-17:33</t>
+          <t>07:04-14:55</t>
+        </is>
+      </c>
+      <c r="T8" s="6" t="inlineStr">
+        <is>
+          <t>08:05-14:00
+14:58-17:32</t>
         </is>
       </c>
     </row>
@@ -1110,96 +1141,101 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:05</t>
+          <t>06:58-15:04</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:04</t>
+          <t>06:57-15:03</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>07:57-13:56
-15:02-17:27</t>
+          <t>07:02-14:59</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:04</t>
+          <t>07:57-13:57
+15:05-17:29</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:05</t>
+          <t>06:58-14:57</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:05</t>
+          <t>06:55-15:05</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:58</t>
+          <t>07:04-14:55</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>07:57-14:01
-15:01-17:33</t>
+          <t>06:58-15:04</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:59</t>
+          <t>08:05-13:56
+14:55-17:30</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:56</t>
+          <t>06:58-15:01</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
+          <t>06:58-15:03</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>07:05-14:59</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>07:03-15:02</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>07:57-14:03
+15:03-17:29</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
           <t>06:57-14:58</t>
         </is>
       </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>07:03-14:58</t>
-        </is>
-      </c>
-      <c r="N9" s="6" t="inlineStr">
-        <is>
-          <t>08:02-13:57
-14:56-17:28</t>
-        </is>
-      </c>
-      <c r="O9" s="6" t="inlineStr">
-        <is>
-          <t>07:01-15:05</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>07:01-15:00</t>
-        </is>
-      </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
-          <t>09:02-14:03</t>
+          <t>06:57-15:03</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:02</t>
+          <t>08:56-13:57</t>
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
         <is>
-          <t>08:01-14:05
-14:55-17:27</t>
+          <t>06:56-15:00</t>
+        </is>
+      </c>
+      <c r="T9" s="6" t="inlineStr">
+        <is>
+          <t>07:57-13:59
+15:05-17:33</t>
         </is>
       </c>
     </row>
@@ -1299,6 +1335,11 @@
           <t>DESCANSO</t>
         </is>
       </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>DESCANSO</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -1396,6 +1437,11 @@
           <t>DESCANSO</t>
         </is>
       </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>DESCANSO</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -1405,96 +1451,101 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:57</t>
+          <t>07:00-14:59</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:02</t>
+          <t>07:02-15:05</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>07:55-14:01
-15:04-17:31</t>
+          <t>06:56-15:03</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:55</t>
+          <t>08:03-14:01
+14:58-17:26</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:04</t>
+          <t>07:04-15:01</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:03</t>
+          <t>06:55-14:55</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:05</t>
+          <t>06:58-15:02</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>08:01-13:55
-15:03-17:31</t>
+          <t>07:01-15:01</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:00</t>
+          <t>07:59-14:03
+15:02-17:34</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:04</t>
+          <t>06:56-15:05</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:59</t>
+          <t>07:05-15:04</t>
         </is>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:56</t>
+          <t>06:59-14:57</t>
         </is>
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>07:59-13:55
-14:59-17:26</t>
+          <t>06:55-15:03</t>
         </is>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:56</t>
+          <t>07:55-14:04
+15:04-17:35</t>
         </is>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:56</t>
+          <t>07:03-14:59</t>
         </is>
       </c>
       <c r="Q12" s="6" t="inlineStr">
         <is>
-          <t>09:04-13:58</t>
+          <t>06:56-14:55</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:55</t>
+          <t>09:04-13:56</t>
         </is>
       </c>
       <c r="S12" s="6" t="inlineStr">
         <is>
-          <t>08:00-13:59
-14:57-17:34</t>
+          <t>07:02-15:03</t>
+        </is>
+      </c>
+      <c r="T12" s="6" t="inlineStr">
+        <is>
+          <t>07:56-14:04
+15:02-17:29</t>
         </is>
       </c>
     </row>
@@ -1506,96 +1557,101 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
+          <t>06:57-15:02</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>06:58-14:56</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>06:58-15:04</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>07:55-14:05
+14:56-17:31</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>07:03-15:00</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>06:57-15:01</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>06:55-14:59</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>06:56-14:55</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>07:56-13:57
+14:59-17:31</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>07:04-15:03</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
           <t>07:00-14:58</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>06:57-15:05</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>07:58-14:04
-14:58-17:32</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>07:00-15:00</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>07:02-14:56</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>07:00-15:05</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
         <is>
           <t>06:57-14:57</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>06:57-15:05</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>08:02-14:01
-15:00-17:34</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:05</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>07:02-15:02</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="inlineStr">
-        <is>
-          <t>06:57-14:57</t>
-        </is>
-      </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>06:57-14:56</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="inlineStr">
-        <is>
-          <t>08:00-13:55
-15:05-17:29</t>
-        </is>
-      </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:56</t>
+          <t>07:55-13:55
+15:04-17:34</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:55</t>
+          <t>06:57-15:00</t>
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
-          <t>09:00-14:03</t>
+          <t>06:59-15:00</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:04</t>
+          <t>08:59-13:57</t>
         </is>
       </c>
       <c r="S13" s="6" t="inlineStr">
         <is>
-          <t>07:55-13:56
-14:55-17:29</t>
+          <t>07:04-15:02</t>
+        </is>
+      </c>
+      <c r="T13" s="6" t="inlineStr">
+        <is>
+          <t>07:59-14:01
+14:59-17:35</t>
         </is>
       </c>
     </row>
@@ -1607,96 +1663,101 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:05</t>
+          <t>06:59-15:03</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:03</t>
+          <t>06:56-15:01</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>08:02-14:00
-15:02-17:35</t>
+          <t>07:02-15:04</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:59</t>
+          <t>08:00-13:58
+14:56-17:34</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
+          <t>07:02-14:57</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
           <t>07:03-15:03</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>07:01-15:05</t>
-        </is>
-      </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:05</t>
+          <t>06:58-15:05</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>07:55-14:00
-15:05-17:27</t>
+          <t>06:57-14:57</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:00</t>
+          <t>07:55-13:57
+15:00-17:29</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:56</t>
+          <t>06:57-14:59</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:00</t>
+          <t>07:00-15:03</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:00</t>
+          <t>07:05-15:02</t>
         </is>
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>08:01-14:01
-14:59-17:25</t>
+          <t>07:04-14:57</t>
         </is>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:59</t>
+          <t>08:01-14:04
+15:05-17:34</t>
         </is>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:55</t>
+          <t>07:05-15:02</t>
         </is>
       </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
-          <t>08:59-13:55</t>
+          <t>07:04-15:03</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:04</t>
+          <t>08:55-14:02</t>
         </is>
       </c>
       <c r="S14" s="6" t="inlineStr">
         <is>
-          <t>07:59-14:00
-14:58-17:33</t>
+          <t>07:03-14:58</t>
+        </is>
+      </c>
+      <c r="T14" s="6" t="inlineStr">
+        <is>
+          <t>08:04-14:05
+15:05-17:25</t>
         </is>
       </c>
     </row>
@@ -1708,96 +1769,101 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:56</t>
+          <t>07:03-14:58</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:03</t>
+          <t>07:02-14:58</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>08:04-14:03
-15:03-17:34</t>
+          <t>07:05-14:58</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:58</t>
+          <t>08:01-14:00
+14:59-17:33</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:03</t>
+          <t>06:55-14:56</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:04</t>
+          <t>07:01-14:56</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:00</t>
+          <t>07:04-14:59</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>07:57-14:02
-14:59-17:30</t>
+          <t>07:05-14:58</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:03</t>
+          <t>08:04-14:01
+15:01-17:26</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:03</t>
+          <t>07:04-14:55</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:04</t>
+          <t>06:58-15:05</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:03</t>
+          <t>07:00-14:59</t>
         </is>
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>07:58-13:57
-14:58-17:27</t>
+          <t>07:04-15:05</t>
         </is>
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:58</t>
+          <t>08:03-13:59
+15:03-17:29</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:00</t>
+          <t>06:55-14:58</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>08:57-14:02</t>
+          <t>07:05-14:56</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:03</t>
+          <t>08:56-14:02</t>
         </is>
       </c>
       <c r="S15" s="6" t="inlineStr">
         <is>
-          <t>07:59-13:58
-15:04-17:34</t>
+          <t>07:03-15:04</t>
+        </is>
+      </c>
+      <c r="T15" s="6" t="inlineStr">
+        <is>
+          <t>08:02-14:00
+15:00-17:25</t>
         </is>
       </c>
     </row>
@@ -1809,96 +1875,101 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
+          <t>07:02-14:58</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
           <t>07:01-15:05</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>07:00-15:01</t>
-        </is>
-      </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>08:03-14:04
-15:05-17:30</t>
+          <t>06:58-15:01</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:56</t>
+          <t>07:59-14:00
+14:56-17:34</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:58</t>
+          <t>07:01-15:02</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:04</t>
+          <t>07:00-14:57</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:05</t>
+          <t>07:05-15:04</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>08:00-13:57
-14:57-17:32</t>
+          <t>07:02-14:59</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
+          <t>08:03-14:03
+15:03-17:33</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:03</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>07:04-15:01</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
           <t>06:57-15:03</t>
         </is>
       </c>
-      <c r="K16" s="6" t="inlineStr">
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>07:02-15:02</t>
+        </is>
+      </c>
+      <c r="O16" s="6" t="inlineStr">
+        <is>
+          <t>08:03-14:05
+15:00-17:28</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>07:05-15:05</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
         <is>
           <t>06:55-14:59</t>
         </is>
       </c>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:04</t>
-        </is>
-      </c>
-      <c r="M16" s="6" t="inlineStr">
-        <is>
-          <t>06:59-14:56</t>
-        </is>
-      </c>
-      <c r="N16" s="6" t="inlineStr">
-        <is>
-          <t>07:56-13:59
-14:56-17:33</t>
-        </is>
-      </c>
-      <c r="O16" s="6" t="inlineStr">
-        <is>
-          <t>06:58-14:58</t>
-        </is>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>07:04-14:59</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>09:00-14:05</t>
-        </is>
-      </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:04</t>
+          <t>09:02-14:05</t>
         </is>
       </c>
       <c r="S16" s="6" t="inlineStr">
         <is>
-          <t>08:01-13:57
-14:58-17:25</t>
+          <t>07:05-14:56</t>
+        </is>
+      </c>
+      <c r="T16" s="6" t="inlineStr">
+        <is>
+          <t>07:56-14:04
+15:01-17:31</t>
         </is>
       </c>
     </row>
@@ -1998,6 +2069,11 @@
           <t>DESCANSO</t>
         </is>
       </c>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>DESCANSO</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
@@ -2095,6 +2171,11 @@
           <t>DESCANSO</t>
         </is>
       </c>
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t>DESCANSO</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
@@ -2104,49 +2185,49 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:02</t>
+          <t>07:03-15:03</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:03</t>
+          <t>06:57-15:01</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>07:59-14:01
-15:02-17:25</t>
+          <t>06:57-15:01</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:57</t>
+          <t>08:02-14:00
+14:58-17:31</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:57</t>
+          <t>06:55-15:00</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:03</t>
+          <t>07:02-15:00</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:55</t>
+          <t>07:00-15:01</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>07:58-13:58
-14:58-17:34</t>
+          <t>07:01-14:58</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:57</t>
+          <t>07:58-14:01
+15:05-17:30</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
@@ -2156,44 +2237,49 @@
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:04</t>
+          <t>06:58-15:03</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:01</t>
+          <t>06:57-14:58</t>
         </is>
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>07:56-14:01
-14:59-17:29</t>
+          <t>07:01-15:05</t>
         </is>
       </c>
       <c r="O19" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:03</t>
+          <t>08:01-13:57
+15:05-17:30</t>
         </is>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
+          <t>07:05-15:03</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
           <t>07:02-14:55</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>09:01-14:00</t>
-        </is>
-      </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:01</t>
+          <t>08:58-13:58</t>
         </is>
       </c>
       <c r="S19" s="6" t="inlineStr">
         <is>
-          <t>07:55-13:55
-15:04-17:26</t>
+          <t>07:01-15:03</t>
+        </is>
+      </c>
+      <c r="T19" s="6" t="inlineStr">
+        <is>
+          <t>08:04-14:04
+15:03-17:32</t>
         </is>
       </c>
     </row>
@@ -2205,96 +2291,101 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:57</t>
+          <t>06:56-15:03</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:02</t>
+          <t>06:57-15:02</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>07:55-14:05
-15:04-17:25</t>
+          <t>06:55-15:02</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:57</t>
+          <t>08:04-13:55
+15:01-17:35</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:57</t>
+          <t>06:58-15:03</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:03</t>
+          <t>06:58-14:57</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:58</t>
+          <t>06:56-15:04</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>07:59-14:01
-14:58-17:35</t>
+          <t>07:02-15:05</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:58</t>
+          <t>08:02-14:04
+15:05-17:25</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:55</t>
+          <t>07:02-14:59</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:58</t>
+          <t>07:05-15:05</t>
         </is>
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:00</t>
+          <t>07:05-15:05</t>
         </is>
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
-          <t>07:56-14:05
-15:02-17:33</t>
+          <t>06:56-15:01</t>
         </is>
       </c>
       <c r="O20" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:01</t>
+          <t>07:55-13:56
+14:59-17:32</t>
         </is>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:02</t>
+          <t>07:02-14:56</t>
         </is>
       </c>
       <c r="Q20" s="6" t="inlineStr">
         <is>
-          <t>08:58-13:55</t>
+          <t>06:59-15:00</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:58</t>
+          <t>09:01-14:02</t>
         </is>
       </c>
       <c r="S20" s="6" t="inlineStr">
         <is>
-          <t>07:57-13:55
-14:55-17:25</t>
+          <t>06:59-15:01</t>
+        </is>
+      </c>
+      <c r="T20" s="6" t="inlineStr">
+        <is>
+          <t>08:03-13:59
+14:59-17:34</t>
         </is>
       </c>
     </row>
@@ -2306,96 +2397,101 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
+          <t>07:01-14:56</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>06:55-14:56</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>07:05-14:59</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>07:56-14:00
+14:55-17:26</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>06:56-15:02</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>06:56-15:01</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>07:05-14:58</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>07:03-14:55</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>08:03-14:00
+14:55-17:35</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
           <t>06:58-14:57</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>06:57-14:57</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>08:04-13:58
-15:00-17:29</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>07:03-15:05</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>07:00-14:57</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>07:05-15:01</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:00</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>07:56-13:56
-15:05-17:27</t>
-        </is>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:56</t>
-        </is>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:00</t>
-        </is>
-      </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:03</t>
+          <t>07:01-15:01</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:57</t>
+          <t>07:05-15:00</t>
         </is>
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>07:55-14:04
-14:59-17:35</t>
+          <t>06:57-15:05</t>
         </is>
       </c>
       <c r="O21" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:57</t>
+          <t>08:05-13:58
+14:58-17:35</t>
         </is>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:03</t>
+          <t>07:01-15:02</t>
         </is>
       </c>
       <c r="Q21" s="6" t="inlineStr">
         <is>
-          <t>08:57-14:00</t>
+          <t>07:01-15:00</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:03</t>
+          <t>08:57-13:56</t>
         </is>
       </c>
       <c r="S21" s="6" t="inlineStr">
         <is>
-          <t>08:00-14:03
-14:55-17:35</t>
+          <t>06:58-14:59</t>
+        </is>
+      </c>
+      <c r="T21" s="6" t="inlineStr">
+        <is>
+          <t>08:02-14:01
+14:59-17:34</t>
         </is>
       </c>
     </row>
@@ -2407,96 +2503,101 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:05</t>
+          <t>07:02-15:04</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:05</t>
+          <t>07:02-14:57</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>08:01-13:57
-15:04-17:34</t>
+          <t>06:59-15:00</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:57</t>
+          <t>07:56-14:05
+15:05-17:26</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:58</t>
+          <t>06:55-15:05</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:59</t>
+          <t>07:02-15:05</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:04</t>
+          <t>07:01-14:56</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>08:05-13:58
-15:04-17:32</t>
+          <t>07:04-15:02</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
+          <t>08:00-13:59
+15:05-17:31</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>06:57-15:05</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>06:55-15:01</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>06:55-15:02</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>07:02-14:56</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>07:59-13:55
+14:59-17:26</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>06:55-15:02</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
           <t>07:05-15:03</t>
         </is>
       </c>
-      <c r="K22" s="6" t="inlineStr">
-        <is>
-          <t>06:57-15:01</t>
-        </is>
-      </c>
-      <c r="L22" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:57</t>
-        </is>
-      </c>
-      <c r="M22" s="6" t="inlineStr">
-        <is>
-          <t>07:03-15:05</t>
-        </is>
-      </c>
-      <c r="N22" s="6" t="inlineStr">
-        <is>
-          <t>07:59-13:59
-14:59-17:29</t>
-        </is>
-      </c>
-      <c r="O22" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:05</t>
-        </is>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>07:04-15:02</t>
-        </is>
-      </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>08:57-14:02</t>
-        </is>
-      </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:57</t>
+          <t>08:55-14:05</t>
         </is>
       </c>
       <c r="S22" s="6" t="inlineStr">
         <is>
-          <t>08:03-14:00
-15:03-17:27</t>
+          <t>07:04-15:03</t>
+        </is>
+      </c>
+      <c r="T22" s="6" t="inlineStr">
+        <is>
+          <t>08:04-14:00
+15:05-17:30</t>
         </is>
       </c>
     </row>
@@ -2508,96 +2609,101 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:55</t>
+          <t>07:05-15:03</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:56</t>
+          <t>07:02-14:55</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>08:00-14:03
-14:57-17:27</t>
+          <t>06:56-15:01</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:55</t>
+          <t>07:56-14:01
+15:04-17:32</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:03</t>
+          <t>07:02-15:02</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:59</t>
+          <t>07:05-15:00</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:04</t>
+          <t>06:56-14:58</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>07:59-14:00
-15:00-17:32</t>
+          <t>06:59-14:55</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:59</t>
+          <t>08:00-13:55
+14:55-17:31</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:57</t>
+          <t>07:04-14:57</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:05</t>
+          <t>07:04-14:57</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:57</t>
+          <t>07:01-14:55</t>
         </is>
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
-          <t>08:04-14:01
-14:58-17:33</t>
+          <t>07:04-15:01</t>
         </is>
       </c>
       <c r="O23" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:05</t>
+          <t>08:02-13:56
+15:01-17:32</t>
         </is>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:03</t>
+          <t>07:00-15:03</t>
         </is>
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
-          <t>09:02-14:05</t>
+          <t>06:55-15:02</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:58</t>
+          <t>08:58-13:59</t>
         </is>
       </c>
       <c r="S23" s="6" t="inlineStr">
         <is>
-          <t>08:00-14:01
-15:05-17:30</t>
+          <t>06:57-14:55</t>
+        </is>
+      </c>
+      <c r="T23" s="6" t="inlineStr">
+        <is>
+          <t>07:56-13:59
+14:59-17:31</t>
         </is>
       </c>
     </row>
@@ -2697,6 +2803,11 @@
           <t>DESCANSO</t>
         </is>
       </c>
+      <c r="T24" s="4" t="inlineStr">
+        <is>
+          <t>DESCANSO</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -2794,6 +2905,11 @@
           <t>DESCANSO</t>
         </is>
       </c>
+      <c r="T25" s="4" t="inlineStr">
+        <is>
+          <t>DESCANSO</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
@@ -2803,96 +2919,101 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:59</t>
+          <t>06:56-15:04</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:02</t>
+          <t>07:00-15:02</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
+          <t>06:55-15:04</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>07:59-13:55
+14:59-17:34</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>06:56-15:00</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>06:57-15:00</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>07:02-14:55</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:01</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
           <t>07:58-14:05
+14:58-17:32</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>07:05-15:02</t>
+        </is>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>07:03-15:00</t>
+        </is>
+      </c>
+      <c r="M26" s="6" t="inlineStr">
+        <is>
+          <t>07:04-14:55</t>
+        </is>
+      </c>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>06:56-15:02</t>
+        </is>
+      </c>
+      <c r="O26" s="6" t="inlineStr">
+        <is>
+          <t>07:56-13:58
+14:56-17:35</t>
+        </is>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>06:58-15:04</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>07:03-14:56</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>09:05-13:59</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>07:02-15:05</t>
+        </is>
+      </c>
+      <c r="T26" s="6" t="inlineStr">
+        <is>
+          <t>08:02-13:55
 15:01-17:28</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:04</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:05</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:55</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>07:03-14:58</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>07:58-13:56
-14:57-17:27</t>
-        </is>
-      </c>
-      <c r="J26" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:58</t>
-        </is>
-      </c>
-      <c r="K26" s="6" t="inlineStr">
-        <is>
-          <t>07:05-15:04</t>
-        </is>
-      </c>
-      <c r="L26" s="6" t="inlineStr">
-        <is>
-          <t>07:02-14:57</t>
-        </is>
-      </c>
-      <c r="M26" s="6" t="inlineStr">
-        <is>
-          <t>07:01-14:58</t>
-        </is>
-      </c>
-      <c r="N26" s="6" t="inlineStr">
-        <is>
-          <t>08:05-13:59
-15:02-17:26</t>
-        </is>
-      </c>
-      <c r="O26" s="6" t="inlineStr">
-        <is>
-          <t>07:04-15:03</t>
-        </is>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:01</t>
-        </is>
-      </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>09:00-14:05</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>06:58-15:04</t>
-        </is>
-      </c>
-      <c r="S26" s="6" t="inlineStr">
-        <is>
-          <t>08:01-14:00
-14:57-17:30</t>
         </is>
       </c>
     </row>
@@ -2904,96 +3025,101 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:03</t>
+          <t>07:04-15:03</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
+          <t>07:00-14:58</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>07:03-15:04</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>07:59-14:00
+15:05-17:31</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>07:02-15:01</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>06:57-14:59</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>07:00-14:59</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>07:05-15:00</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>07:55-14:00
+14:57-17:31</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>06:57-15:02</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>06:56-14:56</t>
+        </is>
+      </c>
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t>07:05-14:58</t>
+        </is>
+      </c>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
           <t>07:01-14:58</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>07:56-14:01
-15:01-17:25</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>07:01-15:00</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>06:59-14:57</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>07:04-14:59</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:01</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>07:59-14:02
-15:03-17:27</t>
-        </is>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
-        <is>
-          <t>06:59-14:55</t>
-        </is>
-      </c>
-      <c r="K27" s="6" t="inlineStr">
-        <is>
-          <t>07:04-14:58</t>
-        </is>
-      </c>
-      <c r="L27" s="6" t="inlineStr">
-        <is>
-          <t>06:58-15:00</t>
-        </is>
-      </c>
-      <c r="M27" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:58</t>
-        </is>
-      </c>
-      <c r="N27" s="6" t="inlineStr">
-        <is>
-          <t>07:55-13:55
-14:58-17:29</t>
-        </is>
-      </c>
       <c r="O27" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:05</t>
+          <t>08:05-13:57
+15:02-17:35</t>
         </is>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:01</t>
+          <t>06:56-15:04</t>
         </is>
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
-          <t>08:55-13:59</t>
+          <t>07:02-15:00</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:04</t>
+          <t>09:04-13:58</t>
         </is>
       </c>
       <c r="S27" s="6" t="inlineStr">
         <is>
-          <t>07:57-14:02
-14:57-17:27</t>
+          <t>07:01-14:56</t>
+        </is>
+      </c>
+      <c r="T27" s="6" t="inlineStr">
+        <is>
+          <t>07:57-14:01
+15:05-17:25</t>
         </is>
       </c>
     </row>
@@ -3005,96 +3131,101 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:00</t>
+          <t>06:58-15:05</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:05</t>
+          <t>06:59-14:59</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>07:59-14:03
-15:00-17:34</t>
+          <t>07:05-15:05</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:04</t>
+          <t>08:03-14:00
+15:01-17:35</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:57</t>
+          <t>07:04-14:56</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:57</t>
+          <t>07:00-15:00</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:59</t>
+          <t>06:57-14:55</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>08:02-14:00
+          <t>06:57-14:55</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>07:57-13:55
+15:02-17:27</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>07:00-15:04</t>
+        </is>
+      </c>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>07:02-15:04</t>
+        </is>
+      </c>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>07:00-15:05</t>
+        </is>
+      </c>
+      <c r="N28" s="6" t="inlineStr">
+        <is>
+          <t>07:04-14:57</t>
+        </is>
+      </c>
+      <c r="O28" s="6" t="inlineStr">
+        <is>
+          <t>07:58-14:00
 14:57-17:28</t>
         </is>
       </c>
-      <c r="J28" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:00</t>
-        </is>
-      </c>
-      <c r="K28" s="6" t="inlineStr">
-        <is>
-          <t>06:59-15:02</t>
-        </is>
-      </c>
-      <c r="L28" s="6" t="inlineStr">
-        <is>
-          <t>07:03-14:55</t>
-        </is>
-      </c>
-      <c r="M28" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:58</t>
-        </is>
-      </c>
-      <c r="N28" s="6" t="inlineStr">
-        <is>
-          <t>08:02-14:01
-15:04-17:34</t>
-        </is>
-      </c>
-      <c r="O28" s="6" t="inlineStr">
-        <is>
-          <t>07:04-15:00</t>
-        </is>
-      </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:05</t>
+          <t>06:57-15:03</t>
         </is>
       </c>
       <c r="Q28" s="6" t="inlineStr">
         <is>
-          <t>09:04-13:56</t>
+          <t>07:00-14:55</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:02</t>
+          <t>09:03-14:00</t>
         </is>
       </c>
       <c r="S28" s="6" t="inlineStr">
         <is>
-          <t>07:58-13:55
-15:01-17:33</t>
+          <t>06:56-15:04</t>
+        </is>
+      </c>
+      <c r="T28" s="6" t="inlineStr">
+        <is>
+          <t>08:04-14:00
+15:03-17:25</t>
         </is>
       </c>
     </row>
@@ -3106,96 +3237,101 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:04</t>
+          <t>07:04-14:57</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
+          <t>06:59-15:03</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>07:04-14:58</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>08:04-13:55
+15:03-17:32</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>07:01-14:56</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>06:56-15:05</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>07:04-15:04</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>07:01-14:58</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>07:57-13:57
+14:57-17:32</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>06:55-15:03</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>06:55-15:03</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>06:57-15:05</t>
+        </is>
+      </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>06:57-14:59</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>07:56-14:03
+15:00-17:27</t>
+        </is>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
           <t>07:00-14:58</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>08:01-14:02
-15:04-17:35</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>06:58-15:03</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>07:04-14:58</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>08:58-14:01</t>
+        </is>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
         <is>
           <t>07:01-15:01</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>06:58-14:58</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>07:01-14:56</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>07:55-13:56
-15:03-17:25</t>
-        </is>
-      </c>
-      <c r="J29" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:58</t>
-        </is>
-      </c>
-      <c r="K29" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:04</t>
-        </is>
-      </c>
-      <c r="L29" s="6" t="inlineStr">
-        <is>
-          <t>07:00-14:58</t>
-        </is>
-      </c>
-      <c r="M29" s="6" t="inlineStr">
-        <is>
-          <t>06:58-14:57</t>
-        </is>
-      </c>
-      <c r="N29" s="6" t="inlineStr">
-        <is>
-          <t>07:56-14:05
-14:56-17:31</t>
-        </is>
-      </c>
-      <c r="O29" s="6" t="inlineStr">
-        <is>
-          <t>07:05-15:04</t>
-        </is>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>07:03-15:01</t>
-        </is>
-      </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>09:03-14:01</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:03</t>
-        </is>
-      </c>
-      <c r="S29" s="6" t="inlineStr">
-        <is>
-          <t>08:02-14:00
-15:04-17:28</t>
+      <c r="T29" s="6" t="inlineStr">
+        <is>
+          <t>08:05-13:55
+14:55-17:25</t>
         </is>
       </c>
     </row>
@@ -3207,96 +3343,101 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:59</t>
+          <t>06:56-15:02</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
+          <t>06:57-14:56</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>06:56-15:01</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>08:05-13:59
+14:55-17:32</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>07:04-14:55</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>07:05-14:56</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>06:59-14:58</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>06:57-15:03</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>08:02-14:05
+15:02-17:32</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
           <t>07:04-15:02</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>08:03-14:05
-15:03-17:26</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>06:56-14:55</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:03</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>07:03-15:01</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:02</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>08:05-13:56
-15:00-17:26</t>
-        </is>
-      </c>
-      <c r="J30" s="6" t="inlineStr">
-        <is>
-          <t>07:04-15:00</t>
-        </is>
-      </c>
-      <c r="K30" s="6" t="inlineStr">
-        <is>
-          <t>07:01-14:58</t>
-        </is>
-      </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:02</t>
+          <t>07:02-15:05</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:55</t>
+          <t>07:01-14:55</t>
         </is>
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>07:57-13:55
-14:58-17:25</t>
+          <t>07:03-15:04</t>
         </is>
       </c>
       <c r="O30" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:57</t>
+          <t>08:02-13:58
+15:02-17:34</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:03</t>
+          <t>07:01-14:59</t>
         </is>
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>09:00-14:05</t>
+          <t>06:59-14:57</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:55</t>
+          <t>09:01-13:58</t>
         </is>
       </c>
       <c r="S30" s="6" t="inlineStr">
         <is>
-          <t>08:05-13:55
-15:00-17:30</t>
+          <t>06:59-14:58</t>
+        </is>
+      </c>
+      <c r="T30" s="6" t="inlineStr">
+        <is>
+          <t>08:04-13:58
+15:04-17:35</t>
         </is>
       </c>
     </row>
@@ -3396,6 +3537,11 @@
           <t>DESCANSO</t>
         </is>
       </c>
+      <c r="T31" s="4" t="inlineStr">
+        <is>
+          <t>DESCANSO</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
@@ -3493,6 +3639,11 @@
           <t>DESCANSO</t>
         </is>
       </c>
+      <c r="T32" s="4" t="inlineStr">
+        <is>
+          <t>DESCANSO</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
@@ -3502,96 +3653,101 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:59</t>
+          <t>06:59-15:00</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:02</t>
+          <t>07:05-15:01</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>07:55-13:56
-15:03-17:34</t>
+          <t>07:00-15:02</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:04</t>
+          <t>08:05-14:03
+15:05-17:35</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:58</t>
+          <t>06:59-15:05</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
+          <t>07:02-14:58</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>06:59-14:56</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>06:55-14:58</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>08:01-14:05
+15:01-17:32</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>07:01-15:04</t>
+        </is>
+      </c>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>06:57-14:58</t>
+        </is>
+      </c>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>06:55-14:56</t>
+        </is>
+      </c>
+      <c r="N33" s="6" t="inlineStr">
+        <is>
           <t>06:58-14:55</t>
         </is>
       </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>06:57-15:05</t>
-        </is>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>07:59-13:59
-14:59-17:31</t>
-        </is>
-      </c>
-      <c r="J33" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:05</t>
-        </is>
-      </c>
-      <c r="K33" s="6" t="inlineStr">
-        <is>
-          <t>06:58-14:55</t>
-        </is>
-      </c>
-      <c r="L33" s="6" t="inlineStr">
-        <is>
-          <t>06:55-14:55</t>
-        </is>
-      </c>
-      <c r="M33" s="6" t="inlineStr">
+      <c r="O33" s="6" t="inlineStr">
+        <is>
+          <t>08:01-14:00
+14:58-17:34</t>
+        </is>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>07:04-15:04</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
         <is>
           <t>07:04-14:57</t>
         </is>
       </c>
-      <c r="N33" s="6" t="inlineStr">
-        <is>
-          <t>08:02-13:58
-15:00-17:35</t>
-        </is>
-      </c>
-      <c r="O33" s="6" t="inlineStr">
-        <is>
-          <t>07:02-15:00</t>
-        </is>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>07:04-14:58</t>
-        </is>
-      </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>09:01-14:00</t>
-        </is>
-      </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:02</t>
+          <t>08:56-13:55</t>
         </is>
       </c>
       <c r="S33" s="6" t="inlineStr">
         <is>
-          <t>07:55-14:03
-15:01-17:33</t>
+          <t>07:05-14:55</t>
+        </is>
+      </c>
+      <c r="T33" s="6" t="inlineStr">
+        <is>
+          <t>08:02-13:59
+15:05-17:25</t>
         </is>
       </c>
     </row>
@@ -3603,102 +3759,107 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:56</t>
+          <t>07:05-15:04</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:55</t>
+          <t>07:02-15:04</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
+          <t>07:04-14:55</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
           <t>07:59-13:56
-15:02-17:25</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>07:02-15:02</t>
+15:00-17:30</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:55</t>
+          <t>06:56-15:04</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:57</t>
+          <t>07:04-14:57</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:03</t>
+          <t>07:02-15:04</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>07:59-13:55
-15:02-17:34</t>
+          <t>07:05-15:02</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:03</t>
+          <t>08:04-14:02
+15:01-17:28</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:04</t>
+          <t>06:58-14:58</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:02</t>
+          <t>07:05-15:01</t>
         </is>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:04</t>
+          <t>06:58-15:03</t>
         </is>
       </c>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>07:57-14:03
-15:01-17:35</t>
+          <t>06:56-15:00</t>
         </is>
       </c>
       <c r="O34" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:55</t>
+          <t>07:55-13:59
+14:58-17:31</t>
         </is>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:05</t>
+          <t>07:00-15:01</t>
         </is>
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>08:55-13:56</t>
+          <t>07:04-14:56</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:00</t>
+          <t>09:03-13:57</t>
         </is>
       </c>
       <c r="S34" s="6" t="inlineStr">
         <is>
-          <t>08:00-13:55
-15:02-17:28</t>
+          <t>07:02-14:56</t>
+        </is>
+      </c>
+      <c r="T34" s="6" t="inlineStr">
+        <is>
+          <t>07:57-13:59
+15:02-17:31</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Cuadrante_Marzo_2026.xlsx
+++ b/Cuadrante_Marzo_2026.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T34"/>
+  <dimension ref="A1:S34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,6 @@
     <col width="25" customWidth="1" min="17" max="17"/>
     <col width="25" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
-    <col width="25" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -523,85 +522,80 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Alberto Gómez Marín</t>
+          <t>Antonio Escalzo Morales</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Antonio Escalzo Morales</t>
+          <t>Antonio Ramón Fuentes Medina</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Antonio Ramón Fuentes Medina</t>
+          <t>Antonio Ruíz Perete</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Antonio Ruíz Perete</t>
+          <t>Fabio Gutiérrez Basante</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Fabio Gutiérrez Basante</t>
+          <t>Francisco Javier Cárdenas Moga</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Francisco Javier Cárdenas Moga</t>
+          <t>Francisco Ordoñez Perabá</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Francisco Ordoñez Perabá</t>
+          <t>Héctor López Ramírez</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Héctor López Ramírez</t>
+          <t>Javier Galera Andújar</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Javier Galera Andújar</t>
+          <t>Jesús Montilla Hermoso</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Jesús Montilla Hermoso</t>
+          <t>Juan José Borrás Ferrete</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Juan José Borrás Ferrete</t>
+          <t>Lourdes Fuentes Buendía</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Lourdes Fuentes Buendía</t>
+          <t>Luis Miguel Colmenero Cobo</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Luis Miguel Colmenero Cobo</t>
+          <t>Manuel Martín Martínez</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Manuel Martín Martínez</t>
+          <t>Manuel Peinado García</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>Manuel Peinado García</t>
+          <t>Tomás García</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>Tomás García</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>Victoria Romero Sabalete</t>
         </is>
@@ -703,11 +697,6 @@
           <t>DESCANSO</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -717,101 +706,96 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:56</t>
+          <t>07:02-14:58</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:04</t>
+          <t>07:00-15:03</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:03</t>
+          <t>07:55-14:02
+14:56-17:26</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>08:01-13:58
-14:59-17:34</t>
+          <t>07:00-15:02</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:55</t>
+          <t>07:04-14:58</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:02</t>
+          <t>07:01-15:01</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:01</t>
+          <t>07:03-15:01</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:03</t>
+          <t>08:03-13:55
+15:05-17:28</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>08:05-13:59
-14:55-17:26</t>
+          <t>06:59-15:02</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:04</t>
+          <t>07:01-14:56</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:01</t>
+          <t>07:02-15:02</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:55</t>
+          <t>06:55-15:00</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:04</t>
+          <t>08:02-13:55
+15:01-17:32</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>07:56-13:56
-14:56-17:34</t>
+          <t>06:55-15:04</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:02</t>
+          <t>07:01-15:00</t>
         </is>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:05</t>
+          <t>09:05-13:55</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>09:03-14:00</t>
+          <t>07:04-14:56</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:57</t>
-        </is>
-      </c>
-      <c r="T5" s="6" t="inlineStr">
-        <is>
-          <t>07:58-14:05
-14:56-17:28</t>
+          <t>08:00-13:57
+15:01-17:25</t>
         </is>
       </c>
     </row>
@@ -823,101 +807,96 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:00</t>
+          <t>07:00-14:57</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:59</t>
+          <t>07:02-14:55</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:04</t>
+          <t>07:57-14:02
+15:03-17:26</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>08:04-13:56
-15:02-17:26</t>
+          <t>06:58-15:00</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
+          <t>07:03-14:59</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>06:58-14:57</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>07:05-14:58</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>08:03-13:55
+14:58-17:30</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>06:55-14:57</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>07:00-14:59</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>06:57-15:00</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:05</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>08:05-13:56
+15:02-17:25</t>
+        </is>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
           <t>06:57-15:02</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>07:03-14:59</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>07:03-15:02</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>07:05-15:04</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>08:01-13:57
-14:59-17:32</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>07:00-14:56</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:02</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>06:56-14:56</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="inlineStr">
-        <is>
-          <t>06:57-14:56</t>
-        </is>
-      </c>
-      <c r="O6" s="6" t="inlineStr">
-        <is>
-          <t>08:04-13:59
-14:56-17:28</t>
-        </is>
-      </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:02</t>
+          <t>06:59-15:00</t>
         </is>
       </c>
       <c r="Q6" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:01</t>
+          <t>09:00-14:01</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>09:04-14:01</t>
+          <t>06:56-15:03</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:56</t>
-        </is>
-      </c>
-      <c r="T6" s="6" t="inlineStr">
-        <is>
-          <t>08:04-14:03
-15:00-17:31</t>
+          <t>08:00-13:59
+15:05-17:25</t>
         </is>
       </c>
     </row>
@@ -929,101 +908,96 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:00</t>
+          <t>07:05-14:55</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:57</t>
+          <t>07:03-14:55</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
+          <t>08:02-14:05
+15:02-17:28</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>06:55-15:01</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
           <t>06:57-14:58</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>07:55-14:00
-14:59-17:26</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>06:56-14:56</t>
-        </is>
-      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:04</t>
+          <t>07:02-14:56</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:04</t>
+          <t>07:00-14:59</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:05</t>
+          <t>08:03-14:01
+14:59-17:29</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>07:58-13:58
-15:03-17:32</t>
+          <t>07:03-14:58</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:01</t>
+          <t>06:55-14:56</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:02</t>
+          <t>07:05-14:59</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:04</t>
+          <t>06:57-14:59</t>
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:55</t>
+          <t>08:00-13:56
+14:57-17:27</t>
         </is>
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>
-          <t>08:02-13:59
-14:55-17:26</t>
+          <t>07:05-14:56</t>
         </is>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:58</t>
+          <t>06:57-14:55</t>
         </is>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:04</t>
+          <t>08:56-13:58</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>09:04-14:05</t>
+          <t>06:56-15:01</t>
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:04</t>
-        </is>
-      </c>
-      <c r="T7" s="6" t="inlineStr">
-        <is>
-          <t>07:55-13:59
-14:58-17:33</t>
+          <t>07:56-14:05
+15:00-17:29</t>
         </is>
       </c>
     </row>
@@ -1035,101 +1009,96 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:05</t>
+          <t>06:59-14:57</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:04</t>
+          <t>06:55-15:00</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:58</t>
+          <t>08:03-14:01
+15:03-17:25</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>08:01-14:02
-15:00-17:35</t>
+          <t>07:04-14:55</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:56</t>
+          <t>06:57-14:59</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:00</t>
+          <t>07:02-15:00</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:02</t>
+          <t>06:59-14:57</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:04</t>
+          <t>07:56-13:55
+14:56-17:32</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>07:57-14:02
-14:59-17:34</t>
+          <t>06:59-15:04</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:56</t>
+          <t>06:59-15:03</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:05</t>
+          <t>07:04-15:05</t>
         </is>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:55</t>
+          <t>06:56-14:58</t>
         </is>
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:03</t>
+          <t>07:59-13:58
+14:57-17:34</t>
         </is>
       </c>
       <c r="O8" s="6" t="inlineStr">
         <is>
-          <t>07:58-14:03
-15:03-17:28</t>
+          <t>07:03-15:02</t>
         </is>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:04</t>
+          <t>07:04-15:00</t>
         </is>
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:03</t>
+          <t>08:56-14:03</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>08:58-14:00</t>
+          <t>07:04-15:00</t>
         </is>
       </c>
       <c r="S8" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:55</t>
-        </is>
-      </c>
-      <c r="T8" s="6" t="inlineStr">
-        <is>
-          <t>08:05-14:00
-14:58-17:32</t>
+          <t>07:59-13:56
+15:05-17:35</t>
         </is>
       </c>
     </row>
@@ -1141,101 +1110,96 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:04</t>
+          <t>06:57-14:55</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:03</t>
+          <t>07:04-15:02</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:59</t>
+          <t>07:55-14:00
+15:03-17:32</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>07:57-13:57
+          <t>06:56-15:02</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>07:01-15:03</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>06:58-14:55</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>06:57-15:01</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>07:55-14:03
+14:56-17:26</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>06:55-15:00</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>06:59-14:58</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>07:01-15:02</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>07:01-15:03</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>08:03-14:00
 15:05-17:29</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>06:58-14:57</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:05</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>07:04-14:55</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>06:58-15:04</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>08:05-13:56
-14:55-17:30</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>06:58-15:01</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>06:58-15:03</t>
-        </is>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:59</t>
-        </is>
-      </c>
-      <c r="N9" s="6" t="inlineStr">
-        <is>
-          <t>07:03-15:02</t>
-        </is>
-      </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>07:57-14:03
-15:03-17:29</t>
+          <t>07:05-15:00</t>
         </is>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:58</t>
+          <t>06:56-14:59</t>
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:03</t>
+          <t>08:59-13:57</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>08:56-13:57</t>
+          <t>06:58-15:02</t>
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:00</t>
-        </is>
-      </c>
-      <c r="T9" s="6" t="inlineStr">
-        <is>
-          <t>07:57-13:59
-15:05-17:33</t>
+          <t>07:58-13:59
+14:59-17:29</t>
         </is>
       </c>
     </row>
@@ -1335,11 +1299,6 @@
           <t>DESCANSO</t>
         </is>
       </c>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -1437,11 +1396,6 @@
           <t>DESCANSO</t>
         </is>
       </c>
-      <c r="T11" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -1451,101 +1405,96 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:59</t>
+          <t>07:01-14:57</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:05</t>
+          <t>07:04-14:57</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:03</t>
+          <t>08:03-14:04
+15:04-17:25</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>08:03-14:01
-14:58-17:26</t>
+          <t>07:04-14:58</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:01</t>
+          <t>07:00-14:55</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:55</t>
+          <t>06:57-14:57</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
+          <t>07:04-15:02</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>07:59-14:02
+15:01-17:33</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>07:00-15:04</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>07:04-15:02</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
           <t>06:58-15:02</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>07:01-15:01</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>07:59-14:03
-15:02-17:34</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>06:56-15:05</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="inlineStr">
-        <is>
-          <t>07:05-15:04</t>
-        </is>
-      </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:57</t>
+          <t>07:01-15:00</t>
         </is>
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:03</t>
+          <t>07:59-13:55
+15:01-17:32</t>
         </is>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
-          <t>07:55-14:04
-15:04-17:35</t>
+          <t>06:59-14:58</t>
         </is>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:59</t>
+          <t>07:01-15:05</t>
         </is>
       </c>
       <c r="Q12" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:55</t>
+          <t>08:55-13:55</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>09:04-13:56</t>
+          <t>07:01-15:03</t>
         </is>
       </c>
       <c r="S12" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:03</t>
-        </is>
-      </c>
-      <c r="T12" s="6" t="inlineStr">
-        <is>
-          <t>07:56-14:04
-15:02-17:29</t>
+          <t>08:03-13:55
+14:56-17:28</t>
         </is>
       </c>
     </row>
@@ -1557,101 +1506,96 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:02</t>
+          <t>06:59-15:00</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:56</t>
+          <t>07:05-14:58</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:04</t>
+          <t>08:03-13:55
+15:02-17:34</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>07:55-14:05
-14:56-17:31</t>
+          <t>06:55-14:55</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:00</t>
+          <t>06:55-14:55</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:01</t>
+          <t>06:55-15:05</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:59</t>
+          <t>06:56-14:56</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:55</t>
+          <t>08:05-14:05
+15:01-17:30</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>07:56-13:57
-14:59-17:31</t>
+          <t>07:01-14:58</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:03</t>
+          <t>06:58-14:55</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
+          <t>06:59-15:00</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>07:01-14:56</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>08:02-13:59
+15:04-17:31</t>
+        </is>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
           <t>07:00-14:58</t>
         </is>
       </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>07:00-15:05</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="inlineStr">
-        <is>
-          <t>06:57-14:57</t>
-        </is>
-      </c>
-      <c r="O13" s="6" t="inlineStr">
-        <is>
-          <t>07:55-13:55
-15:04-17:34</t>
-        </is>
-      </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:00</t>
+          <t>07:01-14:57</t>
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:00</t>
+          <t>08:59-14:05</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>08:59-13:57</t>
+          <t>07:03-15:05</t>
         </is>
       </c>
       <c r="S13" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:02</t>
-        </is>
-      </c>
-      <c r="T13" s="6" t="inlineStr">
-        <is>
-          <t>07:59-14:01
-14:59-17:35</t>
+          <t>08:00-13:56
+15:04-17:35</t>
         </is>
       </c>
     </row>
@@ -1663,101 +1607,96 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:03</t>
+          <t>07:05-14:56</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:01</t>
+          <t>07:03-15:03</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:04</t>
+          <t>07:56-13:57
+14:57-17:31</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>08:00-13:58
-14:56-17:34</t>
+          <t>07:01-15:02</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:57</t>
+          <t>07:05-15:03</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:03</t>
+          <t>07:01-15:04</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:05</t>
+          <t>07:05-14:59</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:57</t>
+          <t>08:05-13:59
+14:56-17:27</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>07:55-13:57
-15:00-17:29</t>
+          <t>07:00-15:05</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:59</t>
+          <t>06:56-14:57</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:03</t>
+          <t>06:57-15:03</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:02</t>
+          <t>07:04-14:57</t>
         </is>
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:57</t>
+          <t>08:05-13:58
+14:56-17:33</t>
         </is>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
-          <t>08:01-14:04
-15:05-17:34</t>
+          <t>06:55-14:56</t>
         </is>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:02</t>
+          <t>06:59-15:00</t>
         </is>
       </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:03</t>
+          <t>08:58-13:56</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>08:55-14:02</t>
+          <t>07:03-14:55</t>
         </is>
       </c>
       <c r="S14" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:58</t>
-        </is>
-      </c>
-      <c r="T14" s="6" t="inlineStr">
-        <is>
-          <t>08:04-14:05
-15:05-17:25</t>
+          <t>08:02-14:03
+14:58-17:29</t>
         </is>
       </c>
     </row>
@@ -1769,101 +1708,96 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:58</t>
+          <t>07:03-14:59</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:58</t>
+          <t>06:59-14:55</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:58</t>
+          <t>08:04-14:05
+15:03-17:33</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
+          <t>06:58-15:02</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>06:56-15:03</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>07:02-15:01</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>07:04-14:59</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
           <t>08:01-14:00
-14:59-17:33</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>06:55-14:56</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>07:01-14:56</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
+15:05-17:28</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>07:02-15:02</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>06:59-15:02</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
         <is>
           <t>07:04-14:59</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>07:05-14:58</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>08:04-14:01
-15:01-17:26</t>
-        </is>
-      </c>
-      <c r="K15" s="6" t="inlineStr">
-        <is>
-          <t>07:04-14:55</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>06:58-15:05</t>
-        </is>
-      </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:59</t>
+          <t>07:00-14:56</t>
         </is>
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:05</t>
+          <t>07:55-13:59
+14:59-17:35</t>
         </is>
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>08:03-13:59
-15:03-17:29</t>
+          <t>07:02-15:01</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:58</t>
+          <t>07:03-15:04</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:56</t>
+          <t>09:04-14:01</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>08:56-14:02</t>
+          <t>07:03-14:59</t>
         </is>
       </c>
       <c r="S15" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:04</t>
-        </is>
-      </c>
-      <c r="T15" s="6" t="inlineStr">
-        <is>
-          <t>08:02-14:00
-15:00-17:25</t>
+          <t>08:00-14:02
+14:56-17:30</t>
         </is>
       </c>
     </row>
@@ -1875,101 +1809,96 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:58</t>
+          <t>07:02-14:56</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:05</t>
+          <t>06:56-14:55</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:01</t>
+          <t>08:05-13:57
+15:01-17:34</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>07:59-14:00
-14:56-17:34</t>
+          <t>07:04-15:04</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:02</t>
+          <t>07:03-14:59</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:57</t>
+          <t>07:03-14:55</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:04</t>
+          <t>07:01-15:03</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:59</t>
+          <t>08:02-13:55
+15:03-17:26</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>08:03-14:03
-15:03-17:33</t>
+          <t>07:01-14:58</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:03</t>
+          <t>06:57-14:56</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:01</t>
+          <t>06:55-15:02</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:03</t>
+          <t>07:05-15:05</t>
         </is>
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:02</t>
+          <t>07:58-14:01
+14:56-17:33</t>
         </is>
       </c>
       <c r="O16" s="6" t="inlineStr">
         <is>
-          <t>08:03-14:05
-15:00-17:28</t>
+          <t>07:02-14:56</t>
         </is>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:05</t>
+          <t>07:03-15:05</t>
         </is>
       </c>
       <c r="Q16" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:59</t>
+          <t>08:58-13:55</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>09:02-14:05</t>
+          <t>06:56-15:03</t>
         </is>
       </c>
       <c r="S16" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:56</t>
-        </is>
-      </c>
-      <c r="T16" s="6" t="inlineStr">
-        <is>
-          <t>07:56-14:04
-15:01-17:31</t>
+          <t>07:56-13:55
+14:55-17:35</t>
         </is>
       </c>
     </row>
@@ -2069,11 +1998,6 @@
           <t>DESCANSO</t>
         </is>
       </c>
-      <c r="T17" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
@@ -2171,11 +2095,6 @@
           <t>DESCANSO</t>
         </is>
       </c>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
@@ -2185,101 +2104,96 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:03</t>
+          <t>06:57-14:59</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:01</t>
+          <t>06:59-14:58</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:01</t>
+          <t>07:57-14:01
+15:02-17:35</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>08:02-14:00
-14:58-17:31</t>
+          <t>07:00-15:05</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:00</t>
+          <t>07:04-14:58</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:00</t>
+          <t>07:01-14:56</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:01</t>
+          <t>07:02-14:58</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:58</t>
+          <t>07:56-13:58
+15:03-17:26</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>07:58-14:01
-15:05-17:30</t>
+          <t>07:05-15:04</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:59</t>
+          <t>07:02-15:03</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:03</t>
+          <t>07:01-15:01</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:58</t>
+          <t>07:01-14:55</t>
         </is>
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:05</t>
+          <t>08:02-13:58
+15:04-17:34</t>
         </is>
       </c>
       <c r="O19" s="6" t="inlineStr">
         <is>
-          <t>08:01-13:57
-15:05-17:30</t>
+          <t>07:04-14:55</t>
         </is>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:03</t>
+          <t>06:57-15:03</t>
         </is>
       </c>
       <c r="Q19" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:55</t>
+          <t>09:01-14:05</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>08:58-13:58</t>
+          <t>07:01-15:04</t>
         </is>
       </c>
       <c r="S19" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:03</t>
-        </is>
-      </c>
-      <c r="T19" s="6" t="inlineStr">
-        <is>
-          <t>08:04-14:04
-15:03-17:32</t>
+          <t>08:04-13:58
+15:02-17:35</t>
         </is>
       </c>
     </row>
@@ -2291,101 +2205,96 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:03</t>
+          <t>06:55-14:56</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:02</t>
+          <t>07:00-14:56</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
+          <t>07:56-14:04
+14:56-17:34</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>07:01-14:58</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>06:59-14:57</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
           <t>06:55-15:02</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>08:04-13:55
-15:01-17:35</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>06:58-15:03</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>06:58-14:57</t>
-        </is>
-      </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:04</t>
+          <t>06:56-14:58</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:05</t>
+          <t>08:03-14:05
+14:55-17:29</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>08:02-14:04
-15:05-17:25</t>
+          <t>07:00-15:05</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:59</t>
+          <t>06:58-15:05</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:05</t>
+          <t>06:55-15:04</t>
         </is>
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:05</t>
+          <t>06:59-15:02</t>
         </is>
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:01</t>
+          <t>07:59-14:02
+14:59-17:28</t>
         </is>
       </c>
       <c r="O20" s="6" t="inlineStr">
         <is>
-          <t>07:55-13:56
-14:59-17:32</t>
+          <t>07:04-14:59</t>
         </is>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:56</t>
+          <t>07:01-15:02</t>
         </is>
       </c>
       <c r="Q20" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:00</t>
+          <t>09:04-13:57</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>09:01-14:02</t>
+          <t>07:04-15:03</t>
         </is>
       </c>
       <c r="S20" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:01</t>
-        </is>
-      </c>
-      <c r="T20" s="6" t="inlineStr">
-        <is>
-          <t>08:03-13:59
-14:59-17:34</t>
+          <t>08:03-14:00
+14:57-17:35</t>
         </is>
       </c>
     </row>
@@ -2397,101 +2306,96 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:56</t>
+          <t>06:56-14:57</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:56</t>
+          <t>07:00-14:58</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:59</t>
+          <t>08:01-14:05
+14:57-17:34</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>07:56-14:00
-14:55-17:26</t>
+          <t>06:57-14:58</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:02</t>
+          <t>07:00-14:57</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:01</t>
+          <t>07:03-14:56</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:58</t>
+          <t>07:00-15:01</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:55</t>
+          <t>08:00-13:55
+15:00-17:29</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>08:03-14:00
-14:55-17:35</t>
+          <t>06:59-14:56</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
+          <t>07:00-15:02</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>07:03-15:04</t>
+        </is>
+      </c>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
           <t>06:58-14:57</t>
         </is>
       </c>
-      <c r="L21" s="6" t="inlineStr">
-        <is>
-          <t>07:01-15:01</t>
-        </is>
-      </c>
-      <c r="M21" s="6" t="inlineStr">
-        <is>
-          <t>07:05-15:00</t>
-        </is>
-      </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:05</t>
+          <t>08:04-13:55
+14:58-17:32</t>
         </is>
       </c>
       <c r="O21" s="6" t="inlineStr">
         <is>
-          <t>08:05-13:58
-14:58-17:35</t>
+          <t>07:00-15:05</t>
         </is>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:02</t>
+          <t>06:58-15:03</t>
         </is>
       </c>
       <c r="Q21" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:00</t>
+          <t>08:55-13:59</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>08:57-13:56</t>
+          <t>06:59-14:58</t>
         </is>
       </c>
       <c r="S21" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:59</t>
-        </is>
-      </c>
-      <c r="T21" s="6" t="inlineStr">
-        <is>
-          <t>08:02-14:01
-14:59-17:34</t>
+          <t>07:56-14:03
+15:04-17:29</t>
         </is>
       </c>
     </row>
@@ -2503,101 +2407,96 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
+          <t>06:58-15:04</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>06:55-15:03</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>07:58-13:55
+15:03-17:26</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>07:00-14:55</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>06:59-14:56</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>07:01-14:59</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
           <t>07:02-15:04</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>07:57-13:56
+14:57-17:27</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>07:05-14:56</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>07:04-14:59</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
         <is>
           <t>07:02-14:57</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>06:59-15:00</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>07:56-14:05
-15:05-17:26</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:05</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>07:02-15:05</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>07:01-14:56</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>07:04-15:02</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>08:00-13:59
-15:05-17:31</t>
-        </is>
-      </c>
-      <c r="K22" s="6" t="inlineStr">
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>07:00-15:01</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>07:56-13:58
+15:05-17:27</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>07:01-14:59</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
         <is>
           <t>06:57-15:05</t>
         </is>
       </c>
-      <c r="L22" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:01</t>
-        </is>
-      </c>
-      <c r="M22" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:02</t>
-        </is>
-      </c>
-      <c r="N22" s="6" t="inlineStr">
-        <is>
-          <t>07:02-14:56</t>
-        </is>
-      </c>
-      <c r="O22" s="6" t="inlineStr">
-        <is>
-          <t>07:59-13:55
-14:59-17:26</t>
-        </is>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>06:55-15:02</t>
-        </is>
-      </c>
       <c r="Q22" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:03</t>
+          <t>09:00-14:03</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>08:55-14:05</t>
+          <t>06:56-14:57</t>
         </is>
       </c>
       <c r="S22" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:03</t>
-        </is>
-      </c>
-      <c r="T22" s="6" t="inlineStr">
-        <is>
-          <t>08:04-14:00
-15:05-17:30</t>
+          <t>08:02-14:00
+14:55-17:25</t>
         </is>
       </c>
     </row>
@@ -2609,101 +2508,96 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:03</t>
+          <t>06:57-14:55</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:55</t>
+          <t>06:57-15:01</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:01</t>
+          <t>07:57-13:58
+14:58-17:30</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>07:56-14:01
-15:04-17:32</t>
+          <t>07:03-14:58</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:02</t>
+          <t>07:00-14:55</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:00</t>
+          <t>06:59-15:00</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:58</t>
+          <t>06:59-14:56</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:55</t>
+          <t>07:57-14:03
+15:03-17:30</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>08:00-13:55
-14:55-17:31</t>
+          <t>07:02-15:03</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:57</t>
+          <t>06:55-14:55</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:57</t>
+          <t>07:05-14:57</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:55</t>
+          <t>06:59-15:00</t>
         </is>
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:01</t>
+          <t>07:56-14:05
+14:56-17:32</t>
         </is>
       </c>
       <c r="O23" s="6" t="inlineStr">
         <is>
-          <t>08:02-13:56
-15:01-17:32</t>
+          <t>06:59-15:03</t>
         </is>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:03</t>
+          <t>07:04-15:05</t>
         </is>
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:02</t>
+          <t>09:02-14:02</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>08:58-13:59</t>
+          <t>07:03-15:02</t>
         </is>
       </c>
       <c r="S23" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:55</t>
-        </is>
-      </c>
-      <c r="T23" s="6" t="inlineStr">
-        <is>
-          <t>07:56-13:59
-14:59-17:31</t>
+          <t>08:03-13:55
+14:56-17:31</t>
         </is>
       </c>
     </row>
@@ -2803,11 +2697,6 @@
           <t>DESCANSO</t>
         </is>
       </c>
-      <c r="T24" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -2905,11 +2794,6 @@
           <t>DESCANSO</t>
         </is>
       </c>
-      <c r="T25" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
@@ -2919,101 +2803,96 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:04</t>
+          <t>07:05-14:56</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:02</t>
+          <t>07:05-15:03</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:04</t>
+          <t>08:03-13:59
+15:01-17:25</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>07:59-13:55
-14:59-17:34</t>
+          <t>07:05-15:01</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:00</t>
+          <t>07:05-15:03</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:00</t>
+          <t>07:01-14:56</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:55</t>
+          <t>06:58-14:59</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:01</t>
+          <t>07:57-13:56
+15:01-17:27</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>07:58-14:05
-14:58-17:32</t>
+          <t>06:57-14:58</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:02</t>
+          <t>06:58-15:00</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:00</t>
+          <t>07:03-14:59</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:55</t>
+          <t>07:05-14:56</t>
         </is>
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:02</t>
+          <t>07:55-14:05
+14:56-17:31</t>
         </is>
       </c>
       <c r="O26" s="6" t="inlineStr">
         <is>
-          <t>07:56-13:58
-14:56-17:35</t>
+          <t>06:58-14:59</t>
         </is>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:04</t>
+          <t>07:03-14:55</t>
         </is>
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>07:03-14:56</t>
+          <t>08:55-13:57</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>09:05-13:59</t>
+          <t>06:58-14:59</t>
         </is>
       </c>
       <c r="S26" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:05</t>
-        </is>
-      </c>
-      <c r="T26" s="6" t="inlineStr">
-        <is>
-          <t>08:02-13:55
-15:01-17:28</t>
+          <t>08:04-13:58
+14:56-17:30</t>
         </is>
       </c>
     </row>
@@ -3025,101 +2904,96 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:03</t>
+          <t>06:56-14:58</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:58</t>
+          <t>07:05-15:02</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:04</t>
+          <t>07:59-13:58
+15:03-17:35</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>07:59-14:00
-15:05-17:31</t>
+          <t>07:05-15:04</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:01</t>
+          <t>07:03-15:00</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:59</t>
+          <t>06:59-15:01</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:59</t>
+          <t>07:05-15:01</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
+          <t>07:55-14:01
+15:04-17:26</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>06:58-14:57</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
           <t>07:05-15:00</t>
         </is>
       </c>
-      <c r="J27" s="6" t="inlineStr">
-        <is>
-          <t>07:55-14:00
-14:57-17:31</t>
-        </is>
-      </c>
-      <c r="K27" s="6" t="inlineStr">
-        <is>
-          <t>06:57-15:02</t>
-        </is>
-      </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>06:56-14:56</t>
+          <t>07:05-15:05</t>
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:58</t>
+          <t>07:05-15:01</t>
         </is>
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:58</t>
+          <t>08:00-14:01
+14:55-17:34</t>
         </is>
       </c>
       <c r="O27" s="6" t="inlineStr">
         <is>
-          <t>08:05-13:57
-15:02-17:35</t>
+          <t>06:57-14:57</t>
         </is>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:04</t>
+          <t>07:00-15:05</t>
         </is>
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:00</t>
+          <t>08:55-14:02</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>09:04-13:58</t>
+          <t>06:59-15:02</t>
         </is>
       </c>
       <c r="S27" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:56</t>
-        </is>
-      </c>
-      <c r="T27" s="6" t="inlineStr">
-        <is>
-          <t>07:57-14:01
-15:05-17:25</t>
+          <t>08:03-13:56
+14:55-17:28</t>
         </is>
       </c>
     </row>
@@ -3131,101 +3005,96 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:05</t>
+          <t>06:59-14:55</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:59</t>
+          <t>07:05-15:01</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:05</t>
+          <t>08:04-13:55
+14:56-17:34</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>08:03-14:00
-15:01-17:35</t>
+          <t>06:59-14:58</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:56</t>
+          <t>06:58-15:00</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:00</t>
+          <t>07:03-14:58</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:55</t>
+          <t>07:02-14:56</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:55</t>
+          <t>07:56-14:04
+14:58-17:28</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>07:57-13:55
-15:02-17:27</t>
+          <t>06:57-15:00</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:04</t>
+          <t>07:00-15:03</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
+          <t>07:04-14:57</t>
+        </is>
+      </c>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>07:02-15:05</t>
+        </is>
+      </c>
+      <c r="N28" s="6" t="inlineStr">
+        <is>
+          <t>07:55-14:03
+15:00-17:34</t>
+        </is>
+      </c>
+      <c r="O28" s="6" t="inlineStr">
+        <is>
           <t>07:02-15:04</t>
         </is>
       </c>
-      <c r="M28" s="6" t="inlineStr">
-        <is>
-          <t>07:00-15:05</t>
-        </is>
-      </c>
-      <c r="N28" s="6" t="inlineStr">
-        <is>
-          <t>07:04-14:57</t>
-        </is>
-      </c>
-      <c r="O28" s="6" t="inlineStr">
-        <is>
-          <t>07:58-14:00
-14:57-17:28</t>
-        </is>
-      </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:03</t>
+          <t>06:56-14:55</t>
         </is>
       </c>
       <c r="Q28" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:55</t>
+          <t>08:56-13:57</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>09:03-14:00</t>
+          <t>06:57-15:04</t>
         </is>
       </c>
       <c r="S28" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:04</t>
-        </is>
-      </c>
-      <c r="T28" s="6" t="inlineStr">
-        <is>
-          <t>08:04-14:00
-15:03-17:25</t>
+          <t>08:05-14:02
+15:03-17:26</t>
         </is>
       </c>
     </row>
@@ -3237,101 +3106,96 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:57</t>
+          <t>06:57-15:02</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:03</t>
+          <t>06:58-14:57</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:58</t>
+          <t>08:03-13:59
+14:57-17:27</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>08:04-13:55
-15:03-17:32</t>
+          <t>07:01-15:02</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:56</t>
+          <t>07:03-15:02</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:05</t>
+          <t>06:55-15:01</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:04</t>
+          <t>06:56-15:02</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:58</t>
+          <t>08:00-13:58
+15:01-17:34</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>07:57-13:57
-14:57-17:32</t>
+          <t>06:55-15:03</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:03</t>
+          <t>06:57-15:01</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>06:55-15:03</t>
+          <t>07:00-14:57</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:05</t>
+          <t>07:02-14:55</t>
         </is>
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:59</t>
+          <t>07:58-14:03
+14:57-17:31</t>
         </is>
       </c>
       <c r="O29" s="6" t="inlineStr">
         <is>
-          <t>07:56-14:03
-15:00-17:27</t>
+          <t>06:58-15:04</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>07:00-14:58</t>
+          <t>07:03-14:58</t>
         </is>
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:58</t>
+          <t>08:58-13:57</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>08:58-14:01</t>
+          <t>06:56-14:56</t>
         </is>
       </c>
       <c r="S29" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:01</t>
-        </is>
-      </c>
-      <c r="T29" s="6" t="inlineStr">
-        <is>
-          <t>08:05-13:55
-14:55-17:25</t>
+          <t>08:00-14:03
+15:01-17:34</t>
         </is>
       </c>
     </row>
@@ -3343,101 +3207,96 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:02</t>
+          <t>06:57-15:02</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:56</t>
+          <t>07:03-15:04</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:01</t>
+          <t>07:56-13:55
+15:02-17:28</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>08:05-13:59
-14:55-17:32</t>
+          <t>07:03-15:04</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:55</t>
+          <t>06:57-15:00</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:56</t>
+          <t>07:01-15:03</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:58</t>
+          <t>07:04-14:57</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>06:57-15:03</t>
+          <t>08:04-13:56
+15:02-17:31</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>08:02-14:05
-15:02-17:32</t>
+          <t>07:04-14:57</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:02</t>
+          <t>06:57-15:00</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:05</t>
+          <t>07:03-14:56</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:55</t>
+          <t>07:02-15:01</t>
         </is>
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>07:03-15:04</t>
+          <t>08:00-14:03
+15:01-17:28</t>
         </is>
       </c>
       <c r="O30" s="6" t="inlineStr">
         <is>
-          <t>08:02-13:58
-15:02-17:34</t>
+          <t>07:03-14:57</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>07:01-14:59</t>
+          <t>07:00-15:01</t>
         </is>
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:57</t>
+          <t>08:58-13:56</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>09:01-13:58</t>
+          <t>07:02-14:59</t>
         </is>
       </c>
       <c r="S30" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:58</t>
-        </is>
-      </c>
-      <c r="T30" s="6" t="inlineStr">
-        <is>
-          <t>08:04-13:58
-15:04-17:35</t>
+          <t>07:58-14:04
+15:02-17:35</t>
         </is>
       </c>
     </row>
@@ -3537,11 +3396,6 @@
           <t>DESCANSO</t>
         </is>
       </c>
-      <c r="T31" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
@@ -3639,11 +3493,6 @@
           <t>DESCANSO</t>
         </is>
       </c>
-      <c r="T32" s="4" t="inlineStr">
-        <is>
-          <t>DESCANSO</t>
-        </is>
-      </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
@@ -3653,101 +3502,96 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:00</t>
+          <t>06:57-15:05</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:01</t>
+          <t>07:03-14:57</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:02</t>
+          <t>08:05-13:56
+15:03-17:25</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>08:05-14:03
-15:05-17:35</t>
+          <t>07:00-14:56</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>06:59-15:05</t>
+          <t>07:05-15:04</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:58</t>
+          <t>06:57-14:55</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>06:59-14:56</t>
+          <t>06:56-14:59</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:58</t>
+          <t>07:56-14:03
+14:57-17:31</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>08:01-14:05
-15:01-17:32</t>
+          <t>07:04-14:57</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>07:01-15:04</t>
+          <t>07:04-15:01</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>06:57-14:58</t>
+          <t>07:05-14:56</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
-          <t>06:55-14:56</t>
+          <t>07:04-14:57</t>
         </is>
       </c>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:55</t>
+          <t>07:59-14:05
+15:04-17:33</t>
         </is>
       </c>
       <c r="O33" s="6" t="inlineStr">
         <is>
-          <t>08:01-14:00
-14:58-17:34</t>
+          <t>07:05-15:00</t>
         </is>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>07:04-15:04</t>
+          <t>06:59-15:03</t>
         </is>
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:57</t>
+          <t>08:58-13:59</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>08:56-13:55</t>
+          <t>07:03-14:56</t>
         </is>
       </c>
       <c r="S33" s="6" t="inlineStr">
         <is>
-          <t>07:05-14:55</t>
-        </is>
-      </c>
-      <c r="T33" s="6" t="inlineStr">
-        <is>
-          <t>08:02-13:59
-15:05-17:25</t>
+          <t>07:56-14:02
+14:59-17:30</t>
         </is>
       </c>
     </row>
@@ -3759,101 +3603,96 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:04</t>
+          <t>07:04-15:04</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:04</t>
+          <t>07:02-14:57</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:55</t>
+          <t>07:55-13:55
+15:01-17:35</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>07:59-13:56
-15:00-17:30</t>
+          <t>07:04-14:59</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:04</t>
+          <t>06:58-14:58</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:57</t>
+          <t>07:03-14:59</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>07:02-15:04</t>
+          <t>07:01-14:59</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:02</t>
+          <t>08:03-14:02
+15:01-17:35</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>08:04-14:02
-15:01-17:28</t>
+          <t>07:04-15:00</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>06:58-14:58</t>
+          <t>06:59-14:59</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
-          <t>07:05-15:01</t>
+          <t>07:04-15:01</t>
         </is>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
-          <t>06:58-15:03</t>
+          <t>06:57-15:04</t>
         </is>
       </c>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>06:56-15:00</t>
+          <t>08:02-14:05
+14:56-17:35</t>
         </is>
       </c>
       <c r="O34" s="6" t="inlineStr">
         <is>
-          <t>07:55-13:59
-14:58-17:31</t>
+          <t>06:57-15:00</t>
         </is>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>07:00-15:01</t>
+          <t>07:03-14:56</t>
         </is>
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>07:04-14:56</t>
+          <t>09:00-13:58</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>09:03-13:57</t>
+          <t>07:03-15:05</t>
         </is>
       </c>
       <c r="S34" s="6" t="inlineStr">
         <is>
-          <t>07:02-14:56</t>
-        </is>
-      </c>
-      <c r="T34" s="6" t="inlineStr">
-        <is>
-          <t>07:57-13:59
-15:02-17:31</t>
+          <t>07:56-14:03
+15:01-17:32</t>
         </is>
       </c>
     </row>

--- a/Cuadrante_Marzo_2026.xlsx
+++ b/Cuadrante_Marzo_2026.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,27 +26,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="10"/>
+      <name val="Calibri"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E75B6"/>
-        <bgColor rgb="002E75B6"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -58,10 +47,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -69,11 +66,13 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -444,41 +443,41 @@
   <dimension ref="A1:AF20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="15" customWidth="1" min="20" max="20"/>
-    <col width="15" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
-    <col width="15" customWidth="1" min="23" max="23"/>
-    <col width="15" customWidth="1" min="24" max="24"/>
-    <col width="15" customWidth="1" min="25" max="25"/>
-    <col width="15" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="15" customWidth="1" min="28" max="28"/>
-    <col width="15" customWidth="1" min="29" max="29"/>
-    <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="15" customWidth="1" min="31" max="31"/>
-    <col width="15" customWidth="1" min="32" max="32"/>
+    <col width="33.42578125" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Empleado / Fecha</t>
@@ -640,7 +639,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="25" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Adrián Iniesta Punzano</t>
@@ -678,7 +677,7 @@
       <c r="AE2" s="3" t="inlineStr"/>
       <c r="AF2" s="3" t="inlineStr"/>
     </row>
-    <row r="3" ht="25" customHeight="1">
+    <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Adrián Torres Zarrías</t>
@@ -716,7 +715,7 @@
       <c r="AE3" s="3" t="inlineStr"/>
       <c r="AF3" s="3" t="inlineStr"/>
     </row>
-    <row r="4" ht="25" customHeight="1">
+    <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Alberto Gómez Marín</t>
@@ -754,7 +753,7 @@
       <c r="AE4" s="3" t="inlineStr"/>
       <c r="AF4" s="3" t="inlineStr"/>
     </row>
-    <row r="5" ht="25" customHeight="1">
+    <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Antonio Escalzo Morales</t>
@@ -792,7 +791,7 @@
       <c r="AE5" s="3" t="inlineStr"/>
       <c r="AF5" s="3" t="inlineStr"/>
     </row>
-    <row r="6" ht="25" customHeight="1">
+    <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Antonio Ramón Fuentes Medina</t>
@@ -830,7 +829,7 @@
       <c r="AE6" s="3" t="inlineStr"/>
       <c r="AF6" s="3" t="inlineStr"/>
     </row>
-    <row r="7" ht="25" customHeight="1">
+    <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Antonio Ruíz Perete</t>
@@ -868,7 +867,7 @@
       <c r="AE7" s="3" t="inlineStr"/>
       <c r="AF7" s="3" t="inlineStr"/>
     </row>
-    <row r="8" ht="25" customHeight="1">
+    <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Fabio Gutiérrez Basante</t>
@@ -906,7 +905,7 @@
       <c r="AE8" s="3" t="inlineStr"/>
       <c r="AF8" s="3" t="inlineStr"/>
     </row>
-    <row r="9" ht="25" customHeight="1">
+    <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Francisco Javier Cárdenas Moga</t>
@@ -944,7 +943,7 @@
       <c r="AE9" s="3" t="inlineStr"/>
       <c r="AF9" s="3" t="inlineStr"/>
     </row>
-    <row r="10" ht="25" customHeight="1">
+    <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Francisco Ordoñez Perabá</t>
@@ -982,7 +981,7 @@
       <c r="AE10" s="3" t="inlineStr"/>
       <c r="AF10" s="3" t="inlineStr"/>
     </row>
-    <row r="11" ht="25" customHeight="1">
+    <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Héctor López Ramírez</t>
@@ -1020,7 +1019,7 @@
       <c r="AE11" s="3" t="inlineStr"/>
       <c r="AF11" s="3" t="inlineStr"/>
     </row>
-    <row r="12" ht="25" customHeight="1">
+    <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Javier Galera Andújar</t>
@@ -1058,7 +1057,7 @@
       <c r="AE12" s="3" t="inlineStr"/>
       <c r="AF12" s="3" t="inlineStr"/>
     </row>
-    <row r="13" ht="25" customHeight="1">
+    <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Jesús Montilla Hermoso</t>
@@ -1096,7 +1095,7 @@
       <c r="AE13" s="3" t="inlineStr"/>
       <c r="AF13" s="3" t="inlineStr"/>
     </row>
-    <row r="14" ht="25" customHeight="1">
+    <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Juan José Borrás Ferrete</t>
@@ -1134,7 +1133,7 @@
       <c r="AE14" s="3" t="inlineStr"/>
       <c r="AF14" s="3" t="inlineStr"/>
     </row>
-    <row r="15" ht="25" customHeight="1">
+    <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Lourdes Fuentes Buendía</t>
@@ -1172,7 +1171,7 @@
       <c r="AE15" s="3" t="inlineStr"/>
       <c r="AF15" s="3" t="inlineStr"/>
     </row>
-    <row r="16" ht="25" customHeight="1">
+    <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Luis Miguel Colmenero Cobo</t>
@@ -1210,7 +1209,7 @@
       <c r="AE16" s="3" t="inlineStr"/>
       <c r="AF16" s="3" t="inlineStr"/>
     </row>
-    <row r="17" ht="25" customHeight="1">
+    <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Manuel Martín Martínez</t>
@@ -1248,7 +1247,7 @@
       <c r="AE17" s="3" t="inlineStr"/>
       <c r="AF17" s="3" t="inlineStr"/>
     </row>
-    <row r="18" ht="25" customHeight="1">
+    <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Manuel Peinado García</t>
@@ -1286,7 +1285,7 @@
       <c r="AE18" s="3" t="inlineStr"/>
       <c r="AF18" s="3" t="inlineStr"/>
     </row>
-    <row r="19" ht="25" customHeight="1">
+    <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Tomás García</t>
@@ -1324,7 +1323,7 @@
       <c r="AE19" s="3" t="inlineStr"/>
       <c r="AF19" s="3" t="inlineStr"/>
     </row>
-    <row r="20" ht="25" customHeight="1">
+    <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Victoria Romero Sabalete</t>

--- a/Cuadrante_Marzo_2026.xlsx
+++ b/Cuadrante_Marzo_2026.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF20"/>
+  <dimension ref="A1:AF15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.42578125" customWidth="1" min="1" max="1"/>
@@ -642,724 +642,1848 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Adrián Iniesta Punzano</t>
+          <t>Antonio Escalzo Morales</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr"/>
-      <c r="C2" s="3" t="inlineStr"/>
-      <c r="D2" s="3" t="inlineStr"/>
-      <c r="E2" s="3" t="inlineStr"/>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>07:58-14:01
+15:01-17:31</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>08:00-13:59
+14:58-17:35</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>VACACIONES</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>08:05-13:56
+15:02-17:26</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:04-13:58
+</t>
+        </is>
+      </c>
       <c r="H2" s="3" t="inlineStr"/>
       <c r="I2" s="3" t="inlineStr"/>
-      <c r="J2" s="3" t="inlineStr"/>
-      <c r="K2" s="3" t="inlineStr"/>
-      <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr"/>
-      <c r="N2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>07:58-14:03
+15:03-17:26</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>08:05-14:01
+14:56-17:29</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>VACACIONES</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>07:56-14:02
+15:02-17:30</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:03-14:05
+</t>
+        </is>
+      </c>
       <c r="O2" s="3" t="inlineStr"/>
       <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>07:57-13:56
+15:04-17:31</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>07:57-13:58
+15:02-17:35</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>08:02-14:00
+15:00-17:34</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>08:04-13:59
+15:04-17:33</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:04-13:55
+</t>
+        </is>
+      </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" s="3" t="inlineStr"/>
-      <c r="X2" s="3" t="inlineStr"/>
-      <c r="Y2" s="3" t="inlineStr"/>
-      <c r="Z2" s="3" t="inlineStr"/>
-      <c r="AA2" s="3" t="inlineStr"/>
-      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>08:01-13:56
+14:59-17:31</t>
+        </is>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
+        <is>
+          <t>08:05-14:03
+15:05-17:32</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>08:02-13:58
+14:57-17:26</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="inlineStr">
+        <is>
+          <t>07:58-14:05
+14:56-17:31</t>
+        </is>
+      </c>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00-13:56
+</t>
+        </is>
+      </c>
       <c r="AC2" s="3" t="inlineStr"/>
       <c r="AD2" s="3" t="inlineStr"/>
-      <c r="AE2" s="3" t="inlineStr"/>
-      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AE2" s="3" t="inlineStr">
+        <is>
+          <t>VACACIONES</t>
+        </is>
+      </c>
+      <c r="AF2" s="3" t="inlineStr">
+        <is>
+          <t>07:58-14:05
+14:58-17:28</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Adrián Torres Zarrías</t>
+          <t>Antonio Ramón Fuentes Medina</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>07:02-15:01</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>06:55-14:57</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>07:01-15:01</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>07:00-15:05</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>06:55-15:00</t>
+        </is>
+      </c>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>06:56-15:05</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>06:59-15:04</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>07:05-14:55</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>06:56-15:01</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>07:04-15:03</t>
+        </is>
+      </c>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>07:03-14:57</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>06:56-14:55</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>06:57-14:57</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>06:56-14:57</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>06:56-15:05</t>
+        </is>
+      </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr"/>
-      <c r="Y3" s="3" t="inlineStr"/>
-      <c r="Z3" s="3" t="inlineStr"/>
-      <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>06:55-14:59</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>07:05-15:05</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>06:59-14:55</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>07:05-15:00</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>07:02-14:55</t>
+        </is>
+      </c>
       <c r="AC3" s="3" t="inlineStr"/>
       <c r="AD3" s="3" t="inlineStr"/>
-      <c r="AE3" s="3" t="inlineStr"/>
-      <c r="AF3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>VACACIONES</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>06:59-15:06</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Alberto Gómez Marín</t>
+          <t>Antonio Ruíz Perete</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr"/>
-      <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>06:58-15:05</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>06:57-15:01</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>07:02-14:58</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>VACACIONES</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>VACACIONES</t>
+        </is>
+      </c>
       <c r="H4" s="3" t="inlineStr"/>
       <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>07:03-15:04</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>07:00-14:58</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>07:04-15:00</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>07:02-15:03</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>VACACIONES</t>
+        </is>
+      </c>
       <c r="O4" s="3" t="inlineStr"/>
       <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>06:59-14:55</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>06:55-15:04</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>07:02-15:01</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>07:05-14:58</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>07:05-14:55</t>
+        </is>
+      </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" s="3" t="inlineStr"/>
-      <c r="X4" s="3" t="inlineStr"/>
-      <c r="Y4" s="3" t="inlineStr"/>
-      <c r="Z4" s="3" t="inlineStr"/>
-      <c r="AA4" s="3" t="inlineStr"/>
-      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>07:04-15:03</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>07:03-15:00</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>06:55-14:58</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>07:03-14:55</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>07:05-15:04</t>
+        </is>
+      </c>
       <c r="AC4" s="3" t="inlineStr"/>
       <c r="AD4" s="3" t="inlineStr"/>
-      <c r="AE4" s="3" t="inlineStr"/>
-      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>VACACIONES</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>07:01-14:59</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Antonio Escalzo Morales</t>
+          <t>Fabio Gutiérrez Basante</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>07:01-15:05</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>07:03-15:04</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>06:58-14:58</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>06:55-14:55</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>07:01-14:58</t>
+        </is>
+      </c>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>07:04-14:55</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>06:58-14:55</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>07:01-14:59</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>06:58-15:01</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>07:00-15:01</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>06:56-15:03</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>06:58-15:05</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>06:57-15:02</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>06:57-14:56</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>06:57-15:05</t>
+        </is>
+      </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="inlineStr"/>
-      <c r="Y5" s="3" t="inlineStr"/>
-      <c r="Z5" s="3" t="inlineStr"/>
-      <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>06:58-15:05</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>06:58-14:56</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>07:04-14:58</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>07:02-15:01</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>07:01-14:57</t>
+        </is>
+      </c>
       <c r="AC5" s="3" t="inlineStr"/>
       <c r="AD5" s="3" t="inlineStr"/>
-      <c r="AE5" s="3" t="inlineStr"/>
-      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>07:04-15:05</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>06:57-15:02</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Antonio Ramón Fuentes Medina</t>
+          <t>Francisco Javier Cárdenas Moga</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr"/>
-      <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>07:01-14:56</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>06:56-14:56</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>07:02-14:56</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>07:05-14:57</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>07:00-15:00</t>
+        </is>
+      </c>
       <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr"/>
-      <c r="N6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>07:05-15:05</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>06:57-15:04</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>06:55-14:56</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>07:04-14:57</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>07:04-15:03</t>
+        </is>
+      </c>
       <c r="O6" s="3" t="inlineStr"/>
       <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr"/>
-      <c r="U6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>06:55-14:55</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>06:58-14:57</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>06:58-15:05</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>06:55-14:56</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>06:56-15:01</t>
+        </is>
+      </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" s="3" t="inlineStr"/>
-      <c r="X6" s="3" t="inlineStr"/>
-      <c r="Y6" s="3" t="inlineStr"/>
-      <c r="Z6" s="3" t="inlineStr"/>
-      <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>07:04-15:04</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>07:03-14:56</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>07:04-15:01</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>06:59-15:05</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>06:55-14:55</t>
+        </is>
+      </c>
       <c r="AC6" s="3" t="inlineStr"/>
       <c r="AD6" s="3" t="inlineStr"/>
-      <c r="AE6" s="3" t="inlineStr"/>
-      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>07:01-15:02</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>07:02-15:01</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Antonio Ruíz Perete</t>
+          <t>Francisco Ordoñez Perabá</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>07:57-14:01
+14:56-17:30</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>08:04-14:03
+14:56-17:32</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>07:59-14:00
+14:55-17:31</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>07:57-13:57
+15:04-17:33</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:05-14:05
+</t>
+        </is>
+      </c>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>07:55-13:59
+15:04-17:29</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>07:58-14:05
+14:59-17:25</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>07:57-14:03
+15:04-16:31</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>08:00-13:58
+14:59-17:32</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:02-13:56
+</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr"/>
-      <c r="U7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>07:57-14:05
+14:55-17:35</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>08:03-14:05
+14:56-17:34</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>08:00-14:04
+14:55-17:25</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>07:58-13:57
+14:56-17:26</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:57-14:02
+</t>
+        </is>
+      </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr"/>
-      <c r="Y7" s="3" t="inlineStr"/>
-      <c r="Z7" s="3" t="inlineStr"/>
-      <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>07:58-13:56
+14:59-17:34</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>08:04-14:03
+14:56-17:34</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>08:00-13:56
+14:58-17:29</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>08:00-14:03
+15:02-17:26</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:55-13:57
+</t>
+        </is>
+      </c>
       <c r="AC7" s="3" t="inlineStr"/>
       <c r="AD7" s="3" t="inlineStr"/>
-      <c r="AE7" s="3" t="inlineStr"/>
-      <c r="AF7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>08:05-14:02
+15:03-17:25</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>08:02-13:55
+14:57-17:34</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Fabio Gutiérrez Basante</t>
+          <t>Héctor López Ramírez</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr"/>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>07:04-15:00</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>07:04-15:01</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>07:02-15:01</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>06:57-14:56</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>07:03-15:01</t>
+        </is>
+      </c>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr"/>
-      <c r="N8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>06:58-15:04</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>07:03-14:56</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>07:02-14:56</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>07:02-14:56</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>07:04-15:04</t>
+        </is>
+      </c>
       <c r="O8" s="3" t="inlineStr"/>
       <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr"/>
-      <c r="U8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>06:56-14:57</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>06:57-14:56</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>06:58-14:57</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>06:56-14:58</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>06:57-14:56</t>
+        </is>
+      </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" s="3" t="inlineStr"/>
-      <c r="X8" s="3" t="inlineStr"/>
-      <c r="Y8" s="3" t="inlineStr"/>
-      <c r="Z8" s="3" t="inlineStr"/>
-      <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr"/>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>07:04-14:56</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>07:01-15:04</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>06:59-15:00</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>07:05-15:04</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>07:01-15:02</t>
+        </is>
+      </c>
       <c r="AC8" s="3" t="inlineStr"/>
       <c r="AD8" s="3" t="inlineStr"/>
-      <c r="AE8" s="3" t="inlineStr"/>
-      <c r="AF8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>06:58-15:00</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>06:57-14:56</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Francisco Javier Cárdenas Moga</t>
+          <t>Javier Galera Andújar</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>07:05-14:59</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>07:02-15:02</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>07:00-15:01</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>07:01-15:02</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>07:03-15:03</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr"/>
-      <c r="N9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>07:03-15:05</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>07:05-14:59</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>06:57-14:57</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>07:05-14:56</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>07:04-14:59</t>
+        </is>
+      </c>
       <c r="O9" s="3" t="inlineStr"/>
       <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr"/>
-      <c r="U9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>06:55-15:02</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>07:01-14:55</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t>07:02-15:02</t>
+        </is>
+      </c>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>06:58-15:01</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>06:56-15:04</t>
+        </is>
+      </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" s="3" t="inlineStr"/>
-      <c r="X9" s="3" t="inlineStr"/>
-      <c r="Y9" s="3" t="inlineStr"/>
-      <c r="Z9" s="3" t="inlineStr"/>
-      <c r="AA9" s="3" t="inlineStr"/>
-      <c r="AB9" s="3" t="inlineStr"/>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>07:02-15:02</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>06:59-14:56</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>07:03-15:05</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>06:55-15:02</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>06:58-14:57</t>
+        </is>
+      </c>
       <c r="AC9" s="3" t="inlineStr"/>
       <c r="AD9" s="3" t="inlineStr"/>
-      <c r="AE9" s="3" t="inlineStr"/>
-      <c r="AF9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>VACACIONES</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>06:56-15:01</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Francisco Ordoñez Perabá</t>
+          <t>Juan José Borrás Ferrete</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr"/>
-      <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="3" t="inlineStr"/>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>06:57-15:01</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>VACACIONES</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>07:05-15:01</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>07:00-14:56</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>06:57-14:55</t>
+        </is>
+      </c>
       <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="inlineStr"/>
-      <c r="J10" s="3" t="inlineStr"/>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr"/>
-      <c r="N10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>06:58-15:01</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>07:01-14:56</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>06:56-15:05</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>06:56-15:00</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>07:04-14:58</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="inlineStr"/>
       <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr"/>
-      <c r="U10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>06:59-15:03</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>VACACIONES</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t>06:55-15:01</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>07:04-15:04</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>06:57-15:02</t>
+        </is>
+      </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" s="3" t="inlineStr"/>
-      <c r="X10" s="3" t="inlineStr"/>
-      <c r="Y10" s="3" t="inlineStr"/>
-      <c r="Z10" s="3" t="inlineStr"/>
-      <c r="AA10" s="3" t="inlineStr"/>
-      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>06:55-14:55</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>07:04-15:05</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>06:55-15:00</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>07:01-14:59</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>07:03-14:55</t>
+        </is>
+      </c>
       <c r="AC10" s="3" t="inlineStr"/>
       <c r="AD10" s="3" t="inlineStr"/>
-      <c r="AE10" s="3" t="inlineStr"/>
-      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>06:57-15:04</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>06:57-15:03</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Héctor López Ramírez</t>
+          <t>Lourdes Fuentes Buendía</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr"/>
-      <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>VACACIONES</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>VACACIONES</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>08:02-13:58
+14:58-17:35</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>08:00-14:05
+14:55-17:33</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:05-13:55
+</t>
+        </is>
+      </c>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="3" t="inlineStr"/>
-      <c r="K11" s="3" t="inlineStr"/>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr"/>
-      <c r="N11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>07:58-14:00
+14:58-17:35</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>07:58-13:58
+14:57-17:26</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>07:57-13:59
+15:04-17:33</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>07:57-14:03
+15:05-17:33</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:57-13:55
+</t>
+        </is>
+      </c>
       <c r="O11" s="3" t="inlineStr"/>
       <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr"/>
-      <c r="U11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>VACACIONES</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>07:56-14:04
+15:00-17:25</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>08:05-14:00
+14:57-17:33</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>08:01-14:02
+15:05-17:34</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:05-14:01
+</t>
+        </is>
+      </c>
       <c r="V11" s="3" t="inlineStr"/>
       <c r="W11" s="3" t="inlineStr"/>
-      <c r="X11" s="3" t="inlineStr"/>
-      <c r="Y11" s="3" t="inlineStr"/>
-      <c r="Z11" s="3" t="inlineStr"/>
-      <c r="AA11" s="3" t="inlineStr"/>
-      <c r="AB11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>08:02-14:05
+15:00-17:25</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>08:01-14:02
+14:58-17:30</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>07:59-14:02
+14:59-17:30</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>07:57-14:04
+14:55-17:27</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:04-13:56
+</t>
+        </is>
+      </c>
       <c r="AC11" s="3" t="inlineStr"/>
       <c r="AD11" s="3" t="inlineStr"/>
-      <c r="AE11" s="3" t="inlineStr"/>
-      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>07:59-13:58
+15:01-17:28</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>07:57-14:05
+15:04-17:31</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Javier Galera Andújar</t>
+          <t>Manuel Martín Martínez</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr"/>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
       <c r="H12" s="3" t="inlineStr"/>
       <c r="I12" s="3" t="inlineStr"/>
-      <c r="J12" s="3" t="inlineStr"/>
-      <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr"/>
-      <c r="N12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
       <c r="O12" s="3" t="inlineStr"/>
       <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr"/>
-      <c r="T12" s="3" t="inlineStr"/>
-      <c r="U12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
       <c r="V12" s="3" t="inlineStr"/>
       <c r="W12" s="3" t="inlineStr"/>
-      <c r="X12" s="3" t="inlineStr"/>
-      <c r="Y12" s="3" t="inlineStr"/>
-      <c r="Z12" s="3" t="inlineStr"/>
-      <c r="AA12" s="3" t="inlineStr"/>
-      <c r="AB12" s="3" t="inlineStr"/>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>08:01-14:02</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>07:59-13:59</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>08:05-13:56</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>07:57-13:56</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>08:00-14:01</t>
+        </is>
+      </c>
       <c r="AC12" s="3" t="inlineStr"/>
       <c r="AD12" s="3" t="inlineStr"/>
-      <c r="AE12" s="3" t="inlineStr"/>
-      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>08:04-14:02</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>08:05-14:01</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Jesús Montilla Hermoso</t>
+          <t>Manuel Peinado García</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr"/>
-      <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>07:00-14:57</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>07:01-14:59</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>06:58-14:58</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>06:58-14:56</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>06:56-14:58</t>
+        </is>
+      </c>
       <c r="H13" s="3" t="inlineStr"/>
       <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="3" t="inlineStr"/>
-      <c r="K13" s="3" t="inlineStr"/>
-      <c r="L13" s="3" t="inlineStr"/>
-      <c r="M13" s="3" t="inlineStr"/>
-      <c r="N13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>06:58-14:57</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>07:01-14:55</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>07:00-14:57</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>06:59-15:02</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>06:56-14:55</t>
+        </is>
+      </c>
       <c r="O13" s="3" t="inlineStr"/>
       <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="3" t="inlineStr"/>
-      <c r="R13" s="3" t="inlineStr"/>
-      <c r="S13" s="3" t="inlineStr"/>
-      <c r="T13" s="3" t="inlineStr"/>
-      <c r="U13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>09:02-13:58</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>08:56-14:00</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t>08:59-13:55</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t>09:04-13:56</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>08:56-13:56</t>
+        </is>
+      </c>
       <c r="V13" s="3" t="inlineStr"/>
       <c r="W13" s="3" t="inlineStr"/>
-      <c r="X13" s="3" t="inlineStr"/>
-      <c r="Y13" s="3" t="inlineStr"/>
-      <c r="Z13" s="3" t="inlineStr"/>
-      <c r="AA13" s="3" t="inlineStr"/>
-      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>07:01-15:00</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>07:01-15:00</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>06:57-14:59</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>06:58-15:00</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>07:05-15:05</t>
+        </is>
+      </c>
       <c r="AC13" s="3" t="inlineStr"/>
       <c r="AD13" s="3" t="inlineStr"/>
-      <c r="AE13" s="3" t="inlineStr"/>
-      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>07:04-15:02</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>07:05-15:01</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Juan José Borrás Ferrete</t>
+          <t>Tomás García</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr"/>
-      <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>07:03-15:01</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>07:01-14:58</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>06:57-15:02</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>12:05-14:55</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>06:59-15:03</t>
+        </is>
+      </c>
       <c r="H14" s="3" t="inlineStr"/>
       <c r="I14" s="3" t="inlineStr"/>
-      <c r="J14" s="3" t="inlineStr"/>
-      <c r="K14" s="3" t="inlineStr"/>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr"/>
-      <c r="N14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>06:55-15:04</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>07:05-14:55</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>06:59-15:00</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>07:03-15:00</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>07:03-14:58</t>
+        </is>
+      </c>
       <c r="O14" s="3" t="inlineStr"/>
       <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
-      <c r="T14" s="3" t="inlineStr"/>
-      <c r="U14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>06:56-14:55</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>07:05-15:02</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t>07:02-14:55</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>06:55-14:57</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>06:56-14:57</t>
+        </is>
+      </c>
       <c r="V14" s="3" t="inlineStr"/>
       <c r="W14" s="3" t="inlineStr"/>
-      <c r="X14" s="3" t="inlineStr"/>
-      <c r="Y14" s="3" t="inlineStr"/>
-      <c r="Z14" s="3" t="inlineStr"/>
-      <c r="AA14" s="3" t="inlineStr"/>
-      <c r="AB14" s="3" t="inlineStr"/>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>06:57-15:01</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>06:59-14:59</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>07:03-15:05</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>06:57-14:58</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>06:56-14:58</t>
+        </is>
+      </c>
       <c r="AC14" s="3" t="inlineStr"/>
       <c r="AD14" s="3" t="inlineStr"/>
-      <c r="AE14" s="3" t="inlineStr"/>
-      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>06:59-14:57</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>06:58-15:04</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Lourdes Fuentes Buendía</t>
+          <t>Victoria Romero Sabalete</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr"/>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr"/>
-      <c r="G15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>08:01-13:59
+14:55-17:32</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>07:55-14:00
+15:02-17:31</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>07:55-13:57
+15:01-17:32</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>07:55-14:03
+14:57-17:25</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:55-14:04
+</t>
+        </is>
+      </c>
       <c r="H15" s="3" t="inlineStr"/>
       <c r="I15" s="3" t="inlineStr"/>
-      <c r="J15" s="3" t="inlineStr"/>
-      <c r="K15" s="3" t="inlineStr"/>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr"/>
-      <c r="N15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>07:59-14:05
+15:01-17:34</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>07:58-14:04
+14:59-17:30</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>07:56-14:04
+14:55-17:34</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>07:58-14:04
+15:02-17:34</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:03-13:59
+</t>
+        </is>
+      </c>
       <c r="O15" s="3" t="inlineStr"/>
       <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr"/>
-      <c r="T15" s="3" t="inlineStr"/>
-      <c r="U15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>08:04-13:59
+15:03-17:29</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>08:04-14:00
+15:05-17:27</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t>07:55-14:05
+15:04-17:30</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t>07:56-13:56
+14:59-17:28</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00-14:04
+</t>
+        </is>
+      </c>
       <c r="V15" s="3" t="inlineStr"/>
       <c r="W15" s="3" t="inlineStr"/>
-      <c r="X15" s="3" t="inlineStr"/>
-      <c r="Y15" s="3" t="inlineStr"/>
-      <c r="Z15" s="3" t="inlineStr"/>
-      <c r="AA15" s="3" t="inlineStr"/>
-      <c r="AB15" s="3" t="inlineStr"/>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>08:01-13:55
+14:59-17:27</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>07:58-13:59
+15:05-17:31</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>07:58-14:00
+14:57-17:28</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>08:03-14:02
+15:03-17:32</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:57-14:01
+</t>
+        </is>
+      </c>
       <c r="AC15" s="3" t="inlineStr"/>
       <c r="AD15" s="3" t="inlineStr"/>
-      <c r="AE15" s="3" t="inlineStr"/>
-      <c r="AF15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Luis Miguel Colmenero Cobo</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr"/>
-      <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
-      <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr"/>
-      <c r="J16" s="3" t="inlineStr"/>
-      <c r="K16" s="3" t="inlineStr"/>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr"/>
-      <c r="N16" s="3" t="inlineStr"/>
-      <c r="O16" s="3" t="inlineStr"/>
-      <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr"/>
-      <c r="T16" s="3" t="inlineStr"/>
-      <c r="U16" s="3" t="inlineStr"/>
-      <c r="V16" s="3" t="inlineStr"/>
-      <c r="W16" s="3" t="inlineStr"/>
-      <c r="X16" s="3" t="inlineStr"/>
-      <c r="Y16" s="3" t="inlineStr"/>
-      <c r="Z16" s="3" t="inlineStr"/>
-      <c r="AA16" s="3" t="inlineStr"/>
-      <c r="AB16" s="3" t="inlineStr"/>
-      <c r="AC16" s="3" t="inlineStr"/>
-      <c r="AD16" s="3" t="inlineStr"/>
-      <c r="AE16" s="3" t="inlineStr"/>
-      <c r="AF16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Manuel Martín Martínez</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr"/>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr"/>
-      <c r="J17" s="3" t="inlineStr"/>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr"/>
-      <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr"/>
-      <c r="P17" s="3" t="inlineStr"/>
-      <c r="Q17" s="3" t="inlineStr"/>
-      <c r="R17" s="3" t="inlineStr"/>
-      <c r="S17" s="3" t="inlineStr"/>
-      <c r="T17" s="3" t="inlineStr"/>
-      <c r="U17" s="3" t="inlineStr"/>
-      <c r="V17" s="3" t="inlineStr"/>
-      <c r="W17" s="3" t="inlineStr"/>
-      <c r="X17" s="3" t="inlineStr"/>
-      <c r="Y17" s="3" t="inlineStr"/>
-      <c r="Z17" s="3" t="inlineStr"/>
-      <c r="AA17" s="3" t="inlineStr"/>
-      <c r="AB17" s="3" t="inlineStr"/>
-      <c r="AC17" s="3" t="inlineStr"/>
-      <c r="AD17" s="3" t="inlineStr"/>
-      <c r="AE17" s="3" t="inlineStr"/>
-      <c r="AF17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Manuel Peinado García</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr"/>
-      <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="3" t="inlineStr"/>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="3" t="inlineStr"/>
-      <c r="J18" s="3" t="inlineStr"/>
-      <c r="K18" s="3" t="inlineStr"/>
-      <c r="L18" s="3" t="inlineStr"/>
-      <c r="M18" s="3" t="inlineStr"/>
-      <c r="N18" s="3" t="inlineStr"/>
-      <c r="O18" s="3" t="inlineStr"/>
-      <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="3" t="inlineStr"/>
-      <c r="R18" s="3" t="inlineStr"/>
-      <c r="S18" s="3" t="inlineStr"/>
-      <c r="T18" s="3" t="inlineStr"/>
-      <c r="U18" s="3" t="inlineStr"/>
-      <c r="V18" s="3" t="inlineStr"/>
-      <c r="W18" s="3" t="inlineStr"/>
-      <c r="X18" s="3" t="inlineStr"/>
-      <c r="Y18" s="3" t="inlineStr"/>
-      <c r="Z18" s="3" t="inlineStr"/>
-      <c r="AA18" s="3" t="inlineStr"/>
-      <c r="AB18" s="3" t="inlineStr"/>
-      <c r="AC18" s="3" t="inlineStr"/>
-      <c r="AD18" s="3" t="inlineStr"/>
-      <c r="AE18" s="3" t="inlineStr"/>
-      <c r="AF18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Tomás García</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr"/>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
-      <c r="K19" s="3" t="inlineStr"/>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr"/>
-      <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="3" t="inlineStr"/>
-      <c r="R19" s="3" t="inlineStr"/>
-      <c r="S19" s="3" t="inlineStr"/>
-      <c r="T19" s="3" t="inlineStr"/>
-      <c r="U19" s="3" t="inlineStr"/>
-      <c r="V19" s="3" t="inlineStr"/>
-      <c r="W19" s="3" t="inlineStr"/>
-      <c r="X19" s="3" t="inlineStr"/>
-      <c r="Y19" s="3" t="inlineStr"/>
-      <c r="Z19" s="3" t="inlineStr"/>
-      <c r="AA19" s="3" t="inlineStr"/>
-      <c r="AB19" s="3" t="inlineStr"/>
-      <c r="AC19" s="3" t="inlineStr"/>
-      <c r="AD19" s="3" t="inlineStr"/>
-      <c r="AE19" s="3" t="inlineStr"/>
-      <c r="AF19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Victoria Romero Sabalete</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr"/>
-      <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr"/>
-      <c r="K20" s="3" t="inlineStr"/>
-      <c r="L20" s="3" t="inlineStr"/>
-      <c r="M20" s="3" t="inlineStr"/>
-      <c r="N20" s="3" t="inlineStr"/>
-      <c r="O20" s="3" t="inlineStr"/>
-      <c r="P20" s="3" t="inlineStr"/>
-      <c r="Q20" s="3" t="inlineStr"/>
-      <c r="R20" s="3" t="inlineStr"/>
-      <c r="S20" s="3" t="inlineStr"/>
-      <c r="T20" s="3" t="inlineStr"/>
-      <c r="U20" s="3" t="inlineStr"/>
-      <c r="V20" s="3" t="inlineStr"/>
-      <c r="W20" s="3" t="inlineStr"/>
-      <c r="X20" s="3" t="inlineStr"/>
-      <c r="Y20" s="3" t="inlineStr"/>
-      <c r="Z20" s="3" t="inlineStr"/>
-      <c r="AA20" s="3" t="inlineStr"/>
-      <c r="AB20" s="3" t="inlineStr"/>
-      <c r="AC20" s="3" t="inlineStr"/>
-      <c r="AD20" s="3" t="inlineStr"/>
-      <c r="AE20" s="3" t="inlineStr"/>
-      <c r="AF20" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>08:03-14:04
+14:55-17:27</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>07:59-13:58
+15:03-17:35</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
